--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
@@ -28,7 +28,7 @@
   <commentList>
     <comment ref="A5" authorId="0">
       <text>
-        <t>ObjectID:90CB12B4-AF30-AFCD-5004-C4E7BD5CD67F;
+        <t>ObjectID:F099B3DF-FFD7-ADB7-9E62-B7016BECF545;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
@@ -44,505 +44,469 @@
     </comment>
     <comment ref="B9" authorId="0">
       <text>
-        <t>ObjectID:81011408-6140-186E-5869-1329F0D44FFA;
+        <t>ObjectID:5B69656A-7F33-E185-FCF1-C244B2662860;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B10" authorId="0">
       <text>
-        <t>ObjectID:BF7E657D-D05A-0499-FF45-39AE4BBD13D2;
+        <t>ObjectID:C8ED7A2E-0E35-1723-F199-7CD4839E3396;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B11" authorId="0">
       <text>
-        <t>ObjectID:75F778E7-4EDE-465F-32FD-B90E1F4B531C;
+        <t>ObjectID:1574B20B-7958-BE17-BE7D-0826258DF9A3;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B12" authorId="0">
       <text>
-        <t>ObjectID:A9617C5B-EA01-AC98-2B4D-5ECB781D3C61;
+        <t>ObjectID:698E4F01-DD88-B608-0C9A-D1634D38AFBF;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B13" authorId="0">
       <text>
-        <t>ObjectID:F2311549-D2D8-6641-F158-1FCD5DA72C3D;
+        <t>ObjectID:653A1971-779F-B4B9-7FBB-914EE8B898C9;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B14" authorId="0">
       <text>
-        <t>ObjectID:8D10554B-85A6-E8F3-AE90-98522BF2709B;
+        <t>ObjectID:22BA1EF3-9427-00E2-CCC1-A275A5F620F5;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B15" authorId="0">
       <text>
-        <t>ObjectID:CBBA852B-7229-9871-3604-77B743275958;
+        <t>ObjectID:710DDCAA-0EE1-0FF9-BC2A-F3FCC11596A3;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B20" authorId="0">
       <text>
-        <t>ObjectID:2B5755DD-BFDB-0AB3-056A-013C56E9B981;
+        <t>ObjectID:DB70A20B-321C-B6BE-4A98-86423B2E8D0C;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="B25" authorId="0">
       <text>
-        <t>ObjectID:8E151F29-DD71-1863-9271-C5361CB998AD;
+        <t>ObjectID:80A3210E-DBD0-B637-11EF-D3150820523F;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="B26" authorId="0">
       <text>
-        <t>ObjectID:F9867493-3C18-BFBE-C3FC-760F3ABA9469;
+        <t>ObjectID:5BC2BA8D-5621-5C8B-6033-60FA2A25A79A;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="B27" authorId="0">
       <text>
-        <t>ObjectID:D8819499-57AC-DAD5-088D-D6163DFC88E3;
+        <t>ObjectID:5C5FA035-3EB3-E214-2760-3495D3715ADD;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="A30" authorId="0">
       <text>
-        <t>ObjectID:9EB277BE-7029-BA3A-7ED2-D3038A5BB0F7;
+        <t>ObjectID:110FB069-4B9F-3EC1-6FC7-D416346777ED;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0">
       <text>
-        <t>ObjectID:0A748269-11F0-6F0A-4667-79981867EE71;
+        <t>ObjectID:6F2115D2-8D87-9836-0075-ACD791E2BE36;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0">
       <text>
-        <t>ObjectID:0DC8528D-621E-B3E6-D588-8692D6E45ECE;
+        <t>ObjectID:2D35241E-CEBA-AC61-6912-2CF3AE6F1925;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B36" authorId="0">
       <text>
-        <t>ObjectID:BD88747F-A567-E695-8FB1-F158C888E4A5;
+        <t>ObjectID:7657175C-97CD-6858-648E-BF9BC5AAE675;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B37" authorId="0">
       <text>
-        <t>ObjectID:C6B9DCF9-EBFB-8590-7CB3-4536F9387A30;
+        <t>ObjectID:79A0B868-1A2B-BF19-99BB-53A91A11DB76;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0">
       <text>
-        <t>ObjectID:7961CC4F-BA66-2228-A932-0B0346F7A562;
+        <t>ObjectID:4D1FB96F-EE96-0EC4-8ABD-51B98E0E3C3A;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0">
       <text>
-        <t>ObjectID:116A239F-1C67-FC1B-6815-35D5ACAE992B;
+        <t>ObjectID:04F5CBC1-49DB-830D-8136-AFB4838A0107;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0">
       <text>
-        <t>ObjectID:D4892A06-5DB8-541D-0CE1-87349B9F7CF4;
+        <t>ObjectID:5C831949-DA72-CC51-DDEE-DFF2A2F75FBD;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B41" authorId="0">
       <text>
-        <t>ObjectID:BFBDF889-A7E4-DCFD-EBC4-7B96A816B970;
+        <t>ObjectID:18E79CDA-A52B-1B1A-8064-9A047981504A;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B42" authorId="0">
       <text>
-        <t>ObjectID:1B3869AC-9231-7FC5-BD2B-AF1B3A58E1BC;
+        <t>ObjectID:D7E22633-D71E-98DB-2784-1CAED83A9A72;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0">
       <text>
-        <t>ObjectID:506CC65D-B1AB-F31A-4BA9-517671DDF7B6;
+        <t>ObjectID:9C1E8BC5-965E-F2CD-63EA-B004E7B09001;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B44" authorId="0">
       <text>
-        <t>ObjectID:EFBBC641-A321-85C6-19C5-7484C997CEB6;
+        <t>ObjectID:23F0EB27-605F-2535-ECD1-69A75E435849;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B49" authorId="0">
       <text>
-        <t>ObjectID:DB34C21D-3EE5-7339-632A-053443C65A1D;
+        <t>ObjectID:8228ADF2-B425-5C58-C3B9-476EB4417120;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="B54" authorId="0">
       <text>
-        <t>ObjectID:5672E553-2046-F443-A1CF-5056EFCC6128;
+        <t>ObjectID:E8F9C766-3CC9-B6A7-C6A2-172C8BA0470C;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="B55" authorId="0">
       <text>
-        <t>ObjectID:E465E2CF-3E8A-BC03-97AD-612D80B1ED1A;
+        <t>ObjectID:D76DD9EA-4B1F-05CE-CACD-866627772007;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="A58" authorId="0">
       <text>
-        <t>ObjectID:18144285-2A12-39D4-D8F8-0A3A21C806E9;
+        <t>ObjectID:10CD4E57-CC33-A6D3-E73D-A62766F9D850;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B62" authorId="0">
       <text>
-        <t>ObjectID:5257B76A-61F8-1740-CF51-4561C8C5B6CD;
+        <t>ObjectID:1333B9D9-9696-1371-F865-7DD808AD089E;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B63" authorId="0">
       <text>
-        <t>ObjectID:4958C6A9-8928-AFF9-F8B9-E4368BDF72B4;
+        <t>ObjectID:D1B1DF2C-03FA-FEE0-ABED-072E3494B947;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B68" authorId="0">
       <text>
-        <t>ObjectID:A3A2543F-CEE5-46DD-9744-09F43056D2BD;
+        <t>ObjectID:8844675F-B563-A685-C873-06BCC0A621DD;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="A71" authorId="0">
       <text>
-        <t>ObjectID:6CD2FFF6-9693-F671-C30B-FC18055CE5C9;
+        <t>ObjectID:93BED78F-5A0A-FF99-AFF2-0A3590D753D0;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B75" authorId="0">
       <text>
-        <t>ObjectID:46638D63-590B-1E3B-DBE5-F3F7DEA8BE87;
+        <t>ObjectID:2C2D6C32-CDDE-1181-4D22-DCE1793FF5BA;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B76" authorId="0">
       <text>
-        <t>ObjectID:F0C220D1-1997-F6A7-56B2-19A7C44C6152;
+        <t>ObjectID:6B623415-7C87-A9FD-D3D3-F416E1B56ABF;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B81" authorId="0">
-      <text>
-        <t>ObjectID:22C00C2E-977B-6A07-6FDB-8E01B138AD3B;
+    <comment ref="B77" authorId="0">
+      <text>
+        <t>ObjectID:6C92164C-CFE1-C229-958A-009AF11120A5;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B78" authorId="0">
+      <text>
+        <t>ObjectID:AAE777EE-6A71-1B93-B418-5EB714BC788E;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B79" authorId="0">
+      <text>
+        <t>ObjectID:0DFC53E1-50AE-D648-4130-42B1F6DCB4D4;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B84" authorId="0">
+      <text>
+        <t>ObjectID:71E51909-BE1A-1793-A4C8-BEABC6C15586;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="A84" authorId="0">
-      <text>
-        <t>ObjectID:3C6E51DE-D959-2082-62D4-45B31B87D6BE;
+    <comment ref="B89" authorId="0">
+      <text>
+        <t>ObjectID:D5DB20FC-9280-79DF-2F02-082C8BD8F435;
+Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
+      </text>
+    </comment>
+    <comment ref="A92" authorId="0">
+      <text>
+        <t>ObjectID:BF65AE17-0AF9-04F2-1716-E1684667CD81;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B88" authorId="0">
-      <text>
-        <t>ObjectID:F516FBA4-EF01-065E-D1BD-B89E419DA854;
+    <comment ref="B96" authorId="0">
+      <text>
+        <t>ObjectID:A9DDAE05-9CA5-8E72-33BF-E0F8637B572C;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B89" authorId="0">
-      <text>
-        <t>ObjectID:FD482B8E-FAC4-14B8-B6F7-4BB4493553D6;
+    <comment ref="B97" authorId="0">
+      <text>
+        <t>ObjectID:8AE41AEF-A676-BB67-ED5D-C9F22BEFB21A;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B90" authorId="0">
-      <text>
-        <t>ObjectID:E0B817CD-92CC-96B2-7333-4216A6F1F009;
+    <comment ref="B102" authorId="0">
+      <text>
+        <t>ObjectID:C72427A6-3025-503E-D8A4-93CBF783E7E2;
+Class:oracle.dbtools.crest.model.design.relational.Index</t>
+      </text>
+    </comment>
+    <comment ref="A105" authorId="0">
+      <text>
+        <t>ObjectID:28772467-1A41-DF34-A5DB-69CB3AB66234;
+Class:oracle.dbtools.crest.model.design.relational.Table</t>
+      </text>
+    </comment>
+    <comment ref="B109" authorId="0">
+      <text>
+        <t>ObjectID:89097C79-170F-5F0F-FDC1-39D64F8465C4;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B91" authorId="0">
-      <text>
-        <t>ObjectID:4666453C-838B-2004-8F14-E5FC0FD49A0D;
+    <comment ref="B110" authorId="0">
+      <text>
+        <t>ObjectID:BC4F121E-5923-E986-A08C-6B90C94DD6BD;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B92" authorId="0">
-      <text>
-        <t>ObjectID:885D6A6C-4AA2-2EE3-94EF-A44CE8C47F48;
+    <comment ref="B111" authorId="0">
+      <text>
+        <t>ObjectID:7438F3A9-ADB4-8934-9CCC-4CB01ECAA8A9;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B93" authorId="0">
-      <text>
-        <t>ObjectID:10917FDA-EAFE-66E7-E4AE-80E895184321;
+    <comment ref="B112" authorId="0">
+      <text>
+        <t>ObjectID:5DB03AC7-BC5D-F159-4CCA-CBAD92818D84;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B98" authorId="0">
-      <text>
-        <t>ObjectID:62EBD44D-5232-8674-53C9-D3354174D34D;
+    <comment ref="B117" authorId="0">
+      <text>
+        <t>ObjectID:0027DD8A-B5D8-39F1-73A2-938710632EDE;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B103" authorId="0">
-      <text>
-        <t>ObjectID:AEF47B43-F984-0D17-0267-F3B5CE8756C5;
+    <comment ref="B118" authorId="0">
+      <text>
+        <t>ObjectID:A3C9FD1F-4935-2711-E81E-D995DA501D90;
+Class:oracle.dbtools.crest.model.design.relational.Index</t>
+      </text>
+    </comment>
+    <comment ref="A121" authorId="0">
+      <text>
+        <t>ObjectID:B3EB3E44-6E2D-9092-4C63-39282746F303;
+Class:oracle.dbtools.crest.model.design.relational.Table</t>
+      </text>
+    </comment>
+    <comment ref="B125" authorId="0">
+      <text>
+        <t>ObjectID:2DD45A47-0C43-A14B-3473-B90AF68F03F6;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B126" authorId="0">
+      <text>
+        <t>ObjectID:FF19DD8A-D764-66AF-5F8D-5E16C4913319;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B131" authorId="0">
+      <text>
+        <t>ObjectID:7D599655-479F-CF06-6785-FDFD5C3E1A6E;
+Class:oracle.dbtools.crest.model.design.relational.Index</t>
+      </text>
+    </comment>
+    <comment ref="A134" authorId="0">
+      <text>
+        <t>ObjectID:936957AB-E468-D8E8-4C43-E61F68C0FFDB;
+Class:oracle.dbtools.crest.model.design.relational.Table</t>
+      </text>
+    </comment>
+    <comment ref="B138" authorId="0">
+      <text>
+        <t>ObjectID:CF026949-0856-661A-DDC8-187616158D0D;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B139" authorId="0">
+      <text>
+        <t>ObjectID:79F7CAE0-6AE4-54A4-2C31-BDFD0CB6954C;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B144" authorId="0">
+      <text>
+        <t>ObjectID:6AF01A10-D486-622B-B283-E1B863523EC1;
+Class:oracle.dbtools.crest.model.design.relational.Index</t>
+      </text>
+    </comment>
+    <comment ref="A147" authorId="0">
+      <text>
+        <t>ObjectID:26FCADDF-9C2B-E6B6-DDCB-A27F04FADFF7;
+Class:oracle.dbtools.crest.model.design.relational.Table</t>
+      </text>
+    </comment>
+    <comment ref="B151" authorId="0">
+      <text>
+        <t>ObjectID:185D6D98-500D-9399-704D-6DFA12C3BF78;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B152" authorId="0">
+      <text>
+        <t>ObjectID:00C081FD-BD62-CE0E-D7D0-2A6B20E612FD;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B153" authorId="0">
+      <text>
+        <t>ObjectID:6BD52512-9D6F-03CA-997E-CAFD3EF02709;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B154" authorId="0">
+      <text>
+        <t>ObjectID:A41DFE8A-ED44-B843-8845-8446D81828FE;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B155" authorId="0">
+      <text>
+        <t>ObjectID:430E945F-F718-8C61-B18F-C784F59C90CC;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B156" authorId="0">
+      <text>
+        <t>ObjectID:B422B9F3-FDD2-94F4-FE3D-E6F6D1814D1E;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B161" authorId="0">
+      <text>
+        <t>ObjectID:608EF77C-AE79-DC88-51CF-D18430AE8B9E;
+Class:oracle.dbtools.crest.model.design.relational.Index</t>
+      </text>
+    </comment>
+    <comment ref="B166" authorId="0">
+      <text>
+        <t>ObjectID:24163528-F8BC-B7EF-B825-337D06863EC5;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="B104" authorId="0">
-      <text>
-        <t>ObjectID:F0CDA38B-B9FC-DC3D-6BA2-8159C3CD8503;
+    <comment ref="A169" authorId="0">
+      <text>
+        <t>ObjectID:86B573D7-CD13-EBD4-0C4F-B4DEE60F904A;
+Class:oracle.dbtools.crest.model.design.relational.Table</t>
+      </text>
+    </comment>
+    <comment ref="B173" authorId="0">
+      <text>
+        <t>ObjectID:9FF49873-5D91-649D-4627-2BE70D843F9F;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B174" authorId="0">
+      <text>
+        <t>ObjectID:A9E9D69C-9E14-EE96-C054-F15AB9C32B15;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B175" authorId="0">
+      <text>
+        <t>ObjectID:F3A998D8-1D5F-1C74-2B9B-FC8746DCE908;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B176" authorId="0">
+      <text>
+        <t>ObjectID:A8FA0751-F8E1-215B-1F12-B03EDE8C5C28;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B177" authorId="0">
+      <text>
+        <t>ObjectID:F1AE3A41-44AC-5762-B6B2-1A6B6C11A835;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B178" authorId="0">
+      <text>
+        <t>ObjectID:91D44BE7-0B08-6EA0-1784-F0EB2FC0AC7E;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B179" authorId="0">
+      <text>
+        <t>ObjectID:A0BFE2DC-173F-63A1-2AFD-A301BBCE67A9;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B180" authorId="0">
+      <text>
+        <t>ObjectID:76B9EBD1-4F6E-529B-CBA7-003422B33A73;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B185" authorId="0">
+      <text>
+        <t>ObjectID:5A1C52F7-A087-EF0C-0B33-F8586D15E9E2;
+Class:oracle.dbtools.crest.model.design.relational.Index</t>
+      </text>
+    </comment>
+    <comment ref="B190" authorId="0">
+      <text>
+        <t>ObjectID:41C8E158-D607-C5A8-F3E8-C14D33939608;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="A107" authorId="0">
-      <text>
-        <t>ObjectID:F2C75C8A-7424-7680-AC53-F0DFE07B3F68;
-Class:oracle.dbtools.crest.model.design.relational.Table</t>
-      </text>
-    </comment>
-    <comment ref="B111" authorId="0">
-      <text>
-        <t>ObjectID:DED107D2-07E2-FE6A-19B3-970E7C3D9AC5;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B112" authorId="0">
-      <text>
-        <t>ObjectID:2CA22C0F-3E70-79E3-4CC1-4D8A18C741B5;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B117" authorId="0">
-      <text>
-        <t>ObjectID:C4CE16E0-1C34-C60B-F850-1418FF1D438C;
-Class:oracle.dbtools.crest.model.design.relational.Index</t>
-      </text>
-    </comment>
-    <comment ref="A120" authorId="0">
-      <text>
-        <t>ObjectID:4EA60C2F-6DE0-8FCA-8C38-BE4ADEFBDBC8;
-Class:oracle.dbtools.crest.model.design.relational.Table</t>
-      </text>
-    </comment>
-    <comment ref="B124" authorId="0">
-      <text>
-        <t>ObjectID:C66B576B-F4C3-B565-CBCC-2F9C07762CEB;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B125" authorId="0">
-      <text>
-        <t>ObjectID:5A53AED5-921A-1EAC-CF85-5C1022A47953;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B126" authorId="0">
-      <text>
-        <t>ObjectID:FADC9424-B13F-6201-4225-C82C31C6B6C7;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B127" authorId="0">
-      <text>
-        <t>ObjectID:AC31F942-C982-B549-3F8B-C9A5669F7285;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B132" authorId="0">
-      <text>
-        <t>ObjectID:09070F35-9366-9BDE-093A-87B391F0CC0D;
-Class:oracle.dbtools.crest.model.design.relational.Index</t>
-      </text>
-    </comment>
-    <comment ref="B133" authorId="0">
-      <text>
-        <t>ObjectID:65B650A4-1196-466E-D77A-BC26ECFA0C91;
-Class:oracle.dbtools.crest.model.design.relational.Index</t>
-      </text>
-    </comment>
-    <comment ref="A136" authorId="0">
-      <text>
-        <t>ObjectID:AF2AB5F5-1EE8-D50A-F20B-74D099FA9E1B;
-Class:oracle.dbtools.crest.model.design.relational.Table</t>
-      </text>
-    </comment>
-    <comment ref="B140" authorId="0">
-      <text>
-        <t>ObjectID:88182613-8C6B-8237-4F2B-E8615A23F3CF;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B141" authorId="0">
-      <text>
-        <t>ObjectID:525758B3-8BF8-B3F4-269D-7E269B8FB8D6;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B146" authorId="0">
-      <text>
-        <t>ObjectID:2750E838-82E6-5BA0-1CC6-AF1BCDC7990E;
-Class:oracle.dbtools.crest.model.design.relational.Index</t>
-      </text>
-    </comment>
-    <comment ref="A149" authorId="0">
-      <text>
-        <t>ObjectID:96CFC6A1-ABBE-B422-0E42-6AA357B64458;
-Class:oracle.dbtools.crest.model.design.relational.Table</t>
-      </text>
-    </comment>
-    <comment ref="B153" authorId="0">
-      <text>
-        <t>ObjectID:E562EC6C-79B5-BB43-A61E-0BDCE6F58C77;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B154" authorId="0">
-      <text>
-        <t>ObjectID:22BEF716-1B55-B0BA-1EFD-B33AA7BF463A;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B159" authorId="0">
-      <text>
-        <t>ObjectID:CA986A16-12BB-6001-C706-D958874031BB;
-Class:oracle.dbtools.crest.model.design.relational.Index</t>
-      </text>
-    </comment>
-    <comment ref="A162" authorId="0">
-      <text>
-        <t>ObjectID:69284A30-8A7E-E4B1-0B3F-68E7D639F73B;
-Class:oracle.dbtools.crest.model.design.relational.Table</t>
-      </text>
-    </comment>
-    <comment ref="B166" authorId="0">
-      <text>
-        <t>ObjectID:19F8BCC2-46F4-3860-CEB0-0876A3E8F514;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B167" authorId="0">
-      <text>
-        <t>ObjectID:E125D840-CC95-E1F5-6789-03C58AA73907;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B168" authorId="0">
-      <text>
-        <t>ObjectID:0DED2D0A-5259-C377-320D-508BC6692377;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B169" authorId="0">
-      <text>
-        <t>ObjectID:FC60D487-E0AC-FCB5-5FA7-677B262EFD17;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B170" authorId="0">
-      <text>
-        <t>ObjectID:A93C9E7C-8CE1-EB9D-D8A4-515D60140F83;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B171" authorId="0">
-      <text>
-        <t>ObjectID:B44BE613-54E9-ABE6-BF19-9D383A6E1969;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B176" authorId="0">
-      <text>
-        <t>ObjectID:E989073F-64A2-968B-2476-F9C9A1414F26;
-Class:oracle.dbtools.crest.model.design.relational.Index</t>
-      </text>
-    </comment>
-    <comment ref="B181" authorId="0">
-      <text>
-        <t>ObjectID:8717AB4A-5939-A800-7CEA-EF0E6237C048;
-Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
-      </text>
-    </comment>
-    <comment ref="A184" authorId="0">
-      <text>
-        <t>ObjectID:61405D3B-E3C2-9C1E-3780-7358DAEE4C55;
-Class:oracle.dbtools.crest.model.design.relational.Table</t>
-      </text>
-    </comment>
-    <comment ref="B188" authorId="0">
-      <text>
-        <t>ObjectID:132D178D-440C-BDFB-DFC0-9FB51BF534F4;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B189" authorId="0">
-      <text>
-        <t>ObjectID:216F7602-97B8-7D36-33DB-8D81101285F0;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B190" authorId="0">
-      <text>
-        <t>ObjectID:2B383476-AC5D-1802-D02D-FF4D722B6616;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
     <comment ref="B191" authorId="0">
       <text>
-        <t>ObjectID:18A15F6C-C5AC-809C-69A3-14404A8C4E90;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B192" authorId="0">
-      <text>
-        <t>ObjectID:02FCF6E1-B6F1-B982-748D-28A7D8CC1F28;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B193" authorId="0">
-      <text>
-        <t>ObjectID:4D95F55A-C97C-3C3B-8327-6B534B5E9C7C;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B194" authorId="0">
-      <text>
-        <t>ObjectID:FC8D6ADF-601A-AE62-DF1D-4E3338C2E46F;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B195" authorId="0">
-      <text>
-        <t>ObjectID:6EE0646F-04C9-1688-8164-89699FA34E39;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B200" authorId="0">
-      <text>
-        <t>ObjectID:DA77D18B-BFD6-B633-60E9-7CDE685E7A68;
-Class:oracle.dbtools.crest.model.design.relational.Index</t>
-      </text>
-    </comment>
-    <comment ref="B205" authorId="0">
-      <text>
-        <t>ObjectID:BD842AAB-E5CA-2B05-3971-96A4C81CA41C;
-Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
-      </text>
-    </comment>
-    <comment ref="B206" authorId="0">
-      <text>
-        <t>ObjectID:08041685-0A79-C282-89D5-F8E79385DDB1;
+        <t>ObjectID:0930ED40-A874-E892-AE30-63D24583BC07;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
@@ -551,7 +515,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="367">
   <si>
     <t>Diccionario de datos BD</t>
   </si>
@@ -631,460 +595,430 @@
     <t>generateInDDL</t>
   </si>
   <si>
-    <t>90CB12B4-AF30-AFCD-5004-C4E7BD5CD67F</t>
+    <t>F099B3DF-FFD7-ADB7-9E62-B7016BECF545</t>
   </si>
   <si>
     <t>Address</t>
   </si>
   <si>
-    <t>9EB277BE-7029-BA3A-7ED2-D3038A5BB0F7</t>
+    <t>110FB069-4B9F-3EC1-6FC7-D416346777ED</t>
   </si>
   <si>
     <t>AppUser</t>
   </si>
   <si>
-    <t>18144285-2A12-39D4-D8F8-0A3A21C806E9</t>
-  </si>
-  <si>
-    <t>ChargeType</t>
-  </si>
-  <si>
-    <t>6CD2FFF6-9693-F671-C30B-FC18055CE5C9</t>
+    <t>10CD4E57-CC33-A6D3-E73D-A62766F9D850</t>
   </si>
   <si>
     <t>Comuna</t>
   </si>
   <si>
-    <t>3C6E51DE-D959-2082-62D4-45B31B87D6BE</t>
+    <t>93BED78F-5A0A-FF99-AFF2-0A3590D753D0</t>
   </si>
   <si>
     <t>Contract</t>
   </si>
   <si>
-    <t>F2C75C8A-7424-7680-AC53-F0DFE07B3F68</t>
+    <t>BF65AE17-0AF9-04F2-1716-E1684667CD81</t>
   </si>
   <si>
     <t>Country</t>
   </si>
   <si>
-    <t>4EA60C2F-6DE0-8FCA-8C38-BE4ADEFBDBC8</t>
+    <t>28772467-1A41-DF34-A5DB-69CB3AB66234</t>
   </si>
   <si>
     <t>Device</t>
   </si>
   <si>
-    <t>AF2AB5F5-1EE8-D50A-F20B-74D099FA9E1B</t>
+    <t>B3EB3E44-6E2D-9092-4C63-39282746F303</t>
   </si>
   <si>
     <t>ElectricityCompany</t>
   </si>
   <si>
-    <t>96CFC6A1-ABBE-B422-0E42-6AA357B64458</t>
+    <t>936957AB-E468-D8E8-4C43-E61F68C0FFDB</t>
   </si>
   <si>
     <t>Region</t>
   </si>
   <si>
-    <t>69284A30-8A7E-E4B1-0B3F-68E7D639F73B</t>
+    <t>26FCADDF-9C2B-E6B6-DDCB-A27F04FADFF7</t>
   </si>
   <si>
     <t>Result</t>
   </si>
   <si>
-    <t>61405D3B-E3C2-9C1E-3780-7358DAEE4C55</t>
+    <t>86B573D7-CD13-EBD4-0C4F-B4DEE60F904A</t>
   </si>
   <si>
     <t>UserDevice</t>
   </si>
   <si>
-    <t>132D178D-440C-BDFB-DFC0-9FB51BF534F4</t>
+    <t>9FF49873-5D91-649D-4627-2BE70D843F9F</t>
   </si>
   <si>
     <t>alias</t>
   </si>
   <si>
-    <t>19F8BCC2-46F4-3860-CEB0-0876A3E8F514</t>
+    <t>185D6D98-500D-9399-704D-6DFA12C3BF78</t>
   </si>
   <si>
     <t>ampere</t>
   </si>
   <si>
-    <t>0A748269-11F0-6F0A-4667-79981867EE71</t>
+    <t>6F2115D2-8D87-9836-0075-ACD791E2BE36</t>
   </si>
   <si>
     <t>countryCode</t>
   </si>
   <si>
-    <t>216F7602-97B8-7D36-33DB-8D81101285F0</t>
+    <t>A9E9D69C-9E14-EE96-C054-F15AB9C32B15</t>
   </si>
   <si>
     <t>creationDate</t>
   </si>
   <si>
-    <t>E125D840-CC95-E1F5-6789-03C58AA73907</t>
+    <t>00C081FD-BD62-CE0E-D7D0-2A6B20E612FD</t>
   </si>
   <si>
     <t>date</t>
   </si>
   <si>
-    <t>2B383476-AC5D-1802-D02D-FF4D722B6616</t>
+    <t>5B69656A-7F33-E185-FCF1-C244B2662860</t>
   </si>
   <si>
     <t>description</t>
   </si>
   <si>
-    <t>81011408-6140-186E-5869-1329F0D44FFA</t>
-  </si>
-  <si>
-    <t>0DC8528D-621E-B3E6-D588-8692D6E45ECE</t>
+    <t>F3A998D8-1D5F-1C74-2B9B-FC8746DCE908</t>
+  </si>
+  <si>
+    <t>2C2D6C32-CDDE-1181-4D22-DCE1793FF5BA</t>
+  </si>
+  <si>
+    <t>elecricityCost</t>
+  </si>
+  <si>
+    <t>2D35241E-CEBA-AC61-6912-2CF3AE6F1925</t>
   </si>
   <si>
     <t>email</t>
   </si>
   <si>
-    <t>BD88747F-A567-E695-8FB1-F158C888E4A5</t>
+    <t>7657175C-97CD-6858-648E-BF9BC5AAE675</t>
   </si>
   <si>
     <t>firstName</t>
   </si>
   <si>
-    <t>F516FBA4-EF01-065E-D1BD-B89E419DA854</t>
-  </si>
-  <si>
-    <t>fixedCost</t>
-  </si>
-  <si>
-    <t>5257B76A-61F8-1740-CF51-4561C8C5B6CD</t>
+    <t>C8ED7A2E-0E35-1723-F199-7CD4839E3396</t>
   </si>
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>FD482B8E-FAC4-14B8-B6F7-4BB4493553D6</t>
-  </si>
-  <si>
-    <t>C66B576B-F4C3-B565-CBCC-2F9C07762CEB</t>
-  </si>
-  <si>
-    <t>18A15F6C-C5AC-809C-69A3-14404A8C4E90</t>
-  </si>
-  <si>
-    <t>0DED2D0A-5259-C377-320D-508BC6692377</t>
-  </si>
-  <si>
-    <t>46638D63-590B-1E3B-DBE5-F3F7DEA8BE87</t>
-  </si>
-  <si>
-    <t>BF7E657D-D05A-0499-FF45-39AE4BBD13D2</t>
-  </si>
-  <si>
-    <t>E562EC6C-79B5-BB43-A61E-0BDCE6F58C77</t>
-  </si>
-  <si>
-    <t>C6B9DCF9-EBFB-8590-7CB3-4536F9387A30</t>
-  </si>
-  <si>
-    <t>88182613-8C6B-8237-4F2B-E8615A23F3CF</t>
-  </si>
-  <si>
-    <t>DED107D2-07E2-FE6A-19B3-970E7C3D9AC5</t>
-  </si>
-  <si>
-    <t>7961CC4F-BA66-2228-A932-0B0346F7A562</t>
+    <t>1333B9D9-9696-1371-F865-7DD808AD089E</t>
+  </si>
+  <si>
+    <t>6B623415-7C87-A9FD-D3D3-F416E1B56ABF</t>
+  </si>
+  <si>
+    <t>A9DDAE05-9CA5-8E72-33BF-E0F8637B572C</t>
+  </si>
+  <si>
+    <t>89097C79-170F-5F0F-FDC1-39D64F8465C4</t>
+  </si>
+  <si>
+    <t>2DD45A47-0C43-A14B-3473-B90AF68F03F6</t>
+  </si>
+  <si>
+    <t>6BD52512-9D6F-03CA-997E-CAFD3EF02709</t>
+  </si>
+  <si>
+    <t>79A0B868-1A2B-BF19-99BB-53A91A11DB76</t>
+  </si>
+  <si>
+    <t>A8FA0751-F8E1-215B-1F12-B03EDE8C5C28</t>
+  </si>
+  <si>
+    <t>CF026949-0856-661A-DDC8-187616158D0D</t>
+  </si>
+  <si>
+    <t>4D1FB96F-EE96-0EC4-8ABD-51B98E0E3C3A</t>
   </si>
   <si>
     <t>idAddress</t>
   </si>
   <si>
-    <t>02FCF6E1-B6F1-B982-748D-28A7D8CC1F28</t>
-  </si>
-  <si>
-    <t>idAppUser</t>
-  </si>
-  <si>
-    <t>E0B817CD-92CC-96B2-7333-4216A6F1F009</t>
-  </si>
-  <si>
-    <t>idChargeType</t>
-  </si>
-  <si>
-    <t>75F778E7-4EDE-465F-32FD-B90E1F4B531C</t>
+    <t>1574B20B-7958-BE17-BE7D-0826258DF9A3</t>
   </si>
   <si>
     <t>idComuna</t>
   </si>
   <si>
-    <t>116A239F-1C67-FC1B-6815-35D5ACAE992B</t>
+    <t>04F5CBC1-49DB-830D-8136-AFB4838A0107</t>
   </si>
   <si>
     <t>idContract</t>
   </si>
   <si>
-    <t>A9617C5B-EA01-AC98-2B4D-5ECB781D3C61</t>
+    <t>698E4F01-DD88-B608-0C9A-D1634D38AFBF</t>
   </si>
   <si>
     <t>idCountry</t>
   </si>
   <si>
-    <t>4D95F55A-C97C-3C3B-8327-6B534B5E9C7C</t>
+    <t>F1AE3A41-44AC-5762-B6B2-1A6B6C11A835</t>
   </si>
   <si>
     <t>idDevice</t>
   </si>
   <si>
-    <t>4666453C-838B-2004-8F14-E5FC0FD49A0D</t>
+    <t>6C92164C-CFE1-C229-958A-009AF11120A5</t>
   </si>
   <si>
     <t>idElectricityCompany</t>
   </si>
   <si>
-    <t>F2311549-D2D8-6641-F158-1FCD5DA72C3D</t>
+    <t>653A1971-779F-B4B9-7FBB-914EE8B898C9</t>
   </si>
   <si>
     <t>idRegion</t>
   </si>
   <si>
-    <t>FC60D487-E0AC-FCB5-5FA7-677B262EFD17</t>
+    <t>91D44BE7-0B08-6EA0-1784-F0EB2FC0AC7E</t>
+  </si>
+  <si>
+    <t>idUser</t>
+  </si>
+  <si>
+    <t>A41DFE8A-ED44-B843-8845-8446D81828FE</t>
   </si>
   <si>
     <t>idUserDevice</t>
   </si>
   <si>
-    <t>A93C9E7C-8CE1-EB9D-D8A4-515D60140F83</t>
+    <t>430E945F-F718-8C61-B18F-C784F59C90CC</t>
   </si>
   <si>
     <t>kwh</t>
   </si>
   <si>
-    <t>885D6A6C-4AA2-2EE3-94EF-A44CE8C47F48</t>
-  </si>
-  <si>
-    <t>kwhVariable</t>
-  </si>
-  <si>
-    <t>FC8D6ADF-601A-AE62-DF1D-4E3338C2E46F</t>
+    <t>A0BFE2DC-173F-63A1-2AFD-A301BBCE67A9</t>
   </si>
   <si>
     <t>lastConection</t>
   </si>
   <si>
-    <t>D4892A06-5DB8-541D-0CE1-87349B9F7CF4</t>
+    <t>5C831949-DA72-CC51-DDEE-DFF2A2F75FBD</t>
   </si>
   <si>
     <t>lastName</t>
   </si>
   <si>
-    <t>BFBDF889-A7E4-DCFD-EBC4-7B96A816B970</t>
+    <t>18E79CDA-A52B-1B1A-8064-9A047981504A</t>
   </si>
   <si>
     <t>middleName</t>
   </si>
   <si>
-    <t>5A53AED5-921A-1EAC-CF85-5C1022A47953</t>
+    <t>BC4F121E-5923-E986-A08C-6B90C94DD6BD</t>
   </si>
   <si>
     <t>model</t>
   </si>
   <si>
-    <t>4958C6A9-8928-AFF9-F8B9-E4368BDF72B4</t>
-  </si>
-  <si>
-    <t>FADC9424-B13F-6201-4225-C82C31C6B6C7</t>
-  </si>
-  <si>
-    <t>F0C220D1-1997-F6A7-56B2-19A7C44C6152</t>
-  </si>
-  <si>
-    <t>22BEF716-1B55-B0BA-1EFD-B33AA7BF463A</t>
-  </si>
-  <si>
-    <t>525758B3-8BF8-B3F4-269D-7E269B8FB8D6</t>
-  </si>
-  <si>
-    <t>2CA22C0F-3E70-79E3-4CC1-4D8A18C741B5</t>
-  </si>
-  <si>
-    <t>1B3869AC-9231-7FC5-BD2B-AF1B3A58E1BC</t>
+    <t>D1B1DF2C-03FA-FEE0-ABED-072E3494B947</t>
+  </si>
+  <si>
+    <t>8AE41AEF-A676-BB67-ED5D-C9F22BEFB21A</t>
+  </si>
+  <si>
+    <t>7438F3A9-ADB4-8934-9CCC-4CB01ECAA8A9</t>
+  </si>
+  <si>
+    <t>FF19DD8A-D764-66AF-5F8D-5E16C4913319</t>
+  </si>
+  <si>
+    <t>79F7CAE0-6AE4-54A4-2C31-BDFD0CB6954C</t>
+  </si>
+  <si>
+    <t>D7E22633-D71E-98DB-2784-1CAED83A9A72</t>
   </si>
   <si>
     <t>numberPhone</t>
   </si>
   <si>
-    <t>506CC65D-B1AB-F31A-4BA9-517671DDF7B6</t>
+    <t>9C1E8BC5-965E-F2CD-63EA-B004E7B09001</t>
   </si>
   <si>
     <t>password</t>
   </si>
   <si>
-    <t>B44BE613-54E9-ABE6-BF19-9D383A6E1969</t>
-  </si>
-  <si>
-    <t>potential</t>
-  </si>
-  <si>
-    <t>EFBBC641-A321-85C6-19C5-7484C997CEB6</t>
+    <t>B422B9F3-FDD2-94F4-FE3D-E6F6D1814D1E</t>
+  </si>
+  <si>
+    <t>power</t>
+  </si>
+  <si>
+    <t>23F0EB27-605F-2535-ECD1-69A75E435849</t>
   </si>
   <si>
     <t>secondLastName</t>
   </si>
   <si>
-    <t>AC31F942-C982-B549-3F8B-C9A5669F7285</t>
+    <t>5DB03AC7-BC5D-F159-4CCA-CBAD92818D84</t>
   </si>
   <si>
     <t>serialNumber</t>
   </si>
   <si>
-    <t>6EE0646F-04C9-1688-8164-89699FA34E39</t>
+    <t>AAE777EE-6A71-1B93-B418-5EB714BC788E</t>
+  </si>
+  <si>
+    <t>serviceAdminCost</t>
+  </si>
+  <si>
+    <t>76B9EBD1-4F6E-529B-CBA7-003422B33A73</t>
   </si>
   <si>
     <t>status</t>
   </si>
   <si>
-    <t>8D10554B-85A6-E8F3-AE90-98522BF2709B</t>
+    <t>22BA1EF3-9427-00E2-CCC1-A275A5F620F5</t>
   </si>
   <si>
     <t>streetName</t>
   </si>
   <si>
-    <t>CBBA852B-7229-9871-3604-77B743275958</t>
+    <t>710DDCAA-0EE1-0FF9-BC2A-F3FCC11596A3</t>
   </si>
   <si>
     <t>streetNumber</t>
   </si>
   <si>
-    <t>10917FDA-EAFE-66E7-E4AE-80E895184321</t>
-  </si>
-  <si>
-    <t>variableCost</t>
-  </si>
-  <si>
-    <t>8E151F29-DD71-1863-9271-C5361CB998AD</t>
+    <t>0DFC53E1-50AE-D648-4130-42B1F6DCB4D4</t>
+  </si>
+  <si>
+    <t>transportCost</t>
+  </si>
+  <si>
+    <t>80A3210E-DBD0-B637-11EF-D3150820523F</t>
   </si>
   <si>
     <t>Address_Comuna_FK</t>
   </si>
   <si>
-    <t>F9867493-3C18-BFBE-C3FC-760F3ABA9469</t>
+    <t>5BC2BA8D-5621-5C8B-6033-60FA2A25A79A</t>
   </si>
   <si>
     <t>Address_Country_FK</t>
   </si>
   <si>
-    <t>D8819499-57AC-DAD5-088D-D6163DFC88E3</t>
+    <t>5C5FA035-3EB3-E214-2760-3495D3715ADD</t>
   </si>
   <si>
     <t>Address_Region_FK</t>
   </si>
   <si>
-    <t>AEF47B43-F984-0D17-0267-F3B5CE8756C5</t>
-  </si>
-  <si>
-    <t>Contract_ChargeType_FK</t>
-  </si>
-  <si>
-    <t>F0CDA38B-B9FC-DC3D-6BA2-8159C3CD8503</t>
+    <t>E8F9C766-3CC9-B6A7-C6A2-172C8BA0470C</t>
+  </si>
+  <si>
+    <t>AppUser_Address_FK</t>
+  </si>
+  <si>
+    <t>D76DD9EA-4B1F-05CE-CACD-866627772007</t>
+  </si>
+  <si>
+    <t>AppUser_Contract_FK</t>
+  </si>
+  <si>
+    <t>D5DB20FC-9280-79DF-2F02-082C8BD8F435</t>
   </si>
   <si>
     <t>Contract_ElectricityCompany_FK</t>
   </si>
   <si>
-    <t>8717AB4A-5939-A800-7CEA-EF0E6237C048</t>
+    <t>24163528-F8BC-B7EF-B825-337D06863EC5</t>
   </si>
   <si>
     <t>Result_UserDevice_FK</t>
   </si>
   <si>
-    <t>5672E553-2046-F443-A1CF-5056EFCC6128</t>
-  </si>
-  <si>
-    <t>User_Address_FK</t>
-  </si>
-  <si>
-    <t>E465E2CF-3E8A-BC03-97AD-612D80B1ED1A</t>
-  </si>
-  <si>
-    <t>User_Contract_FK</t>
-  </si>
-  <si>
-    <t>BD842AAB-E5CA-2B05-3971-96A4C81CA41C</t>
+    <t>41C8E158-D607-C5A8-F3E8-C14D33939608</t>
   </si>
   <si>
     <t>UserDevice_AppUser_FK</t>
   </si>
   <si>
-    <t>08041685-0A79-C282-89D5-F8E79385DDB1</t>
+    <t>0930ED40-A874-E892-AE30-63D24583BC07</t>
   </si>
   <si>
     <t>UserDevice_Device_FK</t>
   </si>
   <si>
-    <t>2B5755DD-BFDB-0AB3-056A-013C56E9B981</t>
+    <t>DB70A20B-321C-B6BE-4A98-86423B2E8D0C</t>
   </si>
   <si>
     <t>Address_PK</t>
   </si>
   <si>
-    <t>DB34C21D-3EE5-7339-632A-053443C65A1D</t>
+    <t>8228ADF2-B425-5C58-C3B9-476EB4417120</t>
   </si>
   <si>
     <t>AppUser_PK</t>
   </si>
   <si>
-    <t>A3A2543F-CEE5-46DD-9744-09F43056D2BD</t>
-  </si>
-  <si>
-    <t>ChargeType_PK</t>
-  </si>
-  <si>
-    <t>22C00C2E-977B-6A07-6FDB-8E01B138AD3B</t>
+    <t>8844675F-B563-A685-C873-06BCC0A621DD</t>
   </si>
   <si>
     <t>Comuna_PK</t>
   </si>
   <si>
-    <t>62EBD44D-5232-8674-53C9-D3354174D34D</t>
+    <t>71E51909-BE1A-1793-A4C8-BEABC6C15586</t>
   </si>
   <si>
     <t>Contract_PK</t>
   </si>
   <si>
-    <t>C4CE16E0-1C34-C60B-F850-1418FF1D438C</t>
+    <t>C72427A6-3025-503E-D8A4-93CBF783E7E2</t>
   </si>
   <si>
     <t>Country_PK</t>
   </si>
   <si>
-    <t>09070F35-9366-9BDE-093A-87B391F0CC0D</t>
+    <t>0027DD8A-B5D8-39F1-73A2-938710632EDE</t>
   </si>
   <si>
     <t>Device_PK</t>
   </si>
   <si>
-    <t>2750E838-82E6-5BA0-1CC6-AF1BCDC7990E</t>
+    <t>7D599655-479F-CF06-6785-FDFD5C3E1A6E</t>
   </si>
   <si>
     <t>ElectricityCompany_PK</t>
   </si>
   <si>
-    <t>CA986A16-12BB-6001-C706-D958874031BB</t>
+    <t>6AF01A10-D486-622B-B283-E1B863523EC1</t>
   </si>
   <si>
     <t>Region_PK</t>
   </si>
   <si>
-    <t>E989073F-64A2-968B-2476-F9C9A1414F26</t>
+    <t>608EF77C-AE79-DC88-51CF-D18430AE8B9E</t>
   </si>
   <si>
     <t>Result_PK</t>
   </si>
   <si>
-    <t>DA77D18B-BFD6-B633-60E9-7CDE685E7A68</t>
+    <t>5A1C52F7-A087-EF0C-0B33-F8586D15E9E2</t>
   </si>
   <si>
     <t>UserDevice_PK</t>
   </si>
   <si>
-    <t>65B650A4-1196-466E-D77A-BC26ECFA0C91</t>
+    <t>A3C9FD1F-4935-2711-E81E-D995DA501D90</t>
   </si>
   <si>
     <t>Device_serialNumber_UN</t>
@@ -1552,6 +1486,9 @@
     <t>VARCHAR2 (100)</t>
   </si>
   <si>
+    <t>VARCHAR2 (50)</t>
+  </si>
+  <si>
     <t>Mandatory</t>
   </si>
   <si>
@@ -1618,9 +1555,6 @@
     <t>VARCHAR2 (20)</t>
   </si>
   <si>
-    <t>VARCHAR2 (12)</t>
-  </si>
-  <si>
     <t>NUMBER (9)</t>
   </si>
   <si>
@@ -1630,37 +1564,10 @@
     <t>AppUser.id</t>
   </si>
   <si>
-    <t>NUMBER (2)</t>
-  </si>
-  <si>
-    <t>VARCHAR2 (10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ejemplo:
-BT1
-BT2
-BT1-T3
-AT2
-AT3
-</t>
-  </si>
-  <si>
-    <t>ChargeType.id</t>
-  </si>
-  <si>
     <t>Comuna.id</t>
   </si>
   <si>
-    <t>NUMBER (20,2)</t>
-  </si>
-  <si>
-    <t>Costo Fijo</t>
-  </si>
-  <si>
-    <t>Tipo de tarifa</t>
-  </si>
-  <si>
-    <t>Costo Variable</t>
+    <t>NUMBER (10)</t>
   </si>
   <si>
     <t>Contract.id</t>
@@ -1681,6 +1588,9 @@
     <t>Device.serialNumber</t>
   </si>
   <si>
+    <t>VARCHAR2 (40)</t>
+  </si>
+  <si>
     <t>ElectricityCompany.id</t>
   </si>
   <si>
@@ -1690,10 +1600,10 @@
     <t>Contiene mediciones de dispositivo despues de los 60 minutos</t>
   </si>
   <si>
+    <t>NUMBER (10,3)</t>
+  </si>
+  <si>
     <t>DATE</t>
-  </si>
-  <si>
-    <t>NUMBER (15)</t>
   </si>
   <si>
     <t>Result.id</t>
@@ -1895,7 +1805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:H206"/>
+  <dimension ref="A2:H191"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.61328125" customWidth="true" bestFit="true"/>
@@ -1915,464 +1825,464 @@
     </row>
     <row r="4" ht="18.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" ht="18.0" customHeight="true">
       <c r="A5" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="true">
       <c r="B7" t="s" s="5">
-        <v>328</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" ht="18.0" customHeight="true">
       <c r="B8" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>338</v>
-      </c>
       <c r="H8" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" ht="18.0" customHeight="true">
       <c r="B9" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" ht="18.0" customHeight="true">
       <c r="B10" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" ht="18.0" customHeight="true">
       <c r="B11" s="6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" ht="18.0" customHeight="true">
       <c r="B12" s="6" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" ht="18.0" customHeight="true">
       <c r="B13" s="6" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" ht="18.0" customHeight="true">
       <c r="B14" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" ht="18.0" customHeight="true">
       <c r="B15" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" ht="18.0" customHeight="true">
       <c r="B18" t="s" s="5">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" ht="18.0" customHeight="true">
       <c r="B19" s="3" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20" ht="18.0" customHeight="true">
       <c r="B20" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23" ht="18.0" customHeight="true">
       <c r="B23" t="s" s="5">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" ht="18.0" customHeight="true">
       <c r="B24" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" ht="18.0" customHeight="true">
       <c r="B25" s="6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="26" ht="18.0" customHeight="true">
       <c r="B26" s="6" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" ht="18.0" customHeight="true">
       <c r="B27" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" ht="18.0" customHeight="true">
       <c r="A29" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" ht="18.0" customHeight="true">
       <c r="A30" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="32" ht="18.0" customHeight="true">
       <c r="B32" t="s" s="5">
-        <v>328</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" ht="18.0" customHeight="true">
       <c r="B33" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>338</v>
-      </c>
       <c r="H33" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" ht="18.0" customHeight="true">
       <c r="B34" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35" ht="18.0" customHeight="true">
@@ -2380,22 +2290,22 @@
         <v>62</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" ht="18.0" customHeight="true">
@@ -2403,416 +2313,416 @@
         <v>64</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="37" ht="18.0" customHeight="true">
       <c r="B37" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38" ht="18.0" customHeight="true">
       <c r="B38" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39" ht="18.0" customHeight="true">
       <c r="B39" s="6" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" ht="18.0" customHeight="true">
       <c r="B40" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41" ht="18.0" customHeight="true">
       <c r="B41" s="6" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" ht="18.0" customHeight="true">
       <c r="B42" s="6" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" ht="18.0" customHeight="true">
       <c r="B43" s="6" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" ht="18.0" customHeight="true">
       <c r="B44" s="6" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" ht="18.0" customHeight="true">
       <c r="B47" t="s" s="5">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="48" ht="18.0" customHeight="true">
       <c r="B48" s="3" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" ht="18.0" customHeight="true">
       <c r="B49" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" ht="18.0" customHeight="true">
       <c r="B52" t="s" s="5">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" ht="18.0" customHeight="true">
       <c r="B53" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" ht="18.0" customHeight="true">
       <c r="B54" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="55" ht="18.0" customHeight="true">
       <c r="B55" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="57" ht="18.0" customHeight="true">
       <c r="A57" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" ht="18.0" customHeight="true">
       <c r="A58" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="60" ht="18.0" customHeight="true">
       <c r="B60" t="s" s="5">
-        <v>328</v>
+        <v>318</v>
       </c>
     </row>
     <row r="61" ht="18.0" customHeight="true">
       <c r="B61" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G61" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>338</v>
-      </c>
       <c r="H61" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="62" ht="18.0" customHeight="true">
       <c r="B62" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="63" ht="18.0" customHeight="true">
@@ -2820,824 +2730,821 @@
         <v>3</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>361</v>
+        <v>312</v>
       </c>
     </row>
     <row r="66" ht="18.0" customHeight="true">
       <c r="B66" t="s" s="5">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" ht="18.0" customHeight="true">
       <c r="B67" s="3" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="68" ht="18.0" customHeight="true">
       <c r="B68" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="70" ht="18.0" customHeight="true">
       <c r="A70" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
     </row>
     <row r="71" ht="18.0" customHeight="true">
       <c r="A71" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="73" ht="18.0" customHeight="true">
       <c r="B73" t="s" s="5">
-        <v>328</v>
+        <v>318</v>
       </c>
     </row>
     <row r="74" ht="18.0" customHeight="true">
       <c r="B74" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G74" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>338</v>
-      </c>
       <c r="H74" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="75" ht="18.0" customHeight="true">
       <c r="B75" s="6" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="76" ht="18.0" customHeight="true">
       <c r="B76" s="6" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>354</v>
+        <v>321</v>
       </c>
       <c r="D76" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="77" ht="18.0" customHeight="true">
+      <c r="B77" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="78" ht="18.0" customHeight="true">
+      <c r="B78" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="79" ht="18.0" customHeight="true">
+      <c r="B79" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="82" ht="18.0" customHeight="true">
+      <c r="B82" t="s" s="5">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="83" ht="18.0" customHeight="true">
+      <c r="B83" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F83" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E76" s="8" t="s">
+      <c r="G83" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="84" ht="18.0" customHeight="true">
+      <c r="B84" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="87" ht="18.0" customHeight="true">
+      <c r="B87" t="s" s="5">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="88" ht="18.0" customHeight="true">
+      <c r="B88" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="F76" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="79" ht="18.0" customHeight="true">
-      <c r="B79" t="s" s="5">
+      <c r="D88" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G88" s="3" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="80" ht="18.0" customHeight="true">
-      <c r="B80" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="81" ht="18.0" customHeight="true">
-      <c r="B81" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="G81" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="83" ht="18.0" customHeight="true">
-      <c r="A83" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="84" ht="18.0" customHeight="true">
-      <c r="A84" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="F84" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="86" ht="18.0" customHeight="true">
-      <c r="B86" t="s" s="5">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="87" ht="18.0" customHeight="true">
-      <c r="B87" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="88" ht="18.0" customHeight="true">
-      <c r="B88" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G88" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>365</v>
+      <c r="H88" s="3" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="89" ht="18.0" customHeight="true">
       <c r="B89" s="6" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
       <c r="C89" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="91" ht="18.0" customHeight="true">
+      <c r="A91" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="92" ht="18.0" customHeight="true">
+      <c r="A92" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="94" ht="18.0" customHeight="true">
+      <c r="B94" t="s" s="5">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="95" ht="18.0" customHeight="true">
+      <c r="B95" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="96" ht="18.0" customHeight="true">
+      <c r="B96" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="97" ht="18.0" customHeight="true">
+      <c r="B97" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="100" ht="18.0" customHeight="true">
+      <c r="B100" t="s" s="5">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="101" ht="18.0" customHeight="true">
+      <c r="B101" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="D89" s="8" t="s">
+      <c r="E101" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F101" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E89" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G89" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="90" ht="18.0" customHeight="true">
-      <c r="B90" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="G90" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="91" ht="18.0" customHeight="true">
-      <c r="B91" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="92" ht="18.0" customHeight="true">
-      <c r="B92" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G92" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="93" ht="18.0" customHeight="true">
-      <c r="B93" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="D93" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G93" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="96" ht="18.0" customHeight="true">
-      <c r="B96" t="s" s="5">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="97" ht="18.0" customHeight="true">
-      <c r="B97" s="3" t="s">
+      <c r="G101" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="102" ht="18.0" customHeight="true">
+      <c r="B102" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="104" ht="18.0" customHeight="true">
+      <c r="A104" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="105" ht="18.0" customHeight="true">
+      <c r="A105" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="107" ht="18.0" customHeight="true">
+      <c r="B107" t="s" s="5">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="108" ht="18.0" customHeight="true">
+      <c r="B108" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="109" ht="18.0" customHeight="true">
+      <c r="B109" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C109" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="98" ht="18.0" customHeight="true">
-      <c r="B98" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="101" ht="18.0" customHeight="true">
-      <c r="B101" t="s" s="5">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="102" ht="18.0" customHeight="true">
-      <c r="B102" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C102" s="3" t="s">
+      <c r="D109" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="110" ht="18.0" customHeight="true">
+      <c r="B110" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C110" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="103" ht="18.0" customHeight="true">
-      <c r="B103" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="G103" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="104" ht="18.0" customHeight="true">
-      <c r="B104" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="G104" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="106" ht="18.0" customHeight="true">
-      <c r="A106" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="107" ht="18.0" customHeight="true">
-      <c r="A107" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="109" ht="18.0" customHeight="true">
-      <c r="B109" t="s" s="5">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="110" ht="18.0" customHeight="true">
-      <c r="B110" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>325</v>
+      <c r="D110" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="111" ht="18.0" customHeight="true">
       <c r="B111" s="6" t="s">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="112" ht="18.0" customHeight="true">
       <c r="B112" s="6" t="s">
-        <v>3</v>
+        <v>118</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="115" ht="18.0" customHeight="true">
       <c r="B115" t="s" s="5">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="116" ht="18.0" customHeight="true">
       <c r="B116" s="3" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="117" ht="18.0" customHeight="true">
       <c r="B117" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="119" ht="18.0" customHeight="true">
-      <c r="A119" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C119" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="118" ht="18.0" customHeight="true">
+      <c r="B118" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="120" ht="18.0" customHeight="true">
+      <c r="A120" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="121" ht="18.0" customHeight="true">
+      <c r="A121" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="123" ht="18.0" customHeight="true">
+      <c r="B123" t="s" s="5">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="124" ht="18.0" customHeight="true">
+      <c r="B124" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D124" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="D119" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E119" s="2" t="s">
+      <c r="E124" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="F119" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="120" ht="18.0" customHeight="true">
-      <c r="A120" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="122" ht="18.0" customHeight="true">
-      <c r="B122" t="s" s="5">
+      <c r="F124" s="3" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="123" ht="18.0" customHeight="true">
-      <c r="B123" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C123" s="3" t="s">
+      <c r="G124" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="D123" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="H123" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="124" ht="18.0" customHeight="true">
-      <c r="B124" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C124" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="D124" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E124" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="F124" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G124" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>322</v>
+      <c r="H124" s="3" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="125" ht="18.0" customHeight="true">
       <c r="B125" s="6" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>354</v>
+        <v>321</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="126" ht="18.0" customHeight="true">
@@ -3645,1101 +3552,899 @@
         <v>3</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="D126" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="129" ht="18.0" customHeight="true">
+      <c r="B129" t="s" s="5">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="130" ht="18.0" customHeight="true">
+      <c r="B130" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F130" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E126" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F126" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G126" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="127" ht="18.0" customHeight="true">
-      <c r="B127" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="D127" s="8" t="s">
+      <c r="G130" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="131" ht="18.0" customHeight="true">
+      <c r="B131" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="133" ht="18.0" customHeight="true">
+      <c r="A133" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="134" ht="18.0" customHeight="true">
+      <c r="A134" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="136" ht="18.0" customHeight="true">
+      <c r="B136" t="s" s="5">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="137" ht="18.0" customHeight="true">
+      <c r="B137" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="138" ht="18.0" customHeight="true">
+      <c r="B138" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="139" ht="18.0" customHeight="true">
+      <c r="B139" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H139" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="142" ht="18.0" customHeight="true">
+      <c r="B142" t="s" s="5">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="143" ht="18.0" customHeight="true">
+      <c r="B143" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F143" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E127" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F127" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G127" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H127" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="130" ht="18.0" customHeight="true">
-      <c r="B130" t="s" s="5">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="131" ht="18.0" customHeight="true">
-      <c r="B131" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="E131" s="3" t="s">
+      <c r="G143" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="144" ht="18.0" customHeight="true">
+      <c r="B144" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="G144" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="146" ht="18.0" customHeight="true">
+      <c r="A146" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="147" ht="18.0" customHeight="true">
+      <c r="A147" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="149" ht="18.0" customHeight="true">
+      <c r="B149" t="s" s="5">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="150" ht="18.0" customHeight="true">
+      <c r="B150" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F150" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="F131" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="G131" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="132" ht="18.0" customHeight="true">
-      <c r="B132" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="F132" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="G132" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="133" ht="18.0" customHeight="true">
-      <c r="B133" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="E133" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="F133" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="G133" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="135" ht="18.0" customHeight="true">
-      <c r="A135" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="136" ht="18.0" customHeight="true">
-      <c r="A136" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C136" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="D136" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="E136" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="F136" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="138" ht="18.0" customHeight="true">
-      <c r="B138" t="s" s="5">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="139" ht="18.0" customHeight="true">
-      <c r="B139" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C139" s="3" t="s">
+      <c r="G150" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="D139" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E139" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F139" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G139" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="H139" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="140" ht="18.0" customHeight="true">
-      <c r="B140" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="D140" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E140" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="F140" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G140" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="141" ht="18.0" customHeight="true">
-      <c r="B141" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="D141" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E141" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F141" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G141" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H141" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="144" ht="18.0" customHeight="true">
-      <c r="B144" t="s" s="5">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="145" ht="18.0" customHeight="true">
-      <c r="B145" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F145" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="G145" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="146" ht="18.0" customHeight="true">
-      <c r="B146" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D146" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="E146" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="F146" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="G146" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="148" ht="18.0" customHeight="true">
-      <c r="A148" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="149" ht="18.0" customHeight="true">
-      <c r="A149" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="D149" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="E149" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>322</v>
+      <c r="H150" s="3" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="151" ht="18.0" customHeight="true">
-      <c r="B151" t="s" s="5">
-        <v>328</v>
+      <c r="B151" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H151" s="6" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="152" ht="18.0" customHeight="true">
-      <c r="B152" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D152" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F152" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G152" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="H152" s="3" t="s">
-        <v>325</v>
+      <c r="B152" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H152" s="6" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="153" ht="18.0" customHeight="true">
       <c r="B153" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H153" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="154" ht="18.0" customHeight="true">
       <c r="B154" s="6" t="s">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>354</v>
+        <v>321</v>
       </c>
       <c r="D154" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H154" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="155" ht="18.0" customHeight="true">
+      <c r="B155" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="D155" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H155" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="156" ht="18.0" customHeight="true">
+      <c r="B156" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="159" ht="18.0" customHeight="true">
+      <c r="B159" t="s" s="5">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="160" ht="18.0" customHeight="true">
+      <c r="B160" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F160" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E154" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F154" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G154" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="157" ht="18.0" customHeight="true">
-      <c r="B157" t="s" s="5">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="158" ht="18.0" customHeight="true">
-      <c r="B158" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="E158" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F158" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="159" ht="18.0" customHeight="true">
-      <c r="B159" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="E159" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="F159" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="G159" s="6" t="s">
-        <v>322</v>
+      <c r="G160" s="3" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="161" ht="18.0" customHeight="true">
-      <c r="A161" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="F161" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="162" ht="18.0" customHeight="true">
-      <c r="A162" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B162" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C162" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="D162" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="E162" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="F162" s="6" t="s">
-        <v>322</v>
+      <c r="B161" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="G161" s="6" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="164" ht="18.0" customHeight="true">
       <c r="B164" t="s" s="5">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="165" ht="18.0" customHeight="true">
       <c r="B165" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="166" ht="18.0" customHeight="true">
       <c r="B166" s="6" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="D166" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E166" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F166" s="8" t="s">
-        <v>336</v>
+        <v>45</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F166" s="7" t="s">
+        <v>325</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="167" ht="18.0" customHeight="true">
-      <c r="B167" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="168" ht="18.0" customHeight="true">
+      <c r="A168" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="169" ht="18.0" customHeight="true">
+      <c r="A169" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="F169" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="171" ht="18.0" customHeight="true">
+      <c r="B171" t="s" s="5">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="172" ht="18.0" customHeight="true">
+      <c r="B172" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="173" ht="18.0" customHeight="true">
+      <c r="B173" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="E173" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H173" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="174" ht="18.0" customHeight="true">
+      <c r="B174" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H174" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="175" ht="18.0" customHeight="true">
+      <c r="B175" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C167" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="D167" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E167" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F167" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G167" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H167" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="168" ht="18.0" customHeight="true">
-      <c r="B168" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C168" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="D168" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E168" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="F168" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G168" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H168" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="169" ht="18.0" customHeight="true">
-      <c r="B169" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C169" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="D169" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E169" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F169" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="G169" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H169" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="170" ht="18.0" customHeight="true">
-      <c r="B170" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C170" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="D170" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E170" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F170" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G170" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H170" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="171" ht="18.0" customHeight="true">
-      <c r="B171" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C171" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="D171" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E171" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F171" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G171" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H171" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="174" ht="18.0" customHeight="true">
-      <c r="B174" t="s" s="5">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="175" ht="18.0" customHeight="true">
-      <c r="B175" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D175" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="E175" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F175" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="G175" s="3" t="s">
-        <v>325</v>
+      <c r="C175" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="E175" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H175" s="6" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="176" ht="18.0" customHeight="true">
       <c r="B176" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C176" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D176" s="6" t="s">
-        <v>341</v>
+        <v>66</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>325</v>
       </c>
       <c r="E176" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="F176" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="G176" s="6" t="s">
-        <v>322</v>
+        <v>325</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H176" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="177" ht="18.0" customHeight="true">
+      <c r="B177" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E177" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H177" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="178" ht="18.0" customHeight="true">
+      <c r="B178" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H178" s="6" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="179" ht="18.0" customHeight="true">
-      <c r="B179" t="s" s="5">
-        <v>344</v>
+      <c r="B179" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H179" s="6" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="180" ht="18.0" customHeight="true">
-      <c r="B180" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C180" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="D180" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="E180" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F180" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G180" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H180" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="181" ht="18.0" customHeight="true">
-      <c r="B181" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C181" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D181" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E181" s="7" t="s">
+      <c r="B180" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E180" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H180" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="183" ht="18.0" customHeight="true">
+      <c r="B183" t="s" s="5">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="184" ht="18.0" customHeight="true">
+      <c r="B184" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F184" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="F181" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="G181" s="8" t="s">
+      <c r="G184" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="185" ht="18.0" customHeight="true">
+      <c r="B185" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="G185" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="188" ht="18.0" customHeight="true">
+      <c r="B188" t="s" s="5">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="189" ht="18.0" customHeight="true">
+      <c r="B189" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C189" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="H181" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="183" ht="18.0" customHeight="true">
-      <c r="A183" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C183" s="2" t="s">
+      <c r="D189" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E189" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="D183" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="F183" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="184" ht="18.0" customHeight="true">
-      <c r="A184" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B184" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C184" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="D184" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="E184" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="F184" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="186" ht="18.0" customHeight="true">
-      <c r="B186" t="s" s="5">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="187" ht="18.0" customHeight="true">
-      <c r="B187" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C187" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E187" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F187" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G187" s="3" t="s">
+      <c r="F189" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="H187" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="188" ht="18.0" customHeight="true">
-      <c r="B188" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C188" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="D188" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E188" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F188" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G188" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="189" ht="18.0" customHeight="true">
-      <c r="B189" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C189" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="D189" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E189" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F189" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G189" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H189" s="6" t="s">
-        <v>322</v>
+      <c r="G189" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H189" s="3" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="190" ht="18.0" customHeight="true">
       <c r="B190" s="6" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="D190" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="E190" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F190" s="8" t="s">
-        <v>336</v>
+        <v>29</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F190" s="7" t="s">
+        <v>325</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="191" ht="18.0" customHeight="true">
       <c r="B191" s="6" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="D191" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E191" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="F191" s="8" t="s">
-        <v>336</v>
+        <v>37</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E191" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F191" s="7" t="s">
+        <v>325</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="192" ht="18.0" customHeight="true">
-      <c r="B192" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C192" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="D192" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E192" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F192" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="G192" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H192" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="193" ht="18.0" customHeight="true">
-      <c r="B193" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C193" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="D193" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E193" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F193" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="G193" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H193" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="194" ht="18.0" customHeight="true">
-      <c r="B194" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C194" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="D194" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E194" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F194" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G194" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H194" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="195" ht="18.0" customHeight="true">
-      <c r="B195" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C195" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="D195" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E195" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F195" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G195" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="H195" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="198" ht="18.0" customHeight="true">
-      <c r="B198" t="s" s="5">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="199" ht="18.0" customHeight="true">
-      <c r="B199" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C199" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D199" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="E199" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F199" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="G199" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="200" ht="18.0" customHeight="true">
-      <c r="B200" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C200" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D200" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="E200" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="F200" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="G200" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="203" ht="18.0" customHeight="true">
-      <c r="B203" t="s" s="5">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="204" ht="18.0" customHeight="true">
-      <c r="B204" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C204" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="D204" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="E204" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F204" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G204" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H204" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="205" ht="18.0" customHeight="true">
-      <c r="B205" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C205" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D205" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E205" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="F205" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="G205" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="H205" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="206" ht="18.0" customHeight="true">
-      <c r="B206" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C206" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D206" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="E206" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="F206" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="G206" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="H206" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -4747,7 +4452,7 @@
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <dataValidations count="53">
+  <dataValidations count="48">
     <dataValidation type="list" sqref="A5" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
@@ -4814,97 +4519,82 @@
     <dataValidation type="list" sqref="A71" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B81" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B84" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A84" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D89" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>lov_4!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E89" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="F89" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="A92" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B98" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B102" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D103" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>lov_4!B1:B65000</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="D104" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>lov_4!B1:B65000</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="E103" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="E104" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="F103" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="F104" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="A107" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A105" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="B117" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A120" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B118" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B132" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A121" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B133" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B131" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A136" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A134" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B146" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B144" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A149" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A147" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B159" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B161" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A162" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D166" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>lov_4!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E166" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="F166" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="A169" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B176" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B185" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D181" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D190" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E181" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D191" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>lov_4!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E190" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F181" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E191" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A184" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>null!B1:B65000</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="B200" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>null!B1:B65000</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="D205" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>lov_4!B1:B65000</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="D206" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>lov_4!B1:B65000</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="E205" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F190" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E206" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="F205" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="F206" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F191" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4921,18 +4611,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -5080,7 +4770,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5161,14 +4851,6 @@
       </c>
       <c r="B10" s="8" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -5179,308 +4861,308 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>83</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>85</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>95</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>97</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>103</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>108</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>110</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>3</v>
@@ -5488,7 +5170,7 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>3</v>
@@ -5496,34 +5178,34 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>3</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>3</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>3</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>116</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -5572,30 +5254,6 @@
       </c>
       <c r="B49" s="8" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -5606,87 +5264,79 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -5697,95 +5347,87 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -5801,10 +5443,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -5820,546 +5462,546 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -6375,10 +6017,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>

--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
@@ -74,40 +74,40 @@
     </comment>
     <comment ref="B14" authorId="0">
       <text>
-        <t>ObjectID:22BA1EF3-9427-00E2-CCC1-A275A5F620F5;
+        <t>ObjectID:F47928F9-0511-BEAD-2209-EB8AFA51DA23;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B15" authorId="0">
-      <text>
-        <t>ObjectID:710DDCAA-0EE1-0FF9-BC2A-F3FCC11596A3;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B20" authorId="0">
+    <comment ref="B19" authorId="0">
       <text>
         <t>ObjectID:DB70A20B-321C-B6BE-4A98-86423B2E8D0C;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B25" authorId="0">
+    <comment ref="B24" authorId="0">
       <text>
         <t>ObjectID:80A3210E-DBD0-B637-11EF-D3150820523F;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="B26" authorId="0">
+    <comment ref="B25" authorId="0">
       <text>
         <t>ObjectID:5BC2BA8D-5621-5C8B-6033-60FA2A25A79A;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="B27" authorId="0">
+    <comment ref="B26" authorId="0">
       <text>
         <t>ObjectID:5C5FA035-3EB3-E214-2760-3495D3715ADD;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
+    <comment ref="B27" authorId="0">
+      <text>
+        <t>ObjectID:71E2CB75-16C9-4494-82BA-29A58998596E;
+Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
+      </text>
+    </comment>
     <comment ref="A30" authorId="0">
       <text>
         <t>ObjectID:110FB069-4B9F-3EC1-6FC7-D416346777ED;
@@ -440,71 +440,95 @@
     </comment>
     <comment ref="A169" authorId="0">
       <text>
+        <t>ObjectID:5C40F357-EE5C-80FD-0291-9F79E8683608;
+Class:oracle.dbtools.crest.model.design.relational.Table</t>
+      </text>
+    </comment>
+    <comment ref="B173" authorId="0">
+      <text>
+        <t>ObjectID:5B609735-98B7-35FD-C65C-EF956ECDE343;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B174" authorId="0">
+      <text>
+        <t>ObjectID:40EA085C-4114-BA7A-DCA7-FD3FE37559C9;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B179" authorId="0">
+      <text>
+        <t>ObjectID:01D07402-27E5-7860-AC0C-A34FA8D423FE;
+Class:oracle.dbtools.crest.model.design.relational.Index</t>
+      </text>
+    </comment>
+    <comment ref="A182" authorId="0">
+      <text>
         <t>ObjectID:86B573D7-CD13-EBD4-0C4F-B4DEE60F904A;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B173" authorId="0">
+    <comment ref="B186" authorId="0">
       <text>
         <t>ObjectID:9FF49873-5D91-649D-4627-2BE70D843F9F;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B174" authorId="0">
+    <comment ref="B187" authorId="0">
       <text>
         <t>ObjectID:A9E9D69C-9E14-EE96-C054-F15AB9C32B15;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B175" authorId="0">
+    <comment ref="B188" authorId="0">
       <text>
         <t>ObjectID:F3A998D8-1D5F-1C74-2B9B-FC8746DCE908;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B176" authorId="0">
+    <comment ref="B189" authorId="0">
       <text>
         <t>ObjectID:A8FA0751-F8E1-215B-1F12-B03EDE8C5C28;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B177" authorId="0">
+    <comment ref="B190" authorId="0">
       <text>
         <t>ObjectID:F1AE3A41-44AC-5762-B6B2-1A6B6C11A835;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B178" authorId="0">
+    <comment ref="B191" authorId="0">
       <text>
         <t>ObjectID:91D44BE7-0B08-6EA0-1784-F0EB2FC0AC7E;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B179" authorId="0">
+    <comment ref="B192" authorId="0">
       <text>
         <t>ObjectID:A0BFE2DC-173F-63A1-2AFD-A301BBCE67A9;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B180" authorId="0">
+    <comment ref="B193" authorId="0">
       <text>
         <t>ObjectID:76B9EBD1-4F6E-529B-CBA7-003422B33A73;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B185" authorId="0">
+    <comment ref="B198" authorId="0">
       <text>
         <t>ObjectID:5A1C52F7-A087-EF0C-0B33-F8586D15E9E2;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B190" authorId="0">
+    <comment ref="B203" authorId="0">
       <text>
         <t>ObjectID:41C8E158-D607-C5A8-F3E8-C14D33939608;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="B191" authorId="0">
+    <comment ref="B204" authorId="0">
       <text>
         <t>ObjectID:0930ED40-A874-E892-AE30-63D24583BC07;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
@@ -515,7 +539,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="372">
   <si>
     <t>Diccionario de datos BD</t>
   </si>
@@ -649,6 +673,12 @@
     <t>Result</t>
   </si>
   <si>
+    <t>5C40F357-EE5C-80FD-0291-9F79E8683608</t>
+  </si>
+  <si>
+    <t>Street</t>
+  </si>
+  <si>
     <t>86B573D7-CD13-EBD4-0C4F-B4DEE60F904A</t>
   </si>
   <si>
@@ -685,19 +715,19 @@
     <t>date</t>
   </si>
   <si>
+    <t>F3A998D8-1D5F-1C74-2B9B-FC8746DCE908</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
     <t>5B69656A-7F33-E185-FCF1-C244B2662860</t>
   </si>
   <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>F3A998D8-1D5F-1C74-2B9B-FC8746DCE908</t>
-  </si>
-  <si>
     <t>2C2D6C32-CDDE-1181-4D22-DCE1793FF5BA</t>
   </si>
   <si>
-    <t>elecricityCost</t>
+    <t>electricityCost</t>
   </si>
   <si>
     <t>2D35241E-CEBA-AC61-6912-2CF3AE6F1925</t>
@@ -712,37 +742,46 @@
     <t>firstName</t>
   </si>
   <si>
+    <t>1333B9D9-9696-1371-F865-7DD808AD089E</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>79A0B868-1A2B-BF19-99BB-53A91A11DB76</t>
+  </si>
+  <si>
+    <t>6BD52512-9D6F-03CA-997E-CAFD3EF02709</t>
+  </si>
+  <si>
+    <t>89097C79-170F-5F0F-FDC1-39D64F8465C4</t>
+  </si>
+  <si>
+    <t>A8FA0751-F8E1-215B-1F12-B03EDE8C5C28</t>
+  </si>
+  <si>
+    <t>CF026949-0856-661A-DDC8-187616158D0D</t>
+  </si>
+  <si>
+    <t>6B623415-7C87-A9FD-D3D3-F416E1B56ABF</t>
+  </si>
+  <si>
+    <t>2DD45A47-0C43-A14B-3473-B90AF68F03F6</t>
+  </si>
+  <si>
+    <t>A9DDAE05-9CA5-8E72-33BF-E0F8637B572C</t>
+  </si>
+  <si>
     <t>C8ED7A2E-0E35-1723-F199-7CD4839E3396</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>1333B9D9-9696-1371-F865-7DD808AD089E</t>
-  </si>
-  <si>
-    <t>6B623415-7C87-A9FD-D3D3-F416E1B56ABF</t>
-  </si>
-  <si>
-    <t>A9DDAE05-9CA5-8E72-33BF-E0F8637B572C</t>
-  </si>
-  <si>
-    <t>89097C79-170F-5F0F-FDC1-39D64F8465C4</t>
-  </si>
-  <si>
-    <t>2DD45A47-0C43-A14B-3473-B90AF68F03F6</t>
-  </si>
-  <si>
-    <t>6BD52512-9D6F-03CA-997E-CAFD3EF02709</t>
-  </si>
-  <si>
-    <t>79A0B868-1A2B-BF19-99BB-53A91A11DB76</t>
-  </si>
-  <si>
-    <t>A8FA0751-F8E1-215B-1F12-B03EDE8C5C28</t>
-  </si>
-  <si>
-    <t>CF026949-0856-661A-DDC8-187616158D0D</t>
+    <t>5B609735-98B7-35FD-C65C-EF956ECDE343</t>
+  </si>
+  <si>
+    <t>F47928F9-0511-BEAD-2209-EB8AFA51DA23</t>
+  </si>
+  <si>
+    <t>id_Street</t>
   </si>
   <si>
     <t>4D1FB96F-EE96-0EC4-8ABD-51B98E0E3C3A</t>
@@ -832,16 +871,19 @@
     <t>D1B1DF2C-03FA-FEE0-ABED-072E3494B947</t>
   </si>
   <si>
+    <t>7438F3A9-ADB4-8934-9CCC-4CB01ECAA8A9</t>
+  </si>
+  <si>
+    <t>79F7CAE0-6AE4-54A4-2C31-BDFD0CB6954C</t>
+  </si>
+  <si>
+    <t>FF19DD8A-D764-66AF-5F8D-5E16C4913319</t>
+  </si>
+  <si>
     <t>8AE41AEF-A676-BB67-ED5D-C9F22BEFB21A</t>
   </si>
   <si>
-    <t>7438F3A9-ADB4-8934-9CCC-4CB01ECAA8A9</t>
-  </si>
-  <si>
-    <t>FF19DD8A-D764-66AF-5F8D-5E16C4913319</t>
-  </si>
-  <si>
-    <t>79F7CAE0-6AE4-54A4-2C31-BDFD0CB6954C</t>
+    <t>40EA085C-4114-BA7A-DCA7-FD3FE37559C9</t>
   </si>
   <si>
     <t>D7E22633-D71E-98DB-2784-1CAED83A9A72</t>
@@ -886,18 +928,6 @@
     <t>status</t>
   </si>
   <si>
-    <t>22BA1EF3-9427-00E2-CCC1-A275A5F620F5</t>
-  </si>
-  <si>
-    <t>streetName</t>
-  </si>
-  <si>
-    <t>710DDCAA-0EE1-0FF9-BC2A-F3FCC11596A3</t>
-  </si>
-  <si>
-    <t>streetNumber</t>
-  </si>
-  <si>
     <t>0DFC53E1-50AE-D648-4130-42B1F6DCB4D4</t>
   </si>
   <si>
@@ -922,6 +952,12 @@
     <t>Address_Region_FK</t>
   </si>
   <si>
+    <t>71E2CB75-16C9-4494-82BA-29A58998596E</t>
+  </si>
+  <si>
+    <t>Address_Street_FK</t>
+  </si>
+  <si>
     <t>E8F9C766-3CC9-B6A7-C6A2-172C8BA0470C</t>
   </si>
   <si>
@@ -1012,6 +1048,12 @@
     <t>Result_PK</t>
   </si>
   <si>
+    <t>01D07402-27E5-7860-AC0C-A34FA8D423FE</t>
+  </si>
+  <si>
+    <t>Street_PK</t>
+  </si>
+  <si>
     <t>5A1C52F7-A087-EF0C-0B33-F8586D15E9E2</t>
   </si>
   <si>
@@ -1483,12 +1525,6 @@
     <t>NUMBER (20)</t>
   </si>
   <si>
-    <t>VARCHAR2 (100)</t>
-  </si>
-  <si>
-    <t>VARCHAR2 (50)</t>
-  </si>
-  <si>
     <t>Mandatory</t>
   </si>
   <si>
@@ -1607,6 +1643,9 @@
   </si>
   <si>
     <t>Result.id</t>
+  </si>
+  <si>
+    <t>Street.id</t>
   </si>
   <si>
     <t>VARCHAR2 (30)</t>
@@ -1805,7 +1844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:H191"/>
+  <dimension ref="A2:H204"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.61328125" customWidth="true" bestFit="true"/>
@@ -1825,904 +1864,904 @@
     </row>
     <row r="4" ht="18.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" ht="18.0" customHeight="true">
       <c r="A5" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="true">
       <c r="B7" t="s" s="5">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" ht="18.0" customHeight="true">
       <c r="B8" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" ht="18.0" customHeight="true">
       <c r="B9" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" ht="18.0" customHeight="true">
       <c r="B10" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" ht="18.0" customHeight="true">
       <c r="B11" s="6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12" ht="18.0" customHeight="true">
       <c r="B12" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" ht="18.0" customHeight="true">
       <c r="B13" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" ht="18.0" customHeight="true">
       <c r="B14" s="6" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="15" ht="18.0" customHeight="true">
-      <c r="B15" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="17" ht="18.0" customHeight="true">
+      <c r="B17" t="s" s="5">
+        <v>334</v>
       </c>
     </row>
     <row r="18" ht="18.0" customHeight="true">
-      <c r="B18" t="s" s="5">
-        <v>330</v>
+      <c r="B18" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="19" ht="18.0" customHeight="true">
-      <c r="B19" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="20" ht="18.0" customHeight="true">
-      <c r="B20" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>312</v>
+      <c r="B19" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="22" ht="18.0" customHeight="true">
+      <c r="B22" t="s" s="5">
+        <v>339</v>
       </c>
     </row>
     <row r="23" ht="18.0" customHeight="true">
-      <c r="B23" t="s" s="5">
-        <v>335</v>
+      <c r="B23" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="24" ht="18.0" customHeight="true">
-      <c r="B24" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>315</v>
+      <c r="B24" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="25" ht="18.0" customHeight="true">
       <c r="B25" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26" ht="18.0" customHeight="true">
       <c r="B26" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="27" ht="18.0" customHeight="true">
       <c r="B27" s="6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29" ht="18.0" customHeight="true">
       <c r="A29" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" ht="18.0" customHeight="true">
       <c r="A30" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32" ht="18.0" customHeight="true">
       <c r="B32" t="s" s="5">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" ht="18.0" customHeight="true">
       <c r="B33" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34" ht="18.0" customHeight="true">
       <c r="B34" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="35" ht="18.0" customHeight="true">
       <c r="B35" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="36" ht="18.0" customHeight="true">
       <c r="B36" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" ht="18.0" customHeight="true">
       <c r="B37" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="38" ht="18.0" customHeight="true">
       <c r="B38" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="39" ht="18.0" customHeight="true">
       <c r="B39" s="6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="40" ht="18.0" customHeight="true">
       <c r="B40" s="6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="41" ht="18.0" customHeight="true">
       <c r="B41" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42" ht="18.0" customHeight="true">
       <c r="B42" s="6" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="43" ht="18.0" customHeight="true">
       <c r="B43" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="44" ht="18.0" customHeight="true">
       <c r="B44" s="6" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="47" ht="18.0" customHeight="true">
       <c r="B47" t="s" s="5">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48" ht="18.0" customHeight="true">
       <c r="B48" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="49" ht="18.0" customHeight="true">
       <c r="B49" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" ht="18.0" customHeight="true">
       <c r="B52" t="s" s="5">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="53" ht="18.0" customHeight="true">
       <c r="B53" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="54" ht="18.0" customHeight="true">
       <c r="B54" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" ht="18.0" customHeight="true">
       <c r="B55" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" ht="18.0" customHeight="true">
       <c r="A57" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" ht="18.0" customHeight="true">
       <c r="A58" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" ht="18.0" customHeight="true">
       <c r="B60" t="s" s="5">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" ht="18.0" customHeight="true">
       <c r="B61" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" ht="18.0" customHeight="true">
       <c r="B62" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="63" ht="18.0" customHeight="true">
@@ -2730,437 +2769,437 @@
         <v>3</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="66" ht="18.0" customHeight="true">
       <c r="B66" t="s" s="5">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="67" ht="18.0" customHeight="true">
       <c r="B67" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" ht="18.0" customHeight="true">
       <c r="B68" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="70" ht="18.0" customHeight="true">
       <c r="A70" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="71" ht="18.0" customHeight="true">
       <c r="A71" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="73" ht="18.0" customHeight="true">
       <c r="B73" t="s" s="5">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="74" ht="18.0" customHeight="true">
       <c r="B74" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="75" ht="18.0" customHeight="true">
       <c r="B75" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="76" ht="18.0" customHeight="true">
       <c r="B76" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="77" ht="18.0" customHeight="true">
       <c r="B77" s="6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="78" ht="18.0" customHeight="true">
       <c r="B78" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="79" ht="18.0" customHeight="true">
       <c r="B79" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="82" ht="18.0" customHeight="true">
       <c r="B82" t="s" s="5">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="83" ht="18.0" customHeight="true">
       <c r="B83" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="84" ht="18.0" customHeight="true">
       <c r="B84" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="87" ht="18.0" customHeight="true">
       <c r="B87" t="s" s="5">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="88" ht="18.0" customHeight="true">
       <c r="B88" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="89" ht="18.0" customHeight="true">
       <c r="B89" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="91" ht="18.0" customHeight="true">
       <c r="A91" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="92" ht="18.0" customHeight="true">
       <c r="A92" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="94" ht="18.0" customHeight="true">
       <c r="B94" t="s" s="5">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="95" ht="18.0" customHeight="true">
       <c r="B95" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="96" ht="18.0" customHeight="true">
       <c r="B96" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="97" ht="18.0" customHeight="true">
@@ -3168,181 +3207,181 @@
         <v>3</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="100" ht="18.0" customHeight="true">
       <c r="B100" t="s" s="5">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="101" ht="18.0" customHeight="true">
       <c r="B101" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="102" ht="18.0" customHeight="true">
       <c r="B102" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="104" ht="18.0" customHeight="true">
       <c r="A104" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="105" ht="18.0" customHeight="true">
       <c r="A105" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="107" ht="18.0" customHeight="true">
       <c r="B107" t="s" s="5">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="108" ht="18.0" customHeight="true">
       <c r="B108" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="109" ht="18.0" customHeight="true">
       <c r="B109" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="110" ht="18.0" customHeight="true">
       <c r="B110" s="6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="111" ht="18.0" customHeight="true">
@@ -3350,201 +3389,201 @@
         <v>3</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="112" ht="18.0" customHeight="true">
       <c r="B112" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="115" ht="18.0" customHeight="true">
       <c r="B115" t="s" s="5">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="116" ht="18.0" customHeight="true">
       <c r="B116" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="117" ht="18.0" customHeight="true">
       <c r="B117" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="118" ht="18.0" customHeight="true">
       <c r="B118" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="120" ht="18.0" customHeight="true">
       <c r="A120" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="121" ht="18.0" customHeight="true">
       <c r="A121" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="123" ht="18.0" customHeight="true">
       <c r="B123" t="s" s="5">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="124" ht="18.0" customHeight="true">
       <c r="B124" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="125" ht="18.0" customHeight="true">
       <c r="B125" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="126" ht="18.0" customHeight="true">
@@ -3552,158 +3591,158 @@
         <v>3</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="129" ht="18.0" customHeight="true">
       <c r="B129" t="s" s="5">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="130" ht="18.0" customHeight="true">
       <c r="B130" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="131" ht="18.0" customHeight="true">
       <c r="B131" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="133" ht="18.0" customHeight="true">
       <c r="A133" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="134" ht="18.0" customHeight="true">
       <c r="A134" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="136" ht="18.0" customHeight="true">
       <c r="B136" t="s" s="5">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="137" ht="18.0" customHeight="true">
       <c r="B137" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="138" ht="18.0" customHeight="true">
       <c r="B138" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="139" ht="18.0" customHeight="true">
@@ -3711,740 +3750,899 @@
         <v>3</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="142" ht="18.0" customHeight="true">
       <c r="B142" t="s" s="5">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="143" ht="18.0" customHeight="true">
       <c r="B143" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="144" ht="18.0" customHeight="true">
       <c r="B144" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="146" ht="18.0" customHeight="true">
       <c r="A146" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="147" ht="18.0" customHeight="true">
       <c r="A147" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="149" ht="18.0" customHeight="true">
       <c r="B149" t="s" s="5">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="150" ht="18.0" customHeight="true">
       <c r="B150" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="151" ht="18.0" customHeight="true">
       <c r="B151" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H151" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="152" ht="18.0" customHeight="true">
       <c r="B152" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="153" ht="18.0" customHeight="true">
       <c r="B153" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H153" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="154" ht="18.0" customHeight="true">
       <c r="B154" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="155" ht="18.0" customHeight="true">
       <c r="B155" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="156" ht="18.0" customHeight="true">
       <c r="B156" s="6" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="159" ht="18.0" customHeight="true">
       <c r="B159" t="s" s="5">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="160" ht="18.0" customHeight="true">
       <c r="B160" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="161" ht="18.0" customHeight="true">
       <c r="B161" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G161" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="164" ht="18.0" customHeight="true">
       <c r="B164" t="s" s="5">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="165" ht="18.0" customHeight="true">
       <c r="B165" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="166" ht="18.0" customHeight="true">
       <c r="B166" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="168" ht="18.0" customHeight="true">
       <c r="A168" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="169" ht="18.0" customHeight="true">
       <c r="A169" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>45</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="171" ht="18.0" customHeight="true">
       <c r="B171" t="s" s="5">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="172" ht="18.0" customHeight="true">
       <c r="B172" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="173" ht="18.0" customHeight="true">
       <c r="B173" s="6" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F173" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="174" ht="18.0" customHeight="true">
       <c r="B174" s="6" t="s">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="175" ht="18.0" customHeight="true">
-      <c r="B175" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C175" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="D175" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="E175" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F175" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="G175" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="H175" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="176" ht="18.0" customHeight="true">
-      <c r="B176" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C176" s="8" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="177" ht="18.0" customHeight="true">
+      <c r="B177" t="s" s="5">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="178" ht="18.0" customHeight="true">
+      <c r="B178" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G178" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="D176" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="E176" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F176" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="G176" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="H176" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="177" ht="18.0" customHeight="true">
-      <c r="B177" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C177" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D177" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="E177" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F177" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G177" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="H177" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="178" ht="18.0" customHeight="true">
-      <c r="B178" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C178" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D178" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="E178" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F178" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G178" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="H178" s="6" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="179" ht="18.0" customHeight="true">
       <c r="B179" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C179" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="D179" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="F179" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="G179" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="181" ht="18.0" customHeight="true">
+      <c r="A181" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="182" ht="18.0" customHeight="true">
+      <c r="A182" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="184" ht="18.0" customHeight="true">
+      <c r="B184" t="s" s="5">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="185" ht="18.0" customHeight="true">
+      <c r="B185" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C185" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="E179" s="8" t="s">
+      <c r="D185" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="H185" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="186" ht="18.0" customHeight="true">
+      <c r="B186" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="D186" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="G186" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="H186" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="187" ht="18.0" customHeight="true">
+      <c r="B187" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="D187" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="H187" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="188" ht="18.0" customHeight="true">
+      <c r="B188" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="E188" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="G188" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="H188" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="189" ht="18.0" customHeight="true">
+      <c r="B189" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C189" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="F179" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="G179" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="H179" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="180" ht="18.0" customHeight="true">
-      <c r="B180" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C180" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="D180" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="E180" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F180" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="G180" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="H180" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="183" ht="18.0" customHeight="true">
-      <c r="B183" t="s" s="5">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="184" ht="18.0" customHeight="true">
-      <c r="B184" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C184" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="E184" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G184" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="185" ht="18.0" customHeight="true">
-      <c r="B185" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="C185" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D185" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="E185" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="F185" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="G185" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="188" ht="18.0" customHeight="true">
-      <c r="B188" t="s" s="5">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="189" ht="18.0" customHeight="true">
-      <c r="B189" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C189" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="E189" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F189" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G189" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="H189" s="3" t="s">
-        <v>315</v>
+      <c r="D189" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="G189" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="H189" s="6" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="190" ht="18.0" customHeight="true">
       <c r="B190" s="6" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D190" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E190" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="F190" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>329</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="191" ht="18.0" customHeight="true">
       <c r="B191" s="6" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="C191" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="D191" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="H191" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="192" ht="18.0" customHeight="true">
+      <c r="B192" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="D192" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="H192" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="193" ht="18.0" customHeight="true">
+      <c r="B193" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D193" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="H193" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="196" ht="18.0" customHeight="true">
+      <c r="B196" t="s" s="5">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="197" ht="18.0" customHeight="true">
+      <c r="B197" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="198" ht="18.0" customHeight="true">
+      <c r="B198" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F198" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="G198" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="201" ht="18.0" customHeight="true">
+      <c r="B201" t="s" s="5">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="202" ht="18.0" customHeight="true">
+      <c r="B202" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="H202" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="203" ht="18.0" customHeight="true">
+      <c r="B203" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C203" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E203" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="F203" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="G203" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="H203" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="204" ht="18.0" customHeight="true">
+      <c r="B204" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C204" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D191" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E191" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="F191" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="G191" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="H191" s="6" t="s">
-        <v>312</v>
+      <c r="D204" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E204" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="F204" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="G204" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="H204" s="6" t="s">
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -4452,12 +4650,15 @@
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <dataValidations count="48">
+  <dataValidations count="53">
     <dataValidation type="list" sqref="A5" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B20" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B19" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="D24" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="D25" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
@@ -4468,6 +4669,9 @@
     <dataValidation type="list" sqref="D27" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
+    <dataValidation type="list" sqref="E24" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
     <dataValidation type="list" sqref="E25" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
@@ -4475,6 +4679,9 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E27" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="F24" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F25" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
@@ -4576,25 +4783,31 @@
     <dataValidation type="list" sqref="A169" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B185" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B179" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D190" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A182" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>null!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="B198" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>null!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="D203" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D191" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D204" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E190" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E203" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E191" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E204" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F190" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F203" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F191" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F204" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4611,18 +4824,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -4770,7 +4983,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4851,6 +5064,14 @@
       </c>
       <c r="B10" s="8" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -4861,300 +5082,300 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>3</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>3</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>3</v>
@@ -5162,7 +5383,7 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>3</v>
@@ -5170,7 +5391,7 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>3</v>
@@ -5178,26 +5399,26 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>110</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>114</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -5254,6 +5475,14 @@
       </c>
       <c r="B49" s="8" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -5264,79 +5493,87 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -5347,87 +5584,95 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>166</v>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -5443,10 +5688,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -5462,546 +5707,546 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -6017,10 +6262,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
@@ -74,40 +74,40 @@
     </comment>
     <comment ref="B14" authorId="0">
       <text>
-        <t>ObjectID:F47928F9-0511-BEAD-2209-EB8AFA51DA23;
+        <t>ObjectID:4C47E6AB-D7A0-5C71-6BCD-4C8D2690AC98;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B19" authorId="0">
+    <comment ref="B15" authorId="0">
+      <text>
+        <t>ObjectID:CD86FD61-83F9-9DA7-7D54-D77F4A1A3551;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0">
       <text>
         <t>ObjectID:DB70A20B-321C-B6BE-4A98-86423B2E8D0C;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B24" authorId="0">
+    <comment ref="B25" authorId="0">
       <text>
         <t>ObjectID:80A3210E-DBD0-B637-11EF-D3150820523F;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="B25" authorId="0">
+    <comment ref="B26" authorId="0">
       <text>
         <t>ObjectID:5BC2BA8D-5621-5C8B-6033-60FA2A25A79A;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="B26" authorId="0">
+    <comment ref="B27" authorId="0">
       <text>
         <t>ObjectID:5C5FA035-3EB3-E214-2760-3495D3715ADD;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="B27" authorId="0">
-      <text>
-        <t>ObjectID:71E2CB75-16C9-4494-82BA-29A58998596E;
-Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
-      </text>
-    </comment>
     <comment ref="A30" authorId="0">
       <text>
         <t>ObjectID:110FB069-4B9F-3EC1-6FC7-D416346777ED;
@@ -440,95 +440,71 @@
     </comment>
     <comment ref="A169" authorId="0">
       <text>
-        <t>ObjectID:5C40F357-EE5C-80FD-0291-9F79E8683608;
-Class:oracle.dbtools.crest.model.design.relational.Table</t>
-      </text>
-    </comment>
-    <comment ref="B173" authorId="0">
-      <text>
-        <t>ObjectID:5B609735-98B7-35FD-C65C-EF956ECDE343;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B174" authorId="0">
-      <text>
-        <t>ObjectID:40EA085C-4114-BA7A-DCA7-FD3FE37559C9;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B179" authorId="0">
-      <text>
-        <t>ObjectID:01D07402-27E5-7860-AC0C-A34FA8D423FE;
-Class:oracle.dbtools.crest.model.design.relational.Index</t>
-      </text>
-    </comment>
-    <comment ref="A182" authorId="0">
-      <text>
         <t>ObjectID:86B573D7-CD13-EBD4-0C4F-B4DEE60F904A;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B186" authorId="0">
+    <comment ref="B173" authorId="0">
       <text>
         <t>ObjectID:9FF49873-5D91-649D-4627-2BE70D843F9F;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B187" authorId="0">
+    <comment ref="B174" authorId="0">
       <text>
         <t>ObjectID:A9E9D69C-9E14-EE96-C054-F15AB9C32B15;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B188" authorId="0">
+    <comment ref="B175" authorId="0">
       <text>
         <t>ObjectID:F3A998D8-1D5F-1C74-2B9B-FC8746DCE908;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B189" authorId="0">
+    <comment ref="B176" authorId="0">
       <text>
         <t>ObjectID:A8FA0751-F8E1-215B-1F12-B03EDE8C5C28;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B190" authorId="0">
+    <comment ref="B177" authorId="0">
       <text>
         <t>ObjectID:F1AE3A41-44AC-5762-B6B2-1A6B6C11A835;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B191" authorId="0">
+    <comment ref="B178" authorId="0">
       <text>
         <t>ObjectID:91D44BE7-0B08-6EA0-1784-F0EB2FC0AC7E;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B192" authorId="0">
+    <comment ref="B179" authorId="0">
       <text>
         <t>ObjectID:A0BFE2DC-173F-63A1-2AFD-A301BBCE67A9;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B193" authorId="0">
+    <comment ref="B180" authorId="0">
       <text>
         <t>ObjectID:76B9EBD1-4F6E-529B-CBA7-003422B33A73;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B198" authorId="0">
+    <comment ref="B185" authorId="0">
       <text>
         <t>ObjectID:5A1C52F7-A087-EF0C-0B33-F8586D15E9E2;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B203" authorId="0">
+    <comment ref="B190" authorId="0">
       <text>
         <t>ObjectID:41C8E158-D607-C5A8-F3E8-C14D33939608;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="B204" authorId="0">
+    <comment ref="B191" authorId="0">
       <text>
         <t>ObjectID:0930ED40-A874-E892-AE30-63D24583BC07;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
@@ -539,7 +515,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="367">
   <si>
     <t>Diccionario de datos BD</t>
   </si>
@@ -673,12 +649,6 @@
     <t>Result</t>
   </si>
   <si>
-    <t>5C40F357-EE5C-80FD-0291-9F79E8683608</t>
-  </si>
-  <si>
-    <t>Street</t>
-  </si>
-  <si>
     <t>86B573D7-CD13-EBD4-0C4F-B4DEE60F904A</t>
   </si>
   <si>
@@ -775,15 +745,6 @@
     <t>C8ED7A2E-0E35-1723-F199-7CD4839E3396</t>
   </si>
   <si>
-    <t>5B609735-98B7-35FD-C65C-EF956ECDE343</t>
-  </si>
-  <si>
-    <t>F47928F9-0511-BEAD-2209-EB8AFA51DA23</t>
-  </si>
-  <si>
-    <t>id_Street</t>
-  </si>
-  <si>
     <t>4D1FB96F-EE96-0EC4-8ABD-51B98E0E3C3A</t>
   </si>
   <si>
@@ -883,9 +844,6 @@
     <t>8AE41AEF-A676-BB67-ED5D-C9F22BEFB21A</t>
   </si>
   <si>
-    <t>40EA085C-4114-BA7A-DCA7-FD3FE37559C9</t>
-  </si>
-  <si>
     <t>D7E22633-D71E-98DB-2784-1CAED83A9A72</t>
   </si>
   <si>
@@ -928,6 +886,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>4C47E6AB-D7A0-5C71-6BCD-4C8D2690AC98</t>
+  </si>
+  <si>
+    <t>streetName</t>
+  </si>
+  <si>
+    <t>CD86FD61-83F9-9DA7-7D54-D77F4A1A3551</t>
+  </si>
+  <si>
+    <t>streetNumber</t>
+  </si>
+  <si>
     <t>0DFC53E1-50AE-D648-4130-42B1F6DCB4D4</t>
   </si>
   <si>
@@ -952,12 +922,6 @@
     <t>Address_Region_FK</t>
   </si>
   <si>
-    <t>71E2CB75-16C9-4494-82BA-29A58998596E</t>
-  </si>
-  <si>
-    <t>Address_Street_FK</t>
-  </si>
-  <si>
     <t>E8F9C766-3CC9-B6A7-C6A2-172C8BA0470C</t>
   </si>
   <si>
@@ -1048,12 +1012,6 @@
     <t>Result_PK</t>
   </si>
   <si>
-    <t>01D07402-27E5-7860-AC0C-A34FA8D423FE</t>
-  </si>
-  <si>
-    <t>Street_PK</t>
-  </si>
-  <si>
     <t>5A1C52F7-A087-EF0C-0B33-F8586D15E9E2</t>
   </si>
   <si>
@@ -1525,6 +1483,12 @@
     <t>NUMBER (20)</t>
   </si>
   <si>
+    <t>VARCHAR2 (100)</t>
+  </si>
+  <si>
+    <t>VARCHAR2 (50)</t>
+  </si>
+  <si>
     <t>Mandatory</t>
   </si>
   <si>
@@ -1643,9 +1607,6 @@
   </si>
   <si>
     <t>Result.id</t>
-  </si>
-  <si>
-    <t>Street.id</t>
   </si>
   <si>
     <t>VARCHAR2 (30)</t>
@@ -1844,7 +1805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:H204"/>
+  <dimension ref="A2:H191"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.61328125" customWidth="true" bestFit="true"/>
@@ -1864,904 +1825,904 @@
     </row>
     <row r="4" ht="18.0" customHeight="true">
       <c r="A4" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="5" ht="18.0" customHeight="true">
       <c r="A5" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="true">
       <c r="B7" t="s" s="5">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" ht="18.0" customHeight="true">
       <c r="B8" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="D8" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" ht="18.0" customHeight="true">
       <c r="B9" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" ht="18.0" customHeight="true">
       <c r="B10" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" ht="18.0" customHeight="true">
       <c r="B11" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" ht="18.0" customHeight="true">
       <c r="B12" s="6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" ht="18.0" customHeight="true">
       <c r="B13" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" ht="18.0" customHeight="true">
       <c r="B14" s="6" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E14" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15" ht="18.0" customHeight="true">
+      <c r="B15" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="18" ht="18.0" customHeight="true">
+      <c r="B18" t="s" s="5">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" ht="18.0" customHeight="true">
+      <c r="B19" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="G14" s="8" t="s">
+      <c r="E19" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="17" ht="18.0" customHeight="true">
-      <c r="B17" t="s" s="5">
+      <c r="F19" s="3" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="18" ht="18.0" customHeight="true">
-      <c r="B18" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="20" ht="18.0" customHeight="true">
+      <c r="B20" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="23" ht="18.0" customHeight="true">
+      <c r="B23" t="s" s="5">
         <v>335</v>
       </c>
-      <c r="E18" s="3" t="s">
+    </row>
+    <row r="24" ht="18.0" customHeight="true">
+      <c r="B24" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="19" ht="18.0" customHeight="true">
-      <c r="B19" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="22" ht="18.0" customHeight="true">
-      <c r="B22" t="s" s="5">
+      <c r="G24" s="3" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="23" ht="18.0" customHeight="true">
-      <c r="B23" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="24" ht="18.0" customHeight="true">
-      <c r="B24" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>318</v>
+      <c r="H24" s="3" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="25" ht="18.0" customHeight="true">
       <c r="B25" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="26" ht="18.0" customHeight="true">
       <c r="B26" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" ht="18.0" customHeight="true">
       <c r="B27" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" ht="18.0" customHeight="true">
       <c r="A29" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="30" ht="18.0" customHeight="true">
       <c r="A30" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="32" ht="18.0" customHeight="true">
       <c r="B32" t="s" s="5">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" ht="18.0" customHeight="true">
       <c r="B33" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="D33" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="G33" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" ht="18.0" customHeight="true">
       <c r="B34" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35" ht="18.0" customHeight="true">
       <c r="B35" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" ht="18.0" customHeight="true">
       <c r="B36" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="37" ht="18.0" customHeight="true">
       <c r="B37" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38" ht="18.0" customHeight="true">
       <c r="B38" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39" ht="18.0" customHeight="true">
       <c r="B39" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" ht="18.0" customHeight="true">
       <c r="B40" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41" ht="18.0" customHeight="true">
       <c r="B41" s="6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" ht="18.0" customHeight="true">
       <c r="B42" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" ht="18.0" customHeight="true">
       <c r="B43" s="6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" ht="18.0" customHeight="true">
       <c r="B44" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" ht="18.0" customHeight="true">
       <c r="B47" t="s" s="5">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="48" ht="18.0" customHeight="true">
       <c r="B48" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" ht="18.0" customHeight="true">
       <c r="B49" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" ht="18.0" customHeight="true">
       <c r="B52" t="s" s="5">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" ht="18.0" customHeight="true">
       <c r="B53" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" ht="18.0" customHeight="true">
       <c r="B54" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="55" ht="18.0" customHeight="true">
       <c r="B55" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="57" ht="18.0" customHeight="true">
       <c r="A57" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="58" ht="18.0" customHeight="true">
       <c r="A58" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="60" ht="18.0" customHeight="true">
       <c r="B60" t="s" s="5">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="61" ht="18.0" customHeight="true">
       <c r="B61" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="D61" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E61" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="G61" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="62" ht="18.0" customHeight="true">
       <c r="B62" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="63" ht="18.0" customHeight="true">
@@ -2769,437 +2730,437 @@
         <v>3</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="66" ht="18.0" customHeight="true">
       <c r="B66" t="s" s="5">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" ht="18.0" customHeight="true">
       <c r="B67" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="68" ht="18.0" customHeight="true">
       <c r="B68" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="70" ht="18.0" customHeight="true">
       <c r="A70" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="71" ht="18.0" customHeight="true">
       <c r="A71" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="73" ht="18.0" customHeight="true">
       <c r="B73" t="s" s="5">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="74" ht="18.0" customHeight="true">
       <c r="B74" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="D74" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F74" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="G74" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="75" ht="18.0" customHeight="true">
       <c r="B75" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="76" ht="18.0" customHeight="true">
       <c r="B76" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="77" ht="18.0" customHeight="true">
       <c r="B77" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="78" ht="18.0" customHeight="true">
       <c r="B78" s="6" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="79" ht="18.0" customHeight="true">
       <c r="B79" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="82" ht="18.0" customHeight="true">
       <c r="B82" t="s" s="5">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="83" ht="18.0" customHeight="true">
       <c r="B83" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="84" ht="18.0" customHeight="true">
       <c r="B84" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="87" ht="18.0" customHeight="true">
       <c r="B87" t="s" s="5">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="88" ht="18.0" customHeight="true">
       <c r="B88" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="89" ht="18.0" customHeight="true">
       <c r="B89" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="91" ht="18.0" customHeight="true">
       <c r="A91" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="92" ht="18.0" customHeight="true">
       <c r="A92" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="94" ht="18.0" customHeight="true">
       <c r="B94" t="s" s="5">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="95" ht="18.0" customHeight="true">
       <c r="B95" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C95" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="D95" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F95" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E95" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="G95" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="96" ht="18.0" customHeight="true">
       <c r="B96" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="97" ht="18.0" customHeight="true">
@@ -3207,181 +3168,181 @@
         <v>3</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="100" ht="18.0" customHeight="true">
       <c r="B100" t="s" s="5">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="101" ht="18.0" customHeight="true">
       <c r="B101" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="102" ht="18.0" customHeight="true">
       <c r="B102" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="104" ht="18.0" customHeight="true">
       <c r="A104" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="105" ht="18.0" customHeight="true">
       <c r="A105" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="107" ht="18.0" customHeight="true">
       <c r="B107" t="s" s="5">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="108" ht="18.0" customHeight="true">
       <c r="B108" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C108" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="D108" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F108" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E108" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="G108" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="109" ht="18.0" customHeight="true">
       <c r="B109" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="110" ht="18.0" customHeight="true">
       <c r="B110" s="6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="111" ht="18.0" customHeight="true">
@@ -3389,201 +3350,201 @@
         <v>3</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="112" ht="18.0" customHeight="true">
       <c r="B112" s="6" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="115" ht="18.0" customHeight="true">
       <c r="B115" t="s" s="5">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="116" ht="18.0" customHeight="true">
       <c r="B116" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="117" ht="18.0" customHeight="true">
       <c r="B117" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="118" ht="18.0" customHeight="true">
       <c r="B118" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="120" ht="18.0" customHeight="true">
       <c r="A120" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F120" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="121" ht="18.0" customHeight="true">
       <c r="A121" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="123" ht="18.0" customHeight="true">
       <c r="B123" t="s" s="5">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="124" ht="18.0" customHeight="true">
       <c r="B124" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C124" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="D124" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F124" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E124" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="G124" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="125" ht="18.0" customHeight="true">
       <c r="B125" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="126" ht="18.0" customHeight="true">
@@ -3591,158 +3552,158 @@
         <v>3</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="129" ht="18.0" customHeight="true">
       <c r="B129" t="s" s="5">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="130" ht="18.0" customHeight="true">
       <c r="B130" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="131" ht="18.0" customHeight="true">
       <c r="B131" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="133" ht="18.0" customHeight="true">
       <c r="A133" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F133" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="134" ht="18.0" customHeight="true">
       <c r="A134" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="136" ht="18.0" customHeight="true">
       <c r="B136" t="s" s="5">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="137" ht="18.0" customHeight="true">
       <c r="B137" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C137" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C137" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="D137" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F137" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E137" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F137" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="G137" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="138" ht="18.0" customHeight="true">
       <c r="B138" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="139" ht="18.0" customHeight="true">
@@ -3750,899 +3711,740 @@
         <v>3</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="142" ht="18.0" customHeight="true">
       <c r="B142" t="s" s="5">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="143" ht="18.0" customHeight="true">
       <c r="B143" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="144" ht="18.0" customHeight="true">
       <c r="B144" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="146" ht="18.0" customHeight="true">
       <c r="A146" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F146" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="147" ht="18.0" customHeight="true">
       <c r="A147" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="149" ht="18.0" customHeight="true">
       <c r="B149" t="s" s="5">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="150" ht="18.0" customHeight="true">
       <c r="B150" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C150" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C150" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="D150" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F150" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E150" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="G150" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="151" ht="18.0" customHeight="true">
       <c r="B151" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H151" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="152" ht="18.0" customHeight="true">
       <c r="B152" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="153" ht="18.0" customHeight="true">
       <c r="B153" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H153" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="154" ht="18.0" customHeight="true">
       <c r="B154" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="155" ht="18.0" customHeight="true">
       <c r="B155" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="156" ht="18.0" customHeight="true">
       <c r="B156" s="6" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="159" ht="18.0" customHeight="true">
       <c r="B159" t="s" s="5">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="160" ht="18.0" customHeight="true">
       <c r="B160" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="161" ht="18.0" customHeight="true">
       <c r="B161" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="G161" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="164" ht="18.0" customHeight="true">
       <c r="B164" t="s" s="5">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="165" ht="18.0" customHeight="true">
       <c r="B165" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="166" ht="18.0" customHeight="true">
       <c r="B166" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="168" ht="18.0" customHeight="true">
       <c r="A168" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F168" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="169" ht="18.0" customHeight="true">
       <c r="A169" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>45</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="171" ht="18.0" customHeight="true">
       <c r="B171" t="s" s="5">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="172" ht="18.0" customHeight="true">
       <c r="B172" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C172" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C172" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="D172" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F172" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E172" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F172" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="G172" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="173" ht="18.0" customHeight="true">
       <c r="B173" s="6" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F173" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="174" ht="18.0" customHeight="true">
       <c r="B174" s="6" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="175" ht="18.0" customHeight="true">
+      <c r="B175" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="E175" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H175" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="176" ht="18.0" customHeight="true">
+      <c r="B176" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H176" s="6" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="177" ht="18.0" customHeight="true">
-      <c r="B177" t="s" s="5">
-        <v>334</v>
+      <c r="B177" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E177" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H177" s="6" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="178" ht="18.0" customHeight="true">
-      <c r="B178" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="E178" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F178" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G178" s="3" t="s">
+      <c r="B178" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C178" s="8" t="s">
         <v>321</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H178" s="6" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="179" ht="18.0" customHeight="true">
       <c r="B179" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H179" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="180" ht="18.0" customHeight="true">
+      <c r="B180" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E180" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H180" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="183" ht="18.0" customHeight="true">
+      <c r="B183" t="s" s="5">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="184" ht="18.0" customHeight="true">
+      <c r="B184" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E184" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C179" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D179" s="6" t="s">
+      <c r="F184" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="185" ht="18.0" customHeight="true">
+      <c r="B185" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="G185" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="188" ht="18.0" customHeight="true">
+      <c r="B188" t="s" s="5">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="189" ht="18.0" customHeight="true">
+      <c r="B189" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C189" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="E179" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="F179" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="G179" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="181" ht="18.0" customHeight="true">
-      <c r="A181" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F181" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="182" ht="18.0" customHeight="true">
-      <c r="A182" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="B182" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C182" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="D182" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="E182" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="F182" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="184" ht="18.0" customHeight="true">
-      <c r="B184" t="s" s="5">
+      <c r="D189" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E189" s="3" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="185" ht="18.0" customHeight="true">
-      <c r="B185" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C185" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D185" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="E185" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F185" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G185" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="H185" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="186" ht="18.0" customHeight="true">
-      <c r="B186" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C186" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="D186" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="E186" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="F186" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="G186" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="H186" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="187" ht="18.0" customHeight="true">
-      <c r="B187" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C187" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="D187" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="E187" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="F187" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="G187" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="H187" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="188" ht="18.0" customHeight="true">
-      <c r="B188" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C188" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="D188" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="E188" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="F188" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="G188" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="189" ht="18.0" customHeight="true">
-      <c r="B189" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C189" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="D189" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="E189" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="F189" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="G189" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="H189" s="6" t="s">
-        <v>318</v>
+      <c r="F189" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H189" s="3" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="190" ht="18.0" customHeight="true">
       <c r="B190" s="6" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="D190" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="E190" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="F190" s="8" t="s">
-        <v>329</v>
+        <v>29</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F190" s="7" t="s">
+        <v>325</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="191" ht="18.0" customHeight="true">
       <c r="B191" s="6" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="D191" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="E191" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="F191" s="8" t="s">
-        <v>329</v>
+        <v>37</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E191" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F191" s="7" t="s">
+        <v>325</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="192" ht="18.0" customHeight="true">
-      <c r="B192" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C192" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="D192" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="E192" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="F192" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="G192" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="H192" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="193" ht="18.0" customHeight="true">
-      <c r="B193" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C193" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="D193" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="E193" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="F193" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="G193" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="H193" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="196" ht="18.0" customHeight="true">
-      <c r="B196" t="s" s="5">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="197" ht="18.0" customHeight="true">
-      <c r="B197" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C197" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="E197" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F197" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G197" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="198" ht="18.0" customHeight="true">
-      <c r="B198" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="C198" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D198" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="E198" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F198" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="G198" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="201" ht="18.0" customHeight="true">
-      <c r="B201" t="s" s="5">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="202" ht="18.0" customHeight="true">
-      <c r="B202" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C202" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="E202" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F202" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G202" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="H202" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="203" ht="18.0" customHeight="true">
-      <c r="B203" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C203" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D203" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E203" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="F203" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="G203" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="H203" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="204" ht="18.0" customHeight="true">
-      <c r="B204" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C204" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D204" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="E204" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="F204" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="G204" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="H204" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -4650,15 +4452,12 @@
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <dataValidations count="53">
+  <dataValidations count="48">
     <dataValidation type="list" sqref="A5" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B19" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B20" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="D24" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="D25" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
@@ -4669,9 +4468,6 @@
     <dataValidation type="list" sqref="D27" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E24" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
     <dataValidation type="list" sqref="E25" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
@@ -4679,9 +4475,6 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E27" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="F24" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F25" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
@@ -4783,31 +4576,25 @@
     <dataValidation type="list" sqref="A169" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B179" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B185" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A182" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>null!B1:B65000</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="B198" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>null!B1:B65000</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="D203" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D190" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D204" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D191" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E203" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E190" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E204" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E191" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F203" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F190" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F204" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F191" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4824,18 +4611,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -4983,7 +4770,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5064,14 +4851,6 @@
       </c>
       <c r="B10" s="8" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -5082,300 +4861,300 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>83</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>85</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>95</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>97</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>103</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>108</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>3</v>
@@ -5383,7 +5162,7 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>3</v>
@@ -5391,7 +5170,7 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>3</v>
@@ -5399,26 +5178,26 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>3</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>3</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -5475,14 +5254,6 @@
       </c>
       <c r="B49" s="8" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -5493,87 +5264,79 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -5584,95 +5347,87 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -5688,10 +5443,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -5707,546 +5462,546 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -6262,10 +6017,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>

--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
@@ -128,377 +128,371 @@
     </comment>
     <comment ref="B36" authorId="0">
       <text>
-        <t>ObjectID:F0E2A9CA-081F-71E9-A9CF-56DDA0A7C649;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B37" authorId="0">
-      <text>
         <t>ObjectID:84B350A2-E9F9-85B7-82B4-BB09E44FACDE;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B38" authorId="0">
+    <comment ref="B37" authorId="0">
       <text>
         <t>ObjectID:33E979A1-6E80-51D0-D0EB-DB2F8C0A44B6;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B39" authorId="0">
+    <comment ref="B38" authorId="0">
       <text>
         <t>ObjectID:7FA5E6A9-9A61-5313-E18B-87C24201D6EE;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B44" authorId="0">
+    <comment ref="B43" authorId="0">
       <text>
         <t>ObjectID:F31A8785-1566-8B79-1912-4802899ECAFD;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B49" authorId="0">
+    <comment ref="B48" authorId="0">
       <text>
         <t>ObjectID:5AC0DBA5-98DC-16BD-67F0-8C7D65E7464D;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="B50" authorId="0">
+    <comment ref="B49" authorId="0">
       <text>
         <t>ObjectID:5DC850B4-B7D2-DE05-EED0-5AE8208A555B;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="A53" authorId="0">
+    <comment ref="A52" authorId="0">
       <text>
         <t>ObjectID:B8A5A6AB-2C80-7160-F587-FEB1D73E4E23;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B57" authorId="0">
+    <comment ref="B56" authorId="0">
       <text>
         <t>ObjectID:86432DD4-A51F-0F1A-801B-E081457493D2;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B58" authorId="0">
+    <comment ref="B57" authorId="0">
       <text>
         <t>ObjectID:6D3F8C10-15CC-9855-E924-64034831049A;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B59" authorId="0">
+    <comment ref="B58" authorId="0">
       <text>
         <t>ObjectID:C244A13E-4EC5-7FE2-F02C-F3A05700E232;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B64" authorId="0">
+    <comment ref="B63" authorId="0">
       <text>
         <t>ObjectID:9448563C-C682-6E0F-0396-00EC03FF551D;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B69" authorId="0">
+    <comment ref="B68" authorId="0">
       <text>
         <t>ObjectID:8E87AA14-C0E3-100D-3FFA-36B5F9A38D60;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="A72" authorId="0">
+    <comment ref="A71" authorId="0">
       <text>
         <t>ObjectID:ECD94709-BBE0-91B5-6EFC-7283F3196C54;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B76" authorId="0">
+    <comment ref="B75" authorId="0">
       <text>
         <t>ObjectID:B068C7BF-D6C8-8135-54F3-DDC2CF1E801B;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B77" authorId="0">
+    <comment ref="B76" authorId="0">
       <text>
         <t>ObjectID:25520CDC-89E3-3BB2-6C44-D60D793C0FA6;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B78" authorId="0">
+    <comment ref="B77" authorId="0">
       <text>
         <t>ObjectID:AADA8B95-96A5-9B24-D7F4-7F015851EFF7;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B79" authorId="0">
+    <comment ref="B78" authorId="0">
       <text>
         <t>ObjectID:94A37B47-9D6B-94F0-9194-957D5671222E;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B80" authorId="0">
+    <comment ref="B79" authorId="0">
       <text>
         <t>ObjectID:BD0F476A-18A9-713C-FBDC-49A23226251A;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B85" authorId="0">
+    <comment ref="B84" authorId="0">
       <text>
         <t>ObjectID:8E294E81-0842-B977-DF00-91D5568B7812;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B90" authorId="0">
+    <comment ref="B89" authorId="0">
       <text>
         <t>ObjectID:FFA23F90-E801-A2D4-E9AC-BE2D4531FC43;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="A93" authorId="0">
+    <comment ref="A92" authorId="0">
       <text>
         <t>ObjectID:D05B5757-4762-17E8-B189-F7DC6C717D4E;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B97" authorId="0">
+    <comment ref="B96" authorId="0">
       <text>
         <t>ObjectID:DC9AB24C-5C4B-1DFF-39C9-3BAEF6CA017E;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B98" authorId="0">
+    <comment ref="B97" authorId="0">
       <text>
         <t>ObjectID:E7804AD4-C5ED-A377-4A90-C1371CBB955D;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B103" authorId="0">
+    <comment ref="B102" authorId="0">
       <text>
         <t>ObjectID:6CB0705F-75C2-8815-A321-6BFA5FAAD288;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="A106" authorId="0">
+    <comment ref="A105" authorId="0">
       <text>
         <t>ObjectID:EE087F47-DD00-CF9F-8B94-45B6F08D990F;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B110" authorId="0">
+    <comment ref="B109" authorId="0">
       <text>
         <t>ObjectID:0A105682-F262-699F-9D1F-B2F7A92E0ADB;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B111" authorId="0">
+    <comment ref="B110" authorId="0">
       <text>
         <t>ObjectID:345BBC95-8061-A492-629E-89A2027EDFED;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B112" authorId="0">
+    <comment ref="B111" authorId="0">
       <text>
         <t>ObjectID:F04CE297-E165-2863-6399-6445729722B5;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B113" authorId="0">
+    <comment ref="B112" authorId="0">
       <text>
         <t>ObjectID:7C86E4ED-7D02-8E89-3A74-2026A356808F;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B118" authorId="0">
+    <comment ref="B117" authorId="0">
       <text>
         <t>ObjectID:05CADB4C-D83F-8791-DD94-9FBFE95D096B;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B119" authorId="0">
+    <comment ref="B118" authorId="0">
       <text>
         <t>ObjectID:79E96C4E-1C5C-543C-C318-7D832E4B5819;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="A122" authorId="0">
+    <comment ref="A121" authorId="0">
       <text>
         <t>ObjectID:B4785CBF-D492-D2F4-33C2-78823D081196;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B126" authorId="0">
+    <comment ref="B125" authorId="0">
       <text>
         <t>ObjectID:C02128BD-9BE9-8E01-3E5E-62EFA28C591A;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B127" authorId="0">
+    <comment ref="B126" authorId="0">
       <text>
         <t>ObjectID:E6A67916-6F07-F598-52A0-5C1E5643F34D;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B132" authorId="0">
+    <comment ref="B131" authorId="0">
       <text>
         <t>ObjectID:89CBDD51-BB44-850F-A47D-3D8533C3CD85;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="A135" authorId="0">
+    <comment ref="A134" authorId="0">
       <text>
         <t>ObjectID:F3F4FA94-F84B-402E-6080-E86D2042628B;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B139" authorId="0">
+    <comment ref="B138" authorId="0">
       <text>
         <t>ObjectID:1662C822-6030-377B-C88E-D7FDE3DBD485;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B140" authorId="0">
+    <comment ref="B139" authorId="0">
       <text>
         <t>ObjectID:37AFA439-59F7-1168-D545-69590D41617C;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B141" authorId="0">
+    <comment ref="B140" authorId="0">
       <text>
         <t>ObjectID:80EA0F28-60B7-4A8F-7254-364B8BD0CC49;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B146" authorId="0">
+    <comment ref="B145" authorId="0">
       <text>
         <t>ObjectID:B58ED608-D363-3FBA-D4FB-C8488BA89B82;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B151" authorId="0">
+    <comment ref="B150" authorId="0">
       <text>
         <t>ObjectID:919AA2F5-AF80-5051-B6F9-538494FE7BAC;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="A154" authorId="0">
+    <comment ref="A153" authorId="0">
       <text>
         <t>ObjectID:8827044B-4A9A-3231-00AE-A01022AC9207;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B158" authorId="0">
+    <comment ref="B157" authorId="0">
       <text>
         <t>ObjectID:0066ECFA-6810-AAC0-BE37-A2A6A7971D22;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B159" authorId="0">
+    <comment ref="B158" authorId="0">
       <text>
         <t>ObjectID:F6B4833B-B9F0-C041-42C8-2A06E11033D2;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B160" authorId="0">
+    <comment ref="B159" authorId="0">
       <text>
         <t>ObjectID:9D2F8BAD-E6E3-B34E-6E99-D3AD8ADC16BE;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B161" authorId="0">
+    <comment ref="B160" authorId="0">
       <text>
         <t>ObjectID:8795FAAF-3165-81A8-FF96-DC0C48E69B9E;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B162" authorId="0">
+    <comment ref="B161" authorId="0">
       <text>
         <t>ObjectID:4A79AC62-C425-C8C1-3A70-B42E1BAEE9D5;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B163" authorId="0">
+    <comment ref="B162" authorId="0">
       <text>
         <t>ObjectID:C4C71948-2C7D-6B64-4FB9-2589057DABB5;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B168" authorId="0">
+    <comment ref="B167" authorId="0">
       <text>
         <t>ObjectID:E425749D-D18D-D192-E4D8-326F4435D4F2;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B173" authorId="0">
+    <comment ref="B172" authorId="0">
       <text>
         <t>ObjectID:AB9E84E2-5500-6E2C-67D3-DF1370708BDF;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="A176" authorId="0">
+    <comment ref="A175" authorId="0">
       <text>
         <t>ObjectID:CB285AEA-5E99-A1B2-D71F-63C2A1502E59;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B180" authorId="0">
+    <comment ref="B179" authorId="0">
       <text>
         <t>ObjectID:01F22734-10A7-3051-FC8E-C5193520622D;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B181" authorId="0">
+    <comment ref="B180" authorId="0">
       <text>
         <t>ObjectID:0D39920E-AC44-F378-CFA1-8A48D7B43D34;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B182" authorId="0">
+    <comment ref="B181" authorId="0">
       <text>
         <t>ObjectID:D32BC5DD-CA21-E925-6A96-0ECEF775B517;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B183" authorId="0">
+    <comment ref="B182" authorId="0">
       <text>
         <t>ObjectID:B7A72C42-C555-1D3D-3E90-655FB8E2CE88;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B184" authorId="0">
+    <comment ref="B183" authorId="0">
       <text>
         <t>ObjectID:B28DB384-F898-21CF-4DE4-34CDFB1673F1;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B185" authorId="0">
+    <comment ref="B184" authorId="0">
       <text>
         <t>ObjectID:C410357A-98CA-84CD-8815-B3C25556F333;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B186" authorId="0">
+    <comment ref="B185" authorId="0">
       <text>
         <t>ObjectID:898749AB-398D-26C3-3C4F-A88AFD9ACDF6;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B187" authorId="0">
+    <comment ref="B186" authorId="0">
       <text>
         <t>ObjectID:340579EC-8B22-1285-4D53-F5C3ECCFC0F3;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B192" authorId="0">
+    <comment ref="B191" authorId="0">
       <text>
         <t>ObjectID:5CC83417-CD6D-1C2E-C695-8664F8B61C41;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B197" authorId="0">
+    <comment ref="B196" authorId="0">
       <text>
         <t>ObjectID:AA6605AF-93AE-856D-9F64-C0175D1DF2C6;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="B198" authorId="0">
+    <comment ref="B197" authorId="0">
       <text>
         <t>ObjectID:74D8B263-9FF2-4C7D-6BA9-935B0A7F0914;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
@@ -509,7 +503,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="364">
   <si>
     <t>Diccionario de datos BD</t>
   </si>
@@ -806,12 +800,6 @@
   </si>
   <si>
     <t>lastName</t>
-  </si>
-  <si>
-    <t>F0E2A9CA-081F-71E9-A9CF-56DDA0A7C649</t>
-  </si>
-  <si>
-    <t>middleName</t>
   </si>
   <si>
     <t>345BBC95-8061-A492-629E-89A2027EDFED</t>
@@ -1796,7 +1784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:H198"/>
+  <dimension ref="A2:H197"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.61328125" customWidth="true" bestFit="true"/>
@@ -1816,70 +1804,70 @@
     </row>
     <row r="4" ht="18.0" customHeight="true">
       <c r="A4" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="5" ht="18.0" customHeight="true">
       <c r="A5" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="true">
       <c r="B7" t="s" s="5">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" ht="18.0" customHeight="true">
       <c r="B8" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>312</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="9" ht="18.0" customHeight="true">
@@ -1887,22 +1875,22 @@
         <v>65</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" ht="18.0" customHeight="true">
@@ -1910,232 +1898,232 @@
         <v>78</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" ht="18.0" customHeight="true">
       <c r="B11" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" ht="18.0" customHeight="true">
       <c r="B12" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" ht="18.0" customHeight="true">
       <c r="B15" t="s" s="5">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" ht="18.0" customHeight="true">
       <c r="B16" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>312</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="17" ht="18.0" customHeight="true">
       <c r="B17" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" ht="18.0" customHeight="true">
       <c r="B20" t="s" s="5">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" ht="18.0" customHeight="true">
       <c r="B21" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>312</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="22" ht="18.0" customHeight="true">
       <c r="B22" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" ht="18.0" customHeight="true">
       <c r="A24" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="25" ht="18.0" customHeight="true">
       <c r="A25" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" ht="18.0" customHeight="true">
       <c r="B27" t="s" s="5">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" ht="18.0" customHeight="true">
       <c r="B28" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>312</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="29" ht="18.0" customHeight="true">
@@ -2143,22 +2131,22 @@
         <v>51</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" ht="18.0" customHeight="true">
@@ -2166,22 +2154,22 @@
         <v>61</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" ht="18.0" customHeight="true">
@@ -2189,22 +2177,22 @@
         <v>63</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32" ht="18.0" customHeight="true">
@@ -2212,22 +2200,22 @@
         <v>65</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" ht="18.0" customHeight="true">
@@ -2235,22 +2223,22 @@
         <v>76</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" ht="18.0" customHeight="true">
@@ -2258,22 +2246,22 @@
         <v>80</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" ht="18.0" customHeight="true">
@@ -2281,45 +2269,45 @@
         <v>98</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" ht="18.0" customHeight="true">
       <c r="B36" s="6" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" ht="18.0" customHeight="true">
@@ -2327,141 +2315,141 @@
         <v>109</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="38" ht="18.0" customHeight="true">
       <c r="B38" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>323</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="39" ht="18.0" customHeight="true">
-      <c r="B39" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="41" ht="18.0" customHeight="true">
+      <c r="B41" t="s" s="5">
+        <v>326</v>
       </c>
     </row>
     <row r="42" ht="18.0" customHeight="true">
-      <c r="B42" t="s" s="5">
+      <c r="B42" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="43" ht="18.0" customHeight="true">
+      <c r="B43" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="43" ht="18.0" customHeight="true">
-      <c r="B43" s="3" t="s">
+      <c r="E43" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="46" ht="18.0" customHeight="true">
+      <c r="B46" t="s" s="5">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="47" ht="18.0" customHeight="true">
+      <c r="B47" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C47" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="44" ht="18.0" customHeight="true">
-      <c r="B44" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="47" ht="18.0" customHeight="true">
-      <c r="B47" t="s" s="5">
-        <v>333</v>
-      </c>
     </row>
     <row r="48" ht="18.0" customHeight="true">
-      <c r="B48" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>314</v>
+      <c r="B48" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="49" ht="18.0" customHeight="true">
@@ -2469,1731 +2457,1731 @@
         <v>131</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G49" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="51" ht="18.0" customHeight="true">
+      <c r="A51" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="52" ht="18.0" customHeight="true">
+      <c r="A52" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="54" ht="18.0" customHeight="true">
+      <c r="B54" t="s" s="5">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="55" ht="18.0" customHeight="true">
+      <c r="B55" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="H49" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="50" ht="18.0" customHeight="true">
-      <c r="B50" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="52" ht="18.0" customHeight="true">
-      <c r="A52" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B52" s="2" t="s">
+      <c r="H55" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="53" ht="18.0" customHeight="true">
-      <c r="A53" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="55" ht="18.0" customHeight="true">
-      <c r="B55" t="s" s="5">
+    </row>
+    <row r="56" ht="18.0" customHeight="true">
+      <c r="B56" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" s="8" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="56" ht="18.0" customHeight="true">
-      <c r="B56" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>314</v>
+      <c r="D56" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="57" ht="18.0" customHeight="true">
       <c r="B57" s="6" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>323</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="58" ht="18.0" customHeight="true">
       <c r="B58" s="6" t="s">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E58" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="61" ht="18.0" customHeight="true">
+      <c r="B61" t="s" s="5">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="62" ht="18.0" customHeight="true">
+      <c r="B62" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="63" ht="18.0" customHeight="true">
+      <c r="B63" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="66" ht="18.0" customHeight="true">
+      <c r="B66" t="s" s="5">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="67" ht="18.0" customHeight="true">
+      <c r="B67" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="68" ht="18.0" customHeight="true">
+      <c r="B68" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="70" ht="18.0" customHeight="true">
+      <c r="A70" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="71" ht="18.0" customHeight="true">
+      <c r="A71" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="73" ht="18.0" customHeight="true">
+      <c r="B73" t="s" s="5">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="74" ht="18.0" customHeight="true">
+      <c r="B74" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G74" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="F58" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="59" ht="18.0" customHeight="true">
-      <c r="B59" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C59" s="8" t="s">
+      <c r="H74" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="75" ht="18.0" customHeight="true">
+      <c r="B75" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C75" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="D59" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="62" ht="18.0" customHeight="true">
-      <c r="B62" t="s" s="5">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="63" ht="18.0" customHeight="true">
-      <c r="B63" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="64" ht="18.0" customHeight="true">
-      <c r="B64" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="67" ht="18.0" customHeight="true">
-      <c r="B67" t="s" s="5">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="68" ht="18.0" customHeight="true">
-      <c r="B68" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="69" ht="18.0" customHeight="true">
-      <c r="B69" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="H69" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="71" ht="18.0" customHeight="true">
-      <c r="A71" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="72" ht="18.0" customHeight="true">
-      <c r="A72" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F72" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="74" ht="18.0" customHeight="true">
-      <c r="B74" t="s" s="5">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="75" ht="18.0" customHeight="true">
-      <c r="B75" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>314</v>
+      <c r="D75" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="76" ht="18.0" customHeight="true">
       <c r="B76" s="6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="77" ht="18.0" customHeight="true">
       <c r="B77" s="6" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>323</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="78" ht="18.0" customHeight="true">
       <c r="B78" s="6" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>319</v>
+        <v>347</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>323</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="79" ht="18.0" customHeight="true">
       <c r="B79" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E79" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="82" ht="18.0" customHeight="true">
+      <c r="B82" t="s" s="5">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="83" ht="18.0" customHeight="true">
+      <c r="B83" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="84" ht="18.0" customHeight="true">
+      <c r="B84" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="87" ht="18.0" customHeight="true">
+      <c r="B87" t="s" s="5">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="88" ht="18.0" customHeight="true">
+      <c r="B88" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="89" ht="18.0" customHeight="true">
+      <c r="B89" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="91" ht="18.0" customHeight="true">
+      <c r="A91" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="92" ht="18.0" customHeight="true">
+      <c r="A92" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="94" ht="18.0" customHeight="true">
+      <c r="B94" t="s" s="5">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="95" ht="18.0" customHeight="true">
+      <c r="B95" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G95" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="F79" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="80" ht="18.0" customHeight="true">
-      <c r="B80" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="83" ht="18.0" customHeight="true">
-      <c r="B83" t="s" s="5">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="84" ht="18.0" customHeight="true">
-      <c r="B84" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C84" s="3" t="s">
+      <c r="H95" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E84" s="3" t="s">
+    </row>
+    <row r="96" ht="18.0" customHeight="true">
+      <c r="B96" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C96" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="85" ht="18.0" customHeight="true">
-      <c r="B85" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="F85" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="88" ht="18.0" customHeight="true">
-      <c r="B88" t="s" s="5">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="89" ht="18.0" customHeight="true">
-      <c r="B89" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="90" ht="18.0" customHeight="true">
-      <c r="B90" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="G90" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="92" ht="18.0" customHeight="true">
-      <c r="A92" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="93" ht="18.0" customHeight="true">
-      <c r="A93" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="95" ht="18.0" customHeight="true">
-      <c r="B95" t="s" s="5">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="96" ht="18.0" customHeight="true">
-      <c r="B96" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>314</v>
+      <c r="D96" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="97" ht="18.0" customHeight="true">
       <c r="B97" s="6" t="s">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>319</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E97" s="8" t="s">
         <v>323</v>
       </c>
       <c r="F97" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="100" ht="18.0" customHeight="true">
+      <c r="B100" t="s" s="5">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="101" ht="18.0" customHeight="true">
+      <c r="B101" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="102" ht="18.0" customHeight="true">
+      <c r="B102" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="104" ht="18.0" customHeight="true">
+      <c r="A104" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="105" ht="18.0" customHeight="true">
+      <c r="A105" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="107" ht="18.0" customHeight="true">
+      <c r="B107" t="s" s="5">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="108" ht="18.0" customHeight="true">
+      <c r="B108" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G108" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="G97" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="98" ht="18.0" customHeight="true">
-      <c r="B98" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G98" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="101" ht="18.0" customHeight="true">
-      <c r="B101" t="s" s="5">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="102" ht="18.0" customHeight="true">
-      <c r="B102" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C102" s="3" t="s">
+      <c r="H108" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E102" s="3" t="s">
+    </row>
+    <row r="109" ht="18.0" customHeight="true">
+      <c r="B109" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C109" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="103" ht="18.0" customHeight="true">
-      <c r="B103" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="105" ht="18.0" customHeight="true">
-      <c r="A105" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="106" ht="18.0" customHeight="true">
-      <c r="A106" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D106" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E106" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="108" ht="18.0" customHeight="true">
-      <c r="B108" t="s" s="5">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="109" ht="18.0" customHeight="true">
-      <c r="B109" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>314</v>
+      <c r="D109" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="110" ht="18.0" customHeight="true">
       <c r="B110" s="6" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E110" s="8" t="s">
         <v>323</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="111" ht="18.0" customHeight="true">
       <c r="B111" s="6" t="s">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="112" ht="18.0" customHeight="true">
       <c r="B112" s="6" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="C112" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="115" ht="18.0" customHeight="true">
+      <c r="B115" t="s" s="5">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="116" ht="18.0" customHeight="true">
+      <c r="B116" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="117" ht="18.0" customHeight="true">
+      <c r="B117" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E117" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="D112" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G112" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="113" ht="18.0" customHeight="true">
-      <c r="B113" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="D113" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G113" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H113" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="116" ht="18.0" customHeight="true">
-      <c r="B116" t="s" s="5">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="117" ht="18.0" customHeight="true">
-      <c r="B117" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>314</v>
+      <c r="F117" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="118" ht="18.0" customHeight="true">
       <c r="B118" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="120" ht="18.0" customHeight="true">
+      <c r="A120" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G118" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="119" ht="18.0" customHeight="true">
-      <c r="B119" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="E119" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G119" s="6" t="s">
-        <v>311</v>
+      <c r="D120" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="121" ht="18.0" customHeight="true">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="123" ht="18.0" customHeight="true">
+      <c r="B123" t="s" s="5">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="124" ht="18.0" customHeight="true">
+      <c r="B124" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="C124" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H124" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="122" ht="18.0" customHeight="true">
-      <c r="A122" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C122" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="124" ht="18.0" customHeight="true">
-      <c r="B124" t="s" s="5">
+    </row>
+    <row r="125" ht="18.0" customHeight="true">
+      <c r="B125" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C125" s="8" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="125" ht="18.0" customHeight="true">
-      <c r="B125" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F125" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G125" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="H125" s="3" t="s">
-        <v>314</v>
+      <c r="D125" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H125" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="126" ht="18.0" customHeight="true">
       <c r="B126" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="129" ht="18.0" customHeight="true">
+      <c r="B129" t="s" s="5">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="130" ht="18.0" customHeight="true">
+      <c r="B130" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="131" ht="18.0" customHeight="true">
+      <c r="B131" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="133" ht="18.0" customHeight="true">
+      <c r="A133" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="134" ht="18.0" customHeight="true">
+      <c r="A134" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="136" ht="18.0" customHeight="true">
+      <c r="B136" t="s" s="5">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="137" ht="18.0" customHeight="true">
+      <c r="B137" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="138" ht="18.0" customHeight="true">
+      <c r="B138" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C126" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="D126" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F126" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G126" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="127" ht="18.0" customHeight="true">
-      <c r="B127" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="D127" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F127" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G127" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H127" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="130" ht="18.0" customHeight="true">
-      <c r="B130" t="s" s="5">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="131" ht="18.0" customHeight="true">
-      <c r="B131" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E131" s="3" t="s">
+      <c r="C138" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="F131" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G131" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="132" ht="18.0" customHeight="true">
-      <c r="B132" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F132" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G132" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="134" ht="18.0" customHeight="true">
-      <c r="A134" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="135" ht="18.0" customHeight="true">
-      <c r="A135" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D135" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E135" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F135" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="137" ht="18.0" customHeight="true">
-      <c r="B137" t="s" s="5">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="138" ht="18.0" customHeight="true">
-      <c r="B138" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F138" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G138" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="H138" s="3" t="s">
-        <v>314</v>
+      <c r="D138" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="139" ht="18.0" customHeight="true">
       <c r="B139" s="6" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E139" s="8" t="s">
         <v>323</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="140" ht="18.0" customHeight="true">
       <c r="B140" s="6" t="s">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E140" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="143" ht="18.0" customHeight="true">
+      <c r="B143" t="s" s="5">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="144" ht="18.0" customHeight="true">
+      <c r="B144" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="145" ht="18.0" customHeight="true">
+      <c r="B145" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="148" ht="18.0" customHeight="true">
+      <c r="B148" t="s" s="5">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="149" ht="18.0" customHeight="true">
+      <c r="B149" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="150" ht="18.0" customHeight="true">
+      <c r="B150" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="H150" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="152" ht="18.0" customHeight="true">
+      <c r="A152" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="153" ht="18.0" customHeight="true">
+      <c r="A153" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="155" ht="18.0" customHeight="true">
+      <c r="B155" t="s" s="5">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="156" ht="18.0" customHeight="true">
+      <c r="B156" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G156" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="F140" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G140" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="141" ht="18.0" customHeight="true">
-      <c r="B141" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="D141" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E141" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F141" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G141" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H141" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="144" ht="18.0" customHeight="true">
-      <c r="B144" t="s" s="5">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="145" ht="18.0" customHeight="true">
-      <c r="B145" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C145" s="3" t="s">
+      <c r="H156" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D145" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F145" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G145" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="146" ht="18.0" customHeight="true">
-      <c r="B146" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D146" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E146" s="8" t="s">
+    </row>
+    <row r="157" ht="18.0" customHeight="true">
+      <c r="B157" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C157" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="F146" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G146" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="149" ht="18.0" customHeight="true">
-      <c r="B149" t="s" s="5">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="150" ht="18.0" customHeight="true">
-      <c r="B150" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D150" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="E150" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G150" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H150" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="151" ht="18.0" customHeight="true">
-      <c r="B151" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C151" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D151" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E151" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="F151" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="G151" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="H151" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="153" ht="18.0" customHeight="true">
-      <c r="A153" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="154" ht="18.0" customHeight="true">
-      <c r="A154" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D154" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E154" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="F154" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="156" ht="18.0" customHeight="true">
-      <c r="B156" t="s" s="5">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="157" ht="18.0" customHeight="true">
-      <c r="B157" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D157" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E157" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="H157" s="3" t="s">
-        <v>314</v>
+      <c r="D157" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H157" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="158" ht="18.0" customHeight="true">
       <c r="B158" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="159" ht="18.0" customHeight="true">
       <c r="B159" s="6" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="160" ht="18.0" customHeight="true">
       <c r="B160" s="6" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E160" s="8" t="s">
         <v>323</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="161" ht="18.0" customHeight="true">
       <c r="B161" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="D161" s="8" t="s">
         <v>323</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>323</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H161" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="162" ht="18.0" customHeight="true">
       <c r="B162" s="6" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C162" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H162" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="165" ht="18.0" customHeight="true">
+      <c r="B165" t="s" s="5">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="166" ht="18.0" customHeight="true">
+      <c r="B166" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="167" ht="18.0" customHeight="true">
+      <c r="B167" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E167" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="D162" s="8" t="s">
+      <c r="F167" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G167" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="170" ht="18.0" customHeight="true">
+      <c r="B170" t="s" s="5">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="171" ht="18.0" customHeight="true">
+      <c r="B171" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="172" ht="18.0" customHeight="true">
+      <c r="B172" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="H172" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="174" ht="18.0" customHeight="true">
+      <c r="A174" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="175" ht="18.0" customHeight="true">
+      <c r="A175" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="177" ht="18.0" customHeight="true">
+      <c r="B177" t="s" s="5">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="178" ht="18.0" customHeight="true">
+      <c r="B178" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G178" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="E162" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F162" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G162" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="163" ht="18.0" customHeight="true">
-      <c r="B163" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C163" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="D163" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="E163" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F163" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G163" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H163" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="166" ht="18.0" customHeight="true">
-      <c r="B166" t="s" s="5">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="167" ht="18.0" customHeight="true">
-      <c r="B167" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C167" s="3" t="s">
+      <c r="H178" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D167" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E167" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F167" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="168" ht="18.0" customHeight="true">
-      <c r="B168" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C168" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D168" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E168" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="F168" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G168" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="171" ht="18.0" customHeight="true">
-      <c r="B171" t="s" s="5">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="172" ht="18.0" customHeight="true">
-      <c r="B172" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C172" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D172" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="E172" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F172" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H172" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="173" ht="18.0" customHeight="true">
-      <c r="B173" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C173" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D173" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E173" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="F173" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="G173" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="H173" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="175" ht="18.0" customHeight="true">
-      <c r="A175" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="176" ht="18.0" customHeight="true">
-      <c r="A176" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C176" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D176" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E176" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F176" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="178" ht="18.0" customHeight="true">
-      <c r="B178" t="s" s="5">
-        <v>317</v>
-      </c>
     </row>
     <row r="179" ht="18.0" customHeight="true">
-      <c r="B179" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C179" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D179" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E179" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F179" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G179" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="H179" s="3" t="s">
-        <v>314</v>
+      <c r="B179" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H179" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="180" ht="18.0" customHeight="true">
       <c r="B180" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F180" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="181" ht="18.0" customHeight="true">
       <c r="B181" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>361</v>
@@ -4202,227 +4190,227 @@
         <v>323</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F181" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="182" ht="18.0" customHeight="true">
       <c r="B182" s="6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>363</v>
+        <v>317</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E182" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F182" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="183" ht="18.0" customHeight="true">
       <c r="B183" s="6" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E183" s="8" t="s">
         <v>323</v>
       </c>
       <c r="F183" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="184" ht="18.0" customHeight="true">
       <c r="B184" s="6" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E184" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F184" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="185" ht="18.0" customHeight="true">
       <c r="B185" s="6" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F185" s="8" t="s">
         <v>323</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H185" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="186" ht="18.0" customHeight="true">
       <c r="B186" s="6" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E186" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F186" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="187" ht="18.0" customHeight="true">
-      <c r="B187" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C187" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="D187" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E187" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F187" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G187" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H187" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="189" ht="18.0" customHeight="true">
+      <c r="B189" t="s" s="5">
+        <v>326</v>
       </c>
     </row>
     <row r="190" ht="18.0" customHeight="true">
-      <c r="B190" t="s" s="5">
+      <c r="B190" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="191" ht="18.0" customHeight="true">
+      <c r="B191" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D191" s="6" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="191" ht="18.0" customHeight="true">
-      <c r="B191" s="3" t="s">
+      <c r="E191" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G191" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="194" ht="18.0" customHeight="true">
+      <c r="B194" t="s" s="5">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="195" ht="18.0" customHeight="true">
+      <c r="B195" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C191" s="3" t="s">
+      <c r="C195" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="H195" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D191" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F191" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G191" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="192" ht="18.0" customHeight="true">
-      <c r="B192" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C192" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D192" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E192" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="F192" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G192" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="195" ht="18.0" customHeight="true">
-      <c r="B195" t="s" s="5">
-        <v>333</v>
-      </c>
     </row>
     <row r="196" ht="18.0" customHeight="true">
-      <c r="B196" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C196" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F196" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G196" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H196" s="3" t="s">
-        <v>314</v>
+      <c r="B196" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E196" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F196" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="H196" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="197" ht="18.0" customHeight="true">
@@ -4430,45 +4418,22 @@
         <v>143</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H197" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="198" ht="18.0" customHeight="true">
-      <c r="B198" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C198" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D198" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E198" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="F198" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="G198" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="H198" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -4495,130 +4460,130 @@
     <dataValidation type="list" sqref="A25" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B44" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B43" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="D48" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="D49" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D50" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>lov_4!B1:B65000</formula1>
+    <dataValidation type="list" sqref="E48" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E49" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E50" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F48" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F49" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F50" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A52" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>null!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="B63" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>null!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="D68" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>lov_4!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E68" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A53" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F68" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="A71" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B64" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B84" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D69" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D89" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E69" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E89" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F69" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F89" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A72" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A92" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B85" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B102" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D90" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>lov_4!B1:B65000</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="E90" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="F90" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="A93" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A105" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B103" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>null!B1:B65000</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="A106" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B117" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="B118" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B119" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A121" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A122" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B131" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B132" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A134" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A135" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B145" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B146" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D150" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>lov_4!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E150" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="F150" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="A153" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D151" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B167" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>null!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="D172" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E151" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E172" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F151" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F172" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A154" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A175" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B168" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B191" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D173" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D196" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="E173" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="F173" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="A176" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>null!B1:B65000</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="B192" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>null!B1:B65000</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="D197" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D198" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>lov_4!B1:B65000</formula1>
+    <dataValidation type="list" sqref="E196" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E197" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E198" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F196" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F197" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="F198" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4635,18 +4600,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -4885,7 +4850,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5149,12 +5114,12 @@
         <v>101</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>102</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>3</v>
@@ -5162,7 +5127,7 @@
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>3</v>
@@ -5170,7 +5135,7 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>3</v>
@@ -5178,7 +5143,7 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>3</v>
@@ -5186,10 +5151,10 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>107</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -5262,14 +5227,6 @@
       </c>
       <c r="B47" s="8" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -5285,74 +5242,74 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -5368,82 +5325,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -5459,10 +5416,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -5478,546 +5435,546 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -6033,10 +5990,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
@@ -28,7 +28,7 @@
   <commentList>
     <comment ref="A5" authorId="0">
       <text>
-        <t>ObjectID:A36A1254-AE7F-DE6B-D3EA-4134EF11F842;
+        <t>ObjectID:BE59DDEB-2961-4197-F76F-B817E05B3D4B;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
@@ -39,462 +39,504 @@
     </comment>
     <comment ref="B4" authorId="0">
       <text>
-        <t>ModelID:D5E686F9-8C50-711F-E9FC-D7BCAE5F50E6</t>
+        <t>ModelID:89F2C501-11B9-3D7E-8A22-96BE05DB5817</t>
       </text>
     </comment>
     <comment ref="B9" authorId="0">
       <text>
-        <t>ObjectID:A916ECC8-AD4E-F75D-4B55-4750502B16AD;
+        <t>ObjectID:615315FD-EF83-FB7A-8AB8-292D4194FF1E;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B10" authorId="0">
       <text>
-        <t>ObjectID:D585E8D8-09E1-036F-B2D0-15DEA3752A33;
+        <t>ObjectID:21EC97DF-1E1A-CDF6-7F7F-FDB04E287767;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B11" authorId="0">
       <text>
-        <t>ObjectID:2E39AF8F-4248-0D6B-7642-8F6C678F8CCF;
+        <t>ObjectID:AE5BD9F2-6313-D432-2674-B8E52865A6A2;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B12" authorId="0">
       <text>
-        <t>ObjectID:5A5CBCC1-0A75-CEEC-7E2C-EB15B5BEB145;
+        <t>ObjectID:754472F2-BBC9-01D7-3065-91FA7F418345;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B17" authorId="0">
       <text>
-        <t>ObjectID:0720CDBE-0745-D3C8-56BA-AF523EF21883;
+        <t>ObjectID:E458BDEB-C8FF-7F66-7A7F-E99EE778EAC1;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="B22" authorId="0">
       <text>
-        <t>ObjectID:47CC5308-1543-1767-8C4A-ADE5B8F77AEA;
+        <t>ObjectID:3F4F74A7-9382-56B2-EC84-398C37AC9069;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="A25" authorId="0">
       <text>
-        <t>ObjectID:4E6262BE-0941-E243-DDDC-B76DFC8DEF7C;
+        <t>ObjectID:B74D2B92-6181-52A3-6451-55154CCCB449;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0">
       <text>
-        <t>ObjectID:C4823130-73FD-764F-51BD-0BABB447DB30;
+        <t>ObjectID:93C10ECE-2B0C-AF90-6BE3-86A5C9D53868;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0">
       <text>
-        <t>ObjectID:901DD0A6-1758-7B29-E145-5606A3D447A2;
+        <t>ObjectID:254BED24-3145-3387-0719-E1E478CEFE92;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0">
       <text>
-        <t>ObjectID:F2D76C45-6AD5-8A29-78D5-87EB84455F4C;
+        <t>ObjectID:463F92FB-D068-8187-1339-4D542C0FB293;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B32" authorId="0">
       <text>
-        <t>ObjectID:1F2CCE1B-18BF-72B4-59D7-1F0E477BBEA8;
+        <t>ObjectID:A5BF70AC-2700-6399-33A6-EED3E3631787;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B33" authorId="0">
       <text>
-        <t>ObjectID:A1904782-464A-5DD2-6809-97C453F6BFB5;
+        <t>ObjectID:6B18BD86-D78A-DFF3-2B29-D099B857B7F1;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0">
       <text>
-        <t>ObjectID:9C1339C5-6B66-FF56-0DF9-70CEA9914EE0;
+        <t>ObjectID:054DEEF8-1367-3A10-59DB-33C41E40E516;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0">
       <text>
-        <t>ObjectID:7C8C090A-510B-18C1-B99E-1A436DF05CE6;
+        <t>ObjectID:99C39193-C45C-BEDD-E898-36AD07AFBD6D;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B36" authorId="0">
       <text>
-        <t>ObjectID:84B350A2-E9F9-85B7-82B4-BB09E44FACDE;
+        <t>ObjectID:BE6CCBA7-246F-F003-6181-E48CD286D01F;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B37" authorId="0">
       <text>
-        <t>ObjectID:33E979A1-6E80-51D0-D0EB-DB2F8C0A44B6;
+        <t>ObjectID:42273DB2-D04F-3BFE-39EE-567370D65DE6;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0">
       <text>
-        <t>ObjectID:7FA5E6A9-9A61-5313-E18B-87C24201D6EE;
+        <t>ObjectID:33C1567D-0A91-FC62-7EEC-128359F701D7;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0">
       <text>
-        <t>ObjectID:F31A8785-1566-8B79-1912-4802899ECAFD;
+        <t>ObjectID:CFE5693B-1EF3-B65F-414A-14B1577BB8EC;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="B48" authorId="0">
       <text>
-        <t>ObjectID:5AC0DBA5-98DC-16BD-67F0-8C7D65E7464D;
+        <t>ObjectID:5E5996B1-0261-3FA0-89AF-68ED840980E4;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="B49" authorId="0">
       <text>
-        <t>ObjectID:5DC850B4-B7D2-DE05-EED0-5AE8208A555B;
+        <t>ObjectID:AF7482BA-CE15-D252-8566-F3A51B3B7781;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="A52" authorId="0">
       <text>
-        <t>ObjectID:B8A5A6AB-2C80-7160-F587-FEB1D73E4E23;
+        <t>ObjectID:39E5C551-B715-AEA6-BCD1-F132800F4B52;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B56" authorId="0">
       <text>
-        <t>ObjectID:86432DD4-A51F-0F1A-801B-E081457493D2;
+        <t>ObjectID:430DE1EB-E953-1D52-F887-98986AD97B5C;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B57" authorId="0">
       <text>
-        <t>ObjectID:6D3F8C10-15CC-9855-E924-64034831049A;
+        <t>ObjectID:A8C99DEF-8D99-DCC7-4218-5AF2D7CE0460;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B58" authorId="0">
       <text>
-        <t>ObjectID:C244A13E-4EC5-7FE2-F02C-F3A05700E232;
+        <t>ObjectID:CF0EC2C2-1664-01B7-89AD-3E320E5A3B23;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B63" authorId="0">
       <text>
-        <t>ObjectID:9448563C-C682-6E0F-0396-00EC03FF551D;
+        <t>ObjectID:3A1D1823-99E0-5D7E-21DB-FB4A2411277F;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="B68" authorId="0">
       <text>
-        <t>ObjectID:8E87AA14-C0E3-100D-3FFA-36B5F9A38D60;
+        <t>ObjectID:6220D5A5-C299-AF56-E6BD-6F33CE588850;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="A71" authorId="0">
       <text>
-        <t>ObjectID:ECD94709-BBE0-91B5-6EFC-7283F3196C54;
+        <t>ObjectID:9412012D-8F5A-24C5-FC14-BFDE03A3834F;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B75" authorId="0">
       <text>
-        <t>ObjectID:B068C7BF-D6C8-8135-54F3-DDC2CF1E801B;
+        <t>ObjectID:3CD305C0-A8EE-C2AB-B4A0-FFD67093C959;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B76" authorId="0">
       <text>
-        <t>ObjectID:25520CDC-89E3-3BB2-6C44-D60D793C0FA6;
+        <t>ObjectID:E86052E6-5F17-C60F-FE23-09BFEC8ABC52;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B77" authorId="0">
       <text>
-        <t>ObjectID:AADA8B95-96A5-9B24-D7F4-7F015851EFF7;
+        <t>ObjectID:1B2AF109-5895-6C1E-40FB-4B222ADF5375;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B78" authorId="0">
       <text>
-        <t>ObjectID:94A37B47-9D6B-94F0-9194-957D5671222E;
+        <t>ObjectID:3A991CE4-51C1-A587-3F7B-FEB51550FC5E;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B79" authorId="0">
       <text>
-        <t>ObjectID:BD0F476A-18A9-713C-FBDC-49A23226251A;
+        <t>ObjectID:1F7E614D-DB93-2852-2D76-3FD8A77404B7;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B84" authorId="0">
       <text>
-        <t>ObjectID:8E294E81-0842-B977-DF00-91D5568B7812;
+        <t>ObjectID:69550BDE-7C21-2319-A0DC-41ABCB0DCCC8;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="B89" authorId="0">
       <text>
-        <t>ObjectID:FFA23F90-E801-A2D4-E9AC-BE2D4531FC43;
+        <t>ObjectID:1A7A46B4-A5BB-9963-38A7-0CA953FBC311;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="A92" authorId="0">
       <text>
-        <t>ObjectID:D05B5757-4762-17E8-B189-F7DC6C717D4E;
+        <t>ObjectID:2CC2FB13-8CA5-0A26-69E9-27224FF28239;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B96" authorId="0">
       <text>
-        <t>ObjectID:DC9AB24C-5C4B-1DFF-39C9-3BAEF6CA017E;
+        <t>ObjectID:B3B466F2-0B6F-1CB1-8F58-3A114F8C63BA;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B97" authorId="0">
       <text>
-        <t>ObjectID:E7804AD4-C5ED-A377-4A90-C1371CBB955D;
+        <t>ObjectID:6A543D3E-CDB2-0B84-4129-647EEE7510CB;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B102" authorId="0">
       <text>
-        <t>ObjectID:6CB0705F-75C2-8815-A321-6BFA5FAAD288;
+        <t>ObjectID:2AC03C25-3831-5BC3-81A3-643523A60A9F;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="A105" authorId="0">
       <text>
-        <t>ObjectID:EE087F47-DD00-CF9F-8B94-45B6F08D990F;
+        <t>ObjectID:73687451-F72D-7430-24BC-625E4A733080;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B109" authorId="0">
       <text>
-        <t>ObjectID:0A105682-F262-699F-9D1F-B2F7A92E0ADB;
+        <t>ObjectID:CA915E21-200D-7184-1521-198020501E55;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B110" authorId="0">
       <text>
-        <t>ObjectID:345BBC95-8061-A492-629E-89A2027EDFED;
+        <t>ObjectID:9F5DB5DB-6466-A0C5-B055-4281B4AC4172;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B111" authorId="0">
       <text>
-        <t>ObjectID:F04CE297-E165-2863-6399-6445729722B5;
+        <t>ObjectID:6B0A2361-5661-B3DF-7493-049F85F7F980;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B112" authorId="0">
       <text>
-        <t>ObjectID:7C86E4ED-7D02-8E89-3A74-2026A356808F;
+        <t>ObjectID:9C6621B9-EF9D-CE31-14F3-F45EBABD4942;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B117" authorId="0">
       <text>
-        <t>ObjectID:05CADB4C-D83F-8791-DD94-9FBFE95D096B;
+        <t>ObjectID:90B82748-D561-5445-43F3-104EBD560BB6;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="B118" authorId="0">
       <text>
-        <t>ObjectID:79E96C4E-1C5C-543C-C318-7D832E4B5819;
+        <t>ObjectID:F54F86BF-EDFF-D302-50C8-14B2D5BAB8D4;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="A121" authorId="0">
       <text>
-        <t>ObjectID:B4785CBF-D492-D2F4-33C2-78823D081196;
+        <t>ObjectID:0D580267-E860-C399-6E61-F0538E07B0F8;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B125" authorId="0">
       <text>
-        <t>ObjectID:C02128BD-9BE9-8E01-3E5E-62EFA28C591A;
+        <t>ObjectID:017D57CC-645E-4920-15EC-1C9568C9FECE;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B126" authorId="0">
       <text>
-        <t>ObjectID:E6A67916-6F07-F598-52A0-5C1E5643F34D;
+        <t>ObjectID:35C45BEA-A44B-281F-776D-E686DB9F29F2;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B131" authorId="0">
       <text>
-        <t>ObjectID:89CBDD51-BB44-850F-A47D-3D8533C3CD85;
+        <t>ObjectID:43EF62E2-4F84-8F8D-0A1E-26C238D03A72;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="A134" authorId="0">
       <text>
-        <t>ObjectID:F3F4FA94-F84B-402E-6080-E86D2042628B;
+        <t>ObjectID:B2D4B9D3-A8A1-261C-3323-1BFE69DC4D39;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B138" authorId="0">
       <text>
-        <t>ObjectID:1662C822-6030-377B-C88E-D7FDE3DBD485;
+        <t>ObjectID:F0C8DEED-9306-5A61-4CBA-8C61E7C2ED73;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B139" authorId="0">
       <text>
-        <t>ObjectID:37AFA439-59F7-1168-D545-69590D41617C;
+        <t>ObjectID:8BF22F09-ED2B-9FE3-634A-FC4550738ADC;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B140" authorId="0">
       <text>
-        <t>ObjectID:80EA0F28-60B7-4A8F-7254-364B8BD0CC49;
+        <t>ObjectID:4B515041-ACD9-99C4-27B9-C147D82A08C4;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B145" authorId="0">
-      <text>
-        <t>ObjectID:B58ED608-D363-3FBA-D4FB-C8488BA89B82;
+    <comment ref="B141" authorId="0">
+      <text>
+        <t>ObjectID:B5DB67C7-D8D1-CB96-DB06-62643CBAD3F7;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B146" authorId="0">
+      <text>
+        <t>ObjectID:BB006E51-FB85-8346-6CC6-15335EC5A711;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B150" authorId="0">
-      <text>
-        <t>ObjectID:919AA2F5-AF80-5051-B6F9-538494FE7BAC;
+    <comment ref="B147" authorId="0">
+      <text>
+        <t>ObjectID:BA848D2E-5838-25CA-B963-D9B7AFD79E9E;
+Class:oracle.dbtools.crest.model.design.relational.Index</t>
+      </text>
+    </comment>
+    <comment ref="A150" authorId="0">
+      <text>
+        <t>ObjectID:E11C7B03-BD57-3A45-7BBD-3F6A277CCBB9;
+Class:oracle.dbtools.crest.model.design.relational.Table</t>
+      </text>
+    </comment>
+    <comment ref="B154" authorId="0">
+      <text>
+        <t>ObjectID:6D1A3FA8-F979-56CA-F333-DE584D71E9D8;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B155" authorId="0">
+      <text>
+        <t>ObjectID:6D73AB1A-5354-2711-3B37-A68B8A099079;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B156" authorId="0">
+      <text>
+        <t>ObjectID:BC77D151-BC65-88EA-7671-5C9A0DAB542F;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B161" authorId="0">
+      <text>
+        <t>ObjectID:083497A0-D703-EC31-71B6-AA15F2192845;
+Class:oracle.dbtools.crest.model.design.relational.Index</t>
+      </text>
+    </comment>
+    <comment ref="B166" authorId="0">
+      <text>
+        <t>ObjectID:3F8B3718-EC6C-1C37-DEBA-A1745C212A91;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="A153" authorId="0">
-      <text>
-        <t>ObjectID:8827044B-4A9A-3231-00AE-A01022AC9207;
+    <comment ref="A169" authorId="0">
+      <text>
+        <t>ObjectID:220C4288-9B1F-3E10-2C33-BDFCB9DCFD4D;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B157" authorId="0">
-      <text>
-        <t>ObjectID:0066ECFA-6810-AAC0-BE37-A2A6A7971D22;
+    <comment ref="B173" authorId="0">
+      <text>
+        <t>ObjectID:57CAB14E-29C7-5D92-C7C0-6C6D7D014685;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B158" authorId="0">
-      <text>
-        <t>ObjectID:F6B4833B-B9F0-C041-42C8-2A06E11033D2;
+    <comment ref="B174" authorId="0">
+      <text>
+        <t>ObjectID:49039BFA-516D-0985-5B04-3EEEA8A700E2;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B159" authorId="0">
-      <text>
-        <t>ObjectID:9D2F8BAD-E6E3-B34E-6E99-D3AD8ADC16BE;
+    <comment ref="B175" authorId="0">
+      <text>
+        <t>ObjectID:5B69787F-90B9-14E0-8DEE-4012406206B4;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B160" authorId="0">
-      <text>
-        <t>ObjectID:8795FAAF-3165-81A8-FF96-DC0C48E69B9E;
+    <comment ref="B176" authorId="0">
+      <text>
+        <t>ObjectID:15F769F5-49F6-CC43-71C2-FF704C638C1A;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B161" authorId="0">
-      <text>
-        <t>ObjectID:4A79AC62-C425-C8C1-3A70-B42E1BAEE9D5;
+    <comment ref="B177" authorId="0">
+      <text>
+        <t>ObjectID:80BC2183-0748-53E4-0D5F-6BB3362DE3C7;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B162" authorId="0">
-      <text>
-        <t>ObjectID:C4C71948-2C7D-6B64-4FB9-2589057DABB5;
+    <comment ref="B178" authorId="0">
+      <text>
+        <t>ObjectID:7AB70A62-442D-8F1D-2832-B0B51B9FA5AB;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B167" authorId="0">
-      <text>
-        <t>ObjectID:E425749D-D18D-D192-E4D8-326F4435D4F2;
+    <comment ref="B183" authorId="0">
+      <text>
+        <t>ObjectID:0C93F24B-8280-1374-5824-C859E64ECFFF;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B172" authorId="0">
-      <text>
-        <t>ObjectID:AB9E84E2-5500-6E2C-67D3-DF1370708BDF;
+    <comment ref="B188" authorId="0">
+      <text>
+        <t>ObjectID:6EBE25FD-4D8B-2C25-313E-A046D9B28639;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="A175" authorId="0">
-      <text>
-        <t>ObjectID:CB285AEA-5E99-A1B2-D71F-63C2A1502E59;
+    <comment ref="A191" authorId="0">
+      <text>
+        <t>ObjectID:D7FF44B5-3811-43B7-CF6B-4CB3BCC73E65;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B179" authorId="0">
-      <text>
-        <t>ObjectID:01F22734-10A7-3051-FC8E-C5193520622D;
+    <comment ref="B195" authorId="0">
+      <text>
+        <t>ObjectID:E59B3F94-CF0E-64D3-034F-9ACA353FA5C6;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B180" authorId="0">
-      <text>
-        <t>ObjectID:0D39920E-AC44-F378-CFA1-8A48D7B43D34;
+    <comment ref="B196" authorId="0">
+      <text>
+        <t>ObjectID:34C50EB1-A41D-562B-AD3E-04DF31085334;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B181" authorId="0">
-      <text>
-        <t>ObjectID:D32BC5DD-CA21-E925-6A96-0ECEF775B517;
+    <comment ref="B197" authorId="0">
+      <text>
+        <t>ObjectID:A3BA4F71-0148-03F6-E94E-FB5C7863E9E4;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B182" authorId="0">
-      <text>
-        <t>ObjectID:B7A72C42-C555-1D3D-3E90-655FB8E2CE88;
+    <comment ref="B198" authorId="0">
+      <text>
+        <t>ObjectID:CAD5F08D-6F7F-988F-F7C0-DBB9B261CDEB;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B183" authorId="0">
-      <text>
-        <t>ObjectID:B28DB384-F898-21CF-4DE4-34CDFB1673F1;
+    <comment ref="B199" authorId="0">
+      <text>
+        <t>ObjectID:DD80B398-AB70-2FFF-85B7-96A17D879E8C;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B184" authorId="0">
-      <text>
-        <t>ObjectID:C410357A-98CA-84CD-8815-B3C25556F333;
+    <comment ref="B200" authorId="0">
+      <text>
+        <t>ObjectID:F40997A8-17B5-799B-4070-02102A0B1F75;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B185" authorId="0">
-      <text>
-        <t>ObjectID:898749AB-398D-26C3-3C4F-A88AFD9ACDF6;
+    <comment ref="B201" authorId="0">
+      <text>
+        <t>ObjectID:97AA6B84-A02A-2D10-04F0-441D367ADC7B;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B186" authorId="0">
-      <text>
-        <t>ObjectID:340579EC-8B22-1285-4D53-F5C3ECCFC0F3;
+    <comment ref="B202" authorId="0">
+      <text>
+        <t>ObjectID:0C020521-4649-1A28-58F6-CE7EAD4ECC6F;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B191" authorId="0">
-      <text>
-        <t>ObjectID:5CC83417-CD6D-1C2E-C695-8664F8B61C41;
+    <comment ref="B207" authorId="0">
+      <text>
+        <t>ObjectID:9181BB6D-9394-4C19-96F6-57EAB5AF9AC7;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B196" authorId="0">
-      <text>
-        <t>ObjectID:AA6605AF-93AE-856D-9F64-C0175D1DF2C6;
+    <comment ref="B212" authorId="0">
+      <text>
+        <t>ObjectID:C2093F02-E1DB-0F94-5C0F-3476052B2A0F;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="B197" authorId="0">
-      <text>
-        <t>ObjectID:74D8B263-9FF2-4C7D-6BA9-935B0A7F0914;
+    <comment ref="B213" authorId="0">
+      <text>
+        <t>ObjectID:FAB492A5-BE61-A93F-DBCC-ED412D0B3C9B;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
@@ -503,7 +545,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="378">
   <si>
     <t>Diccionario de datos BD</t>
   </si>
@@ -583,424 +625,460 @@
     <t>generateInDDL</t>
   </si>
   <si>
-    <t>A36A1254-AE7F-DE6B-D3EA-4134EF11F842</t>
+    <t>BE59DDEB-2961-4197-F76F-B817E05B3D4B</t>
   </si>
   <si>
     <t>Address</t>
   </si>
   <si>
-    <t>4E6262BE-0941-E243-DDDC-B76DFC8DEF7C</t>
+    <t>B74D2B92-6181-52A3-6451-55154CCCB449</t>
   </si>
   <si>
     <t>AppUser</t>
   </si>
   <si>
-    <t>B8A5A6AB-2C80-7160-F587-FEB1D73E4E23</t>
+    <t>39E5C551-B715-AEA6-BCD1-F132800F4B52</t>
   </si>
   <si>
     <t>Comuna</t>
   </si>
   <si>
-    <t>ECD94709-BBE0-91B5-6EFC-7283F3196C54</t>
+    <t>9412012D-8F5A-24C5-FC14-BFDE03A3834F</t>
   </si>
   <si>
     <t>Contract</t>
   </si>
   <si>
-    <t>D05B5757-4762-17E8-B189-F7DC6C717D4E</t>
+    <t>2CC2FB13-8CA5-0A26-69E9-27224FF28239</t>
   </si>
   <si>
     <t>Country</t>
   </si>
   <si>
-    <t>EE087F47-DD00-CF9F-8B94-45B6F08D990F</t>
+    <t>73687451-F72D-7430-24BC-625E4A733080</t>
   </si>
   <si>
     <t>Device</t>
   </si>
   <si>
-    <t>B4785CBF-D492-D2F4-33C2-78823D081196</t>
+    <t>0D580267-E860-C399-6E61-F0538E07B0F8</t>
   </si>
   <si>
     <t>ElectricityCompany</t>
   </si>
   <si>
-    <t>F3F4FA94-F84B-402E-6080-E86D2042628B</t>
+    <t>B2D4B9D3-A8A1-261C-3323-1BFE69DC4D39</t>
+  </si>
+  <si>
+    <t>PassRecoverRequest</t>
+  </si>
+  <si>
+    <t>E11C7B03-BD57-3A45-7BBD-3F6A277CCBB9</t>
   </si>
   <si>
     <t>Region</t>
   </si>
   <si>
-    <t>8827044B-4A9A-3231-00AE-A01022AC9207</t>
+    <t>220C4288-9B1F-3E10-2C33-BDFCB9DCFD4D</t>
   </si>
   <si>
     <t>Result</t>
   </si>
   <si>
-    <t>CB285AEA-5E99-A1B2-D71F-63C2A1502E59</t>
+    <t>D7FF44B5-3811-43B7-CF6B-4CB3BCC73E65</t>
   </si>
   <si>
     <t>UserDevice</t>
   </si>
   <si>
-    <t>01F22734-10A7-3051-FC8E-C5193520622D</t>
+    <t>E59B3F94-CF0E-64D3-034F-9ACA353FA5C6</t>
   </si>
   <si>
     <t>alias</t>
   </si>
   <si>
-    <t>0066ECFA-6810-AAC0-BE37-A2A6A7971D22</t>
+    <t>57CAB14E-29C7-5D92-C7C0-6C6D7D014685</t>
   </si>
   <si>
     <t>ampere</t>
   </si>
   <si>
-    <t>C4823130-73FD-764F-51BD-0BABB447DB30</t>
+    <t>93C10ECE-2B0C-AF90-6BE3-86A5C9D53868</t>
   </si>
   <si>
     <t>countryCode</t>
   </si>
   <si>
-    <t>0D39920E-AC44-F378-CFA1-8A48D7B43D34</t>
+    <t>34C50EB1-A41D-562B-AD3E-04DF31085334</t>
   </si>
   <si>
     <t>creationDate</t>
   </si>
   <si>
-    <t>F6B4833B-B9F0-C041-42C8-2A06E11033D2</t>
+    <t>49039BFA-516D-0985-5B04-3EEEA8A700E2</t>
   </si>
   <si>
     <t>date</t>
   </si>
   <si>
-    <t>D32BC5DD-CA21-E925-6A96-0ECEF775B517</t>
+    <t>A3BA4F71-0148-03F6-E94E-FB5C7863E9E4</t>
   </si>
   <si>
     <t>description</t>
   </si>
   <si>
-    <t>B068C7BF-D6C8-8135-54F3-DDC2CF1E801B</t>
+    <t>3CD305C0-A8EE-C2AB-B4A0-FFD67093C959</t>
   </si>
   <si>
     <t>electricityCost</t>
   </si>
   <si>
-    <t>901DD0A6-1758-7B29-E145-5606A3D447A2</t>
+    <t>254BED24-3145-3387-0719-E1E478CEFE92</t>
   </si>
   <si>
     <t>email</t>
   </si>
   <si>
-    <t>F2D76C45-6AD5-8A29-78D5-87EB84455F4C</t>
+    <t>F0C8DEED-9306-5A61-4CBA-8C61E7C2ED73</t>
+  </si>
+  <si>
+    <t>8BF22F09-ED2B-9FE3-634A-FC4550738ADC</t>
+  </si>
+  <si>
+    <t>expireDateTime</t>
+  </si>
+  <si>
+    <t>463F92FB-D068-8187-1339-4D542C0FB293</t>
   </si>
   <si>
     <t>firstName</t>
   </si>
   <si>
-    <t>1F2CCE1B-18BF-72B4-59D7-1F0E477BBEA8</t>
+    <t>615315FD-EF83-FB7A-8AB8-292D4194FF1E</t>
   </si>
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>9D2F8BAD-E6E3-B34E-6E99-D3AD8ADC16BE</t>
-  </si>
-  <si>
-    <t>A916ECC8-AD4E-F75D-4B55-4750502B16AD</t>
-  </si>
-  <si>
-    <t>C02128BD-9BE9-8E01-3E5E-62EFA28C591A</t>
-  </si>
-  <si>
-    <t>86432DD4-A51F-0F1A-801B-E081457493D2</t>
-  </si>
-  <si>
-    <t>B7A72C42-C555-1D3D-3E90-655FB8E2CE88</t>
-  </si>
-  <si>
-    <t>DC9AB24C-5C4B-1DFF-39C9-3BAEF6CA017E</t>
-  </si>
-  <si>
-    <t>25520CDC-89E3-3BB2-6C44-D60D793C0FA6</t>
-  </si>
-  <si>
-    <t>0A105682-F262-699F-9D1F-B2F7A92E0ADB</t>
-  </si>
-  <si>
-    <t>1662C822-6030-377B-C88E-D7FDE3DBD485</t>
-  </si>
-  <si>
-    <t>A1904782-464A-5DD2-6809-97C453F6BFB5</t>
+    <t>430DE1EB-E953-1D52-F887-98986AD97B5C</t>
+  </si>
+  <si>
+    <t>E86052E6-5F17-C60F-FE23-09BFEC8ABC52</t>
+  </si>
+  <si>
+    <t>B3B466F2-0B6F-1CB1-8F58-3A114F8C63BA</t>
+  </si>
+  <si>
+    <t>CA915E21-200D-7184-1521-198020501E55</t>
+  </si>
+  <si>
+    <t>017D57CC-645E-4920-15EC-1C9568C9FECE</t>
+  </si>
+  <si>
+    <t>4B515041-ACD9-99C4-27B9-C147D82A08C4</t>
+  </si>
+  <si>
+    <t>5B69787F-90B9-14E0-8DEE-4012406206B4</t>
+  </si>
+  <si>
+    <t>A5BF70AC-2700-6399-33A6-EED3E3631787</t>
+  </si>
+  <si>
+    <t>CAD5F08D-6F7F-988F-F7C0-DBB9B261CDEB</t>
+  </si>
+  <si>
+    <t>6D1A3FA8-F979-56CA-F333-DE584D71E9D8</t>
+  </si>
+  <si>
+    <t>6B18BD86-D78A-DFF3-2B29-D099B857B7F1</t>
   </si>
   <si>
     <t>idAddress</t>
   </si>
   <si>
-    <t>D585E8D8-09E1-036F-B2D0-15DEA3752A33</t>
+    <t>21EC97DF-1E1A-CDF6-7F7F-FDB04E287767</t>
   </si>
   <si>
     <t>idComuna</t>
   </si>
   <si>
-    <t>9C1339C5-6B66-FF56-0DF9-70CEA9914EE0</t>
+    <t>054DEEF8-1367-3A10-59DB-33C41E40E516</t>
   </si>
   <si>
     <t>idContract</t>
   </si>
   <si>
-    <t>37AFA439-59F7-1168-D545-69590D41617C</t>
+    <t>6D73AB1A-5354-2711-3B37-A68B8A099079</t>
   </si>
   <si>
     <t>idCountry</t>
   </si>
   <si>
-    <t>B28DB384-F898-21CF-4DE4-34CDFB1673F1</t>
+    <t>DD80B398-AB70-2FFF-85B7-96A17D879E8C</t>
   </si>
   <si>
     <t>idDevice</t>
   </si>
   <si>
-    <t>AADA8B95-96A5-9B24-D7F4-7F015851EFF7</t>
+    <t>1B2AF109-5895-6C1E-40FB-4B222ADF5375</t>
   </si>
   <si>
     <t>idElectricityCompany</t>
   </si>
   <si>
-    <t>6D3F8C10-15CC-9855-E924-64034831049A</t>
+    <t>A8C99DEF-8D99-DCC7-4218-5AF2D7CE0460</t>
   </si>
   <si>
     <t>idRegion</t>
   </si>
   <si>
-    <t>C410357A-98CA-84CD-8815-B3C25556F333</t>
+    <t>F40997A8-17B5-799B-4070-02102A0B1F75</t>
   </si>
   <si>
     <t>idUser</t>
   </si>
   <si>
-    <t>8795FAAF-3165-81A8-FF96-DC0C48E69B9E</t>
+    <t>15F769F5-49F6-CC43-71C2-FF704C638C1A</t>
   </si>
   <si>
     <t>idUserDevice</t>
   </si>
   <si>
-    <t>4A79AC62-C425-C8C1-3A70-B42E1BAEE9D5</t>
+    <t>80BC2183-0748-53E4-0D5F-6BB3362DE3C7</t>
   </si>
   <si>
     <t>kwh</t>
   </si>
   <si>
-    <t>898749AB-398D-26C3-3C4F-A88AFD9ACDF6</t>
+    <t>97AA6B84-A02A-2D10-04F0-441D367ADC7B</t>
   </si>
   <si>
     <t>lastConection</t>
   </si>
   <si>
-    <t>7C8C090A-510B-18C1-B99E-1A436DF05CE6</t>
+    <t>99C39193-C45C-BEDD-E898-36AD07AFBD6D</t>
   </si>
   <si>
     <t>lastName</t>
   </si>
   <si>
-    <t>345BBC95-8061-A492-629E-89A2027EDFED</t>
+    <t>9F5DB5DB-6466-A0C5-B055-4281B4AC4172</t>
   </si>
   <si>
     <t>model</t>
   </si>
   <si>
-    <t>E6A67916-6F07-F598-52A0-5C1E5643F34D</t>
-  </si>
-  <si>
-    <t>C244A13E-4EC5-7FE2-F02C-F3A05700E232</t>
-  </si>
-  <si>
-    <t>E7804AD4-C5ED-A377-4A90-C1371CBB955D</t>
-  </si>
-  <si>
-    <t>F04CE297-E165-2863-6399-6445729722B5</t>
-  </si>
-  <si>
-    <t>80EA0F28-60B7-4A8F-7254-364B8BD0CC49</t>
-  </si>
-  <si>
-    <t>84B350A2-E9F9-85B7-82B4-BB09E44FACDE</t>
+    <t>CF0EC2C2-1664-01B7-89AD-3E320E5A3B23</t>
+  </si>
+  <si>
+    <t>6A543D3E-CDB2-0B84-4129-647EEE7510CB</t>
+  </si>
+  <si>
+    <t>6B0A2361-5661-B3DF-7493-049F85F7F980</t>
+  </si>
+  <si>
+    <t>35C45BEA-A44B-281F-776D-E686DB9F29F2</t>
+  </si>
+  <si>
+    <t>BC77D151-BC65-88EA-7671-5C9A0DAB542F</t>
+  </si>
+  <si>
+    <t>BE6CCBA7-246F-F003-6181-E48CD286D01F</t>
   </si>
   <si>
     <t>numberPhone</t>
   </si>
   <si>
-    <t>33E979A1-6E80-51D0-D0EB-DB2F8C0A44B6</t>
+    <t>42273DB2-D04F-3BFE-39EE-567370D65DE6</t>
   </si>
   <si>
     <t>password</t>
   </si>
   <si>
-    <t>C4C71948-2C7D-6B64-4FB9-2589057DABB5</t>
+    <t>7AB70A62-442D-8F1D-2832-B0B51B9FA5AB</t>
   </si>
   <si>
     <t>power</t>
   </si>
   <si>
-    <t>7FA5E6A9-9A61-5313-E18B-87C24201D6EE</t>
+    <t>B5DB67C7-D8D1-CB96-DB06-62643CBAD3F7</t>
+  </si>
+  <si>
+    <t>request</t>
+  </si>
+  <si>
+    <t>33C1567D-0A91-FC62-7EEC-128359F701D7</t>
   </si>
   <si>
     <t>secondLastName</t>
   </si>
   <si>
-    <t>7C86E4ED-7D02-8E89-3A74-2026A356808F</t>
+    <t>9C6621B9-EF9D-CE31-14F3-F45EBABD4942</t>
   </si>
   <si>
     <t>serialNumber</t>
   </si>
   <si>
-    <t>94A37B47-9D6B-94F0-9194-957D5671222E</t>
+    <t>3A991CE4-51C1-A587-3F7B-FEB51550FC5E</t>
   </si>
   <si>
     <t>serviceAdminCost</t>
   </si>
   <si>
-    <t>340579EC-8B22-1285-4D53-F5C3ECCFC0F3</t>
+    <t>0C020521-4649-1A28-58F6-CE7EAD4ECC6F</t>
   </si>
   <si>
     <t>status</t>
   </si>
   <si>
-    <t>2E39AF8F-4248-0D6B-7642-8F6C678F8CCF</t>
+    <t>AE5BD9F2-6313-D432-2674-B8E52865A6A2</t>
   </si>
   <si>
     <t>streetName</t>
   </si>
   <si>
-    <t>5A5CBCC1-0A75-CEEC-7E2C-EB15B5BEB145</t>
+    <t>754472F2-BBC9-01D7-3065-91FA7F418345</t>
   </si>
   <si>
     <t>streetNumber</t>
   </si>
   <si>
-    <t>BD0F476A-18A9-713C-FBDC-49A23226251A</t>
+    <t>1F7E614D-DB93-2852-2D76-3FD8A77404B7</t>
   </si>
   <si>
     <t>transportCost</t>
   </si>
   <si>
-    <t>47CC5308-1543-1767-8C4A-ADE5B8F77AEA</t>
+    <t>3F4F74A7-9382-56B2-EC84-398C37AC9069</t>
   </si>
   <si>
     <t>Address_Comuna_FK</t>
   </si>
   <si>
-    <t>5AC0DBA5-98DC-16BD-67F0-8C7D65E7464D</t>
+    <t>5E5996B1-0261-3FA0-89AF-68ED840980E4</t>
   </si>
   <si>
     <t>AppUser_Address_FK</t>
   </si>
   <si>
-    <t>5DC850B4-B7D2-DE05-EED0-5AE8208A555B</t>
+    <t>AF7482BA-CE15-D252-8566-F3A51B3B7781</t>
   </si>
   <si>
     <t>AppUser_Contract_FK</t>
   </si>
   <si>
-    <t>8E87AA14-C0E3-100D-3FFA-36B5F9A38D60</t>
+    <t>6220D5A5-C299-AF56-E6BD-6F33CE588850</t>
   </si>
   <si>
     <t>Comuna_Region_FK</t>
   </si>
   <si>
-    <t>FFA23F90-E801-A2D4-E9AC-BE2D4531FC43</t>
+    <t>1A7A46B4-A5BB-9963-38A7-0CA953FBC311</t>
   </si>
   <si>
     <t>Contract_ElectricityCompany_FK</t>
   </si>
   <si>
-    <t>919AA2F5-AF80-5051-B6F9-538494FE7BAC</t>
+    <t>3F8B3718-EC6C-1C37-DEBA-A1745C212A91</t>
   </si>
   <si>
     <t>Region_Country_FK</t>
   </si>
   <si>
-    <t>AB9E84E2-5500-6E2C-67D3-DF1370708BDF</t>
+    <t>6EBE25FD-4D8B-2C25-313E-A046D9B28639</t>
   </si>
   <si>
     <t>Result_UserDevice_FK</t>
   </si>
   <si>
-    <t>AA6605AF-93AE-856D-9F64-C0175D1DF2C6</t>
+    <t>C2093F02-E1DB-0F94-5C0F-3476052B2A0F</t>
   </si>
   <si>
     <t>UserDevice_AppUser_FK</t>
   </si>
   <si>
-    <t>74D8B263-9FF2-4C7D-6BA9-935B0A7F0914</t>
+    <t>FAB492A5-BE61-A93F-DBCC-ED412D0B3C9B</t>
   </si>
   <si>
     <t>UserDevice_Device_FK</t>
   </si>
   <si>
-    <t>0720CDBE-0745-D3C8-56BA-AF523EF21883</t>
+    <t>E458BDEB-C8FF-7F66-7A7F-E99EE778EAC1</t>
   </si>
   <si>
     <t>Address_PK</t>
   </si>
   <si>
-    <t>F31A8785-1566-8B79-1912-4802899ECAFD</t>
+    <t>CFE5693B-1EF3-B65F-414A-14B1577BB8EC</t>
   </si>
   <si>
     <t>AppUser_PK</t>
   </si>
   <si>
-    <t>9448563C-C682-6E0F-0396-00EC03FF551D</t>
+    <t>3A1D1823-99E0-5D7E-21DB-FB4A2411277F</t>
   </si>
   <si>
     <t>Comuna_PK</t>
   </si>
   <si>
-    <t>8E294E81-0842-B977-DF00-91D5568B7812</t>
+    <t>69550BDE-7C21-2319-A0DC-41ABCB0DCCC8</t>
   </si>
   <si>
     <t>Contract_PK</t>
   </si>
   <si>
-    <t>6CB0705F-75C2-8815-A321-6BFA5FAAD288</t>
+    <t>2AC03C25-3831-5BC3-81A3-643523A60A9F</t>
   </si>
   <si>
     <t>Country_PK</t>
   </si>
   <si>
-    <t>05CADB4C-D83F-8791-DD94-9FBFE95D096B</t>
+    <t>90B82748-D561-5445-43F3-104EBD560BB6</t>
   </si>
   <si>
     <t>Device_PK</t>
   </si>
   <si>
-    <t>89CBDD51-BB44-850F-A47D-3D8533C3CD85</t>
+    <t>43EF62E2-4F84-8F8D-0A1E-26C238D03A72</t>
   </si>
   <si>
     <t>ElectricityCompany_PK</t>
   </si>
   <si>
-    <t>B58ED608-D363-3FBA-D4FB-C8488BA89B82</t>
+    <t>BB006E51-FB85-8346-6CC6-15335EC5A711</t>
+  </si>
+  <si>
+    <t>PassRecoverRequest_PK</t>
+  </si>
+  <si>
+    <t>083497A0-D703-EC31-71B6-AA15F2192845</t>
   </si>
   <si>
     <t>Region_PK</t>
   </si>
   <si>
-    <t>E425749D-D18D-D192-E4D8-326F4435D4F2</t>
+    <t>0C93F24B-8280-1374-5824-C859E64ECFFF</t>
   </si>
   <si>
     <t>Result_PK</t>
   </si>
   <si>
-    <t>5CC83417-CD6D-1C2E-C695-8664F8B61C41</t>
+    <t>9181BB6D-9394-4C19-96F6-57EAB5AF9AC7</t>
   </si>
   <si>
     <t>UserDevice_PK</t>
   </si>
   <si>
-    <t>79E96C4E-1C5C-543C-C318-7D832E4B5819</t>
-  </si>
-  <si>
-    <t>Device_serialNumber_UN</t>
+    <t>BA848D2E-5838-25CA-B963-D9B7AFD79E9E</t>
+  </si>
+  <si>
+    <t>UK_PassRecoverRequest</t>
+  </si>
+  <si>
+    <t>F54F86BF-EDFF-D302-50C8-14B2D5BAB8D4</t>
+  </si>
+  <si>
+    <t>UK_serialNumber</t>
   </si>
   <si>
     <t>LOGDT005</t>
@@ -1573,6 +1651,15 @@
     <t>ElectricityCompany.id</t>
   </si>
   <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>PassRecoverRequest.id</t>
+  </si>
+  <si>
+    <t>PassRecoverRequest.request</t>
+  </si>
+  <si>
     <t>Region.id</t>
   </si>
   <si>
@@ -1580,9 +1667,6 @@
   </si>
   <si>
     <t>NUMBER (10,3)</t>
-  </si>
-  <si>
-    <t>DATE</t>
   </si>
   <si>
     <t>Result.id</t>
@@ -1784,12 +1868,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:H197"/>
+  <dimension ref="A2:H213"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.61328125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.4296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.98046875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="27.2734375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="25.59375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="67.140625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="16.640625" customWidth="true" bestFit="true"/>
@@ -1804,789 +1888,789 @@
     </row>
     <row r="4" ht="18.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" ht="18.0" customHeight="true">
       <c r="A5" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="true">
       <c r="B7" t="s" s="5">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" ht="18.0" customHeight="true">
       <c r="B8" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="9" ht="18.0" customHeight="true">
       <c r="B9" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" ht="18.0" customHeight="true">
       <c r="B10" s="6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" ht="18.0" customHeight="true">
       <c r="B11" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" ht="18.0" customHeight="true">
       <c r="B12" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" ht="18.0" customHeight="true">
       <c r="B15" t="s" s="5">
-        <v>326</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" ht="18.0" customHeight="true">
       <c r="B16" s="3" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>315</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" ht="18.0" customHeight="true">
       <c r="B17" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" ht="18.0" customHeight="true">
       <c r="B20" t="s" s="5">
-        <v>331</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" ht="18.0" customHeight="true">
       <c r="B21" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>320</v>
-      </c>
       <c r="F21" s="3" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" ht="18.0" customHeight="true">
       <c r="B22" s="6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24" ht="18.0" customHeight="true">
       <c r="A24" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" ht="18.0" customHeight="true">
       <c r="A25" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" ht="18.0" customHeight="true">
       <c r="B27" t="s" s="5">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="28" ht="18.0" customHeight="true">
       <c r="B28" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="29" ht="18.0" customHeight="true">
       <c r="B29" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30" ht="18.0" customHeight="true">
       <c r="B30" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31" ht="18.0" customHeight="true">
       <c r="B31" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" ht="18.0" customHeight="true">
       <c r="B32" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" ht="18.0" customHeight="true">
       <c r="B33" s="6" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34" ht="18.0" customHeight="true">
       <c r="B34" s="6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35" ht="18.0" customHeight="true">
       <c r="B35" s="6" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="36" ht="18.0" customHeight="true">
       <c r="B36" s="6" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37" ht="18.0" customHeight="true">
       <c r="B37" s="6" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="38" ht="18.0" customHeight="true">
       <c r="B38" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="41" ht="18.0" customHeight="true">
       <c r="B41" t="s" s="5">
-        <v>326</v>
+        <v>338</v>
       </c>
     </row>
     <row r="42" ht="18.0" customHeight="true">
       <c r="B42" s="3" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="D42" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>315</v>
-      </c>
       <c r="F42" s="3" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="43" ht="18.0" customHeight="true">
       <c r="B43" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="46" ht="18.0" customHeight="true">
       <c r="B46" t="s" s="5">
-        <v>331</v>
+        <v>343</v>
       </c>
     </row>
     <row r="47" ht="18.0" customHeight="true">
       <c r="B47" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>320</v>
-      </c>
       <c r="F47" s="3" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="48" ht="18.0" customHeight="true">
       <c r="B48" s="6" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="49" ht="18.0" customHeight="true">
       <c r="B49" s="6" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="51" ht="18.0" customHeight="true">
       <c r="A51" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="52" ht="18.0" customHeight="true">
       <c r="A52" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="54" ht="18.0" customHeight="true">
       <c r="B54" t="s" s="5">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="55" ht="18.0" customHeight="true">
       <c r="B55" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F55" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="56" ht="18.0" customHeight="true">
       <c r="B56" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" ht="18.0" customHeight="true">
       <c r="B57" s="6" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" ht="18.0" customHeight="true">
@@ -2594,488 +2678,488 @@
         <v>3</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" ht="18.0" customHeight="true">
       <c r="B61" t="s" s="5">
-        <v>326</v>
+        <v>338</v>
       </c>
     </row>
     <row r="62" ht="18.0" customHeight="true">
       <c r="B62" s="3" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="D62" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>315</v>
-      </c>
       <c r="F62" s="3" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" ht="18.0" customHeight="true">
       <c r="B63" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="66" ht="18.0" customHeight="true">
       <c r="B66" t="s" s="5">
-        <v>331</v>
+        <v>343</v>
       </c>
     </row>
     <row r="67" ht="18.0" customHeight="true">
       <c r="B67" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>320</v>
-      </c>
       <c r="F67" s="3" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" ht="18.0" customHeight="true">
       <c r="B68" s="6" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="70" ht="18.0" customHeight="true">
       <c r="A70" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="71" ht="18.0" customHeight="true">
       <c r="A71" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="73" ht="18.0" customHeight="true">
       <c r="B73" t="s" s="5">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="74" ht="18.0" customHeight="true">
       <c r="B74" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F74" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="75" ht="18.0" customHeight="true">
       <c r="B75" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="76" ht="18.0" customHeight="true">
       <c r="B76" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="77" ht="18.0" customHeight="true">
       <c r="B77" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="78" ht="18.0" customHeight="true">
       <c r="B78" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="79" ht="18.0" customHeight="true">
       <c r="B79" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="82" ht="18.0" customHeight="true">
       <c r="B82" t="s" s="5">
-        <v>326</v>
+        <v>338</v>
       </c>
     </row>
     <row r="83" ht="18.0" customHeight="true">
       <c r="B83" s="3" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="D83" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>315</v>
-      </c>
       <c r="F83" s="3" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="84" ht="18.0" customHeight="true">
       <c r="B84" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="87" ht="18.0" customHeight="true">
       <c r="B87" t="s" s="5">
-        <v>331</v>
+        <v>343</v>
       </c>
     </row>
     <row r="88" ht="18.0" customHeight="true">
       <c r="B88" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C88" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>320</v>
-      </c>
       <c r="F88" s="3" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="89" ht="18.0" customHeight="true">
       <c r="B89" s="6" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="91" ht="18.0" customHeight="true">
       <c r="A91" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="92" ht="18.0" customHeight="true">
       <c r="A92" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="94" ht="18.0" customHeight="true">
       <c r="B94" t="s" s="5">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="95" ht="18.0" customHeight="true">
       <c r="B95" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F95" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H95" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="G95" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="96" ht="18.0" customHeight="true">
       <c r="B96" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="97" ht="18.0" customHeight="true">
@@ -3083,181 +3167,181 @@
         <v>3</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="100" ht="18.0" customHeight="true">
       <c r="B100" t="s" s="5">
-        <v>326</v>
+        <v>338</v>
       </c>
     </row>
     <row r="101" ht="18.0" customHeight="true">
       <c r="B101" s="3" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="D101" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>315</v>
-      </c>
       <c r="F101" s="3" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="102" ht="18.0" customHeight="true">
       <c r="B102" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="104" ht="18.0" customHeight="true">
       <c r="A104" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="105" ht="18.0" customHeight="true">
       <c r="A105" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="107" ht="18.0" customHeight="true">
       <c r="B107" t="s" s="5">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="108" ht="18.0" customHeight="true">
       <c r="B108" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F108" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H108" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="109" ht="18.0" customHeight="true">
       <c r="B109" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="110" ht="18.0" customHeight="true">
       <c r="B110" s="6" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="111" ht="18.0" customHeight="true">
@@ -3265,201 +3349,201 @@
         <v>3</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="112" ht="18.0" customHeight="true">
       <c r="B112" s="6" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="115" ht="18.0" customHeight="true">
       <c r="B115" t="s" s="5">
-        <v>326</v>
+        <v>338</v>
       </c>
     </row>
     <row r="116" ht="18.0" customHeight="true">
       <c r="B116" s="3" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="D116" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E116" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E116" s="3" t="s">
-        <v>315</v>
-      </c>
       <c r="F116" s="3" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="117" ht="18.0" customHeight="true">
       <c r="B117" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="118" ht="18.0" customHeight="true">
       <c r="B118" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="120" ht="18.0" customHeight="true">
       <c r="A120" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="121" ht="18.0" customHeight="true">
       <c r="A121" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="123" ht="18.0" customHeight="true">
       <c r="B123" t="s" s="5">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="124" ht="18.0" customHeight="true">
       <c r="B124" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F124" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H124" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="G124" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="125" ht="18.0" customHeight="true">
       <c r="B125" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="126" ht="18.0" customHeight="true">
@@ -3467,973 +3551,1198 @@
         <v>3</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="129" ht="18.0" customHeight="true">
       <c r="B129" t="s" s="5">
-        <v>326</v>
+        <v>338</v>
       </c>
     </row>
     <row r="130" ht="18.0" customHeight="true">
       <c r="B130" s="3" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="D130" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E130" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E130" s="3" t="s">
-        <v>315</v>
-      </c>
       <c r="F130" s="3" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="131" ht="18.0" customHeight="true">
       <c r="B131" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="133" ht="18.0" customHeight="true">
       <c r="A133" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="134" ht="18.0" customHeight="true">
       <c r="A134" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="136" ht="18.0" customHeight="true">
       <c r="B136" t="s" s="5">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="137" ht="18.0" customHeight="true">
       <c r="B137" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F137" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H137" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="G137" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H137" s="3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="138" ht="18.0" customHeight="true">
       <c r="B138" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>317</v>
+        <v>352</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="139" ht="18.0" customHeight="true">
       <c r="B139" s="6" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>317</v>
+        <v>368</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="140" ht="18.0" customHeight="true">
       <c r="B140" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="141" ht="18.0" customHeight="true">
+      <c r="B141" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H141" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="144" ht="18.0" customHeight="true">
+      <c r="B144" t="s" s="5">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="145" ht="18.0" customHeight="true">
+      <c r="B145" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="146" ht="18.0" customHeight="true">
+      <c r="B146" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="G146" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="147" ht="18.0" customHeight="true">
+      <c r="B147" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="149" ht="18.0" customHeight="true">
+      <c r="A149" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="150" ht="18.0" customHeight="true">
+      <c r="A150" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="152" ht="18.0" customHeight="true">
+      <c r="B152" t="s" s="5">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="153" ht="18.0" customHeight="true">
+      <c r="B153" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="154" ht="18.0" customHeight="true">
+      <c r="B154" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H154" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="155" ht="18.0" customHeight="true">
+      <c r="B155" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D155" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H155" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="156" ht="18.0" customHeight="true">
+      <c r="B156" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C140" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="D140" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E140" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F140" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G140" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="143" ht="18.0" customHeight="true">
-      <c r="B143" t="s" s="5">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="144" ht="18.0" customHeight="true">
-      <c r="B144" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D144" s="3" t="s">
+      <c r="C156" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="159" ht="18.0" customHeight="true">
+      <c r="B159" t="s" s="5">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="160" ht="18.0" customHeight="true">
+      <c r="B160" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E160" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E144" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="G144" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="145" ht="18.0" customHeight="true">
-      <c r="B145" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="C145" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D145" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="E145" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="G145" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="148" ht="18.0" customHeight="true">
-      <c r="B148" t="s" s="5">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="149" ht="18.0" customHeight="true">
-      <c r="B149" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F149" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G149" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="H149" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="150" ht="18.0" customHeight="true">
-      <c r="B150" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E150" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="F150" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G150" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="152" ht="18.0" customHeight="true">
-      <c r="A152" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="153" ht="18.0" customHeight="true">
-      <c r="A153" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="D153" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="E153" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="F153" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="155" ht="18.0" customHeight="true">
-      <c r="B155" t="s" s="5">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="156" ht="18.0" customHeight="true">
-      <c r="B156" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F156" s="3" t="s">
+      <c r="F160" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G160" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="G156" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H156" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="157" ht="18.0" customHeight="true">
-      <c r="B157" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C157" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="D157" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E157" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F157" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G157" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H157" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="158" ht="18.0" customHeight="true">
-      <c r="B158" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C158" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="D158" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E158" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F158" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G158" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="159" ht="18.0" customHeight="true">
-      <c r="B159" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C159" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="D159" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E159" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="F159" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G159" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H159" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="160" ht="18.0" customHeight="true">
-      <c r="B160" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C160" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="D160" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E160" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F160" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="G160" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="161" ht="18.0" customHeight="true">
       <c r="B161" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C161" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="D161" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="G161" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="164" ht="18.0" customHeight="true">
+      <c r="B164" t="s" s="5">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="165" ht="18.0" customHeight="true">
+      <c r="B165" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="166" ht="18.0" customHeight="true">
+      <c r="B166" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="F166" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H166" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="168" ht="18.0" customHeight="true">
+      <c r="A168" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C168" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="E161" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F161" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G161" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H161" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="162" ht="18.0" customHeight="true">
-      <c r="B162" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C162" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="D162" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E162" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F162" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G162" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="165" ht="18.0" customHeight="true">
-      <c r="B165" t="s" s="5">
+      <c r="D168" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F168" s="2" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="166" ht="18.0" customHeight="true">
-      <c r="B166" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D166" s="3" t="s">
+    <row r="169" ht="18.0" customHeight="true">
+      <c r="A169" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="F169" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="171" ht="18.0" customHeight="true">
+      <c r="B171" t="s" s="5">
         <v>327</v>
       </c>
-      <c r="E166" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F166" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="167" ht="18.0" customHeight="true">
-      <c r="B167" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D167" s="6" t="s">
+    </row>
+    <row r="172" ht="18.0" customHeight="true">
+      <c r="B172" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C172" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E167" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="F167" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="G167" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="170" ht="18.0" customHeight="true">
-      <c r="B170" t="s" s="5">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="171" ht="18.0" customHeight="true">
-      <c r="B171" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C171" s="3" t="s">
+      <c r="D172" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D171" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E171" s="3" t="s">
+      <c r="E172" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="173" ht="18.0" customHeight="true">
+      <c r="B173" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="E173" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H173" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="174" ht="18.0" customHeight="true">
+      <c r="B174" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H174" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="175" ht="18.0" customHeight="true">
+      <c r="B175" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E175" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H175" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="176" ht="18.0" customHeight="true">
+      <c r="B176" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H176" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="177" ht="18.0" customHeight="true">
+      <c r="B177" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="E177" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H177" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="178" ht="18.0" customHeight="true">
+      <c r="B178" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H178" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="181" ht="18.0" customHeight="true">
+      <c r="B181" t="s" s="5">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="182" ht="18.0" customHeight="true">
+      <c r="B182" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="F171" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G171" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="H171" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="172" ht="18.0" customHeight="true">
-      <c r="B172" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C172" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D172" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E172" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="F172" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G172" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="H172" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="174" ht="18.0" customHeight="true">
-      <c r="A174" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F174" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="175" ht="18.0" customHeight="true">
-      <c r="A175" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="B175" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C175" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="D175" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="E175" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="F175" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="177" ht="18.0" customHeight="true">
-      <c r="B177" t="s" s="5">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="178" ht="18.0" customHeight="true">
-      <c r="B178" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="E178" s="3" t="s">
+      <c r="C182" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="F178" s="3" t="s">
+      <c r="D182" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G182" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="G178" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H178" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="179" ht="18.0" customHeight="true">
-      <c r="B179" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C179" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="D179" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E179" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F179" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G179" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H179" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="180" ht="18.0" customHeight="true">
-      <c r="B180" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C180" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="D180" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E180" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F180" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G180" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H180" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="181" ht="18.0" customHeight="true">
-      <c r="B181" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C181" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="D181" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="E181" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F181" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G181" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H181" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="182" ht="18.0" customHeight="true">
-      <c r="B182" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C182" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="D182" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E182" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="F182" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G182" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H182" s="6" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="183" ht="18.0" customHeight="true">
       <c r="B183" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C183" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="D183" s="8" t="s">
-        <v>321</v>
+        <v>321</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>340</v>
       </c>
       <c r="E183" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="G183" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="186" ht="18.0" customHeight="true">
+      <c r="B186" t="s" s="5">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="187" ht="18.0" customHeight="true">
+      <c r="B187" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="H187" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="188" ht="18.0" customHeight="true">
+      <c r="B188" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E188" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="G188" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H188" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="190" ht="18.0" customHeight="true">
+      <c r="A190" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C190" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F183" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="G183" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H183" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="184" ht="18.0" customHeight="true">
-      <c r="B184" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C184" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="D184" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E184" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F184" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="G184" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H184" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="185" ht="18.0" customHeight="true">
-      <c r="B185" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C185" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="D185" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E185" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F185" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G185" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H185" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="186" ht="18.0" customHeight="true">
-      <c r="B186" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C186" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="D186" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E186" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F186" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G186" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="H186" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="189" ht="18.0" customHeight="true">
-      <c r="B189" t="s" s="5">
+      <c r="D190" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F190" s="2" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="190" ht="18.0" customHeight="true">
-      <c r="B190" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C190" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D190" s="3" t="s">
+    <row r="191" ht="18.0" customHeight="true">
+      <c r="A191" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="193" ht="18.0" customHeight="true">
+      <c r="B193" t="s" s="5">
         <v>327</v>
       </c>
-      <c r="E190" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F190" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="G190" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="191" ht="18.0" customHeight="true">
-      <c r="B191" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="C191" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D191" s="6" t="s">
+    </row>
+    <row r="194" ht="18.0" customHeight="true">
+      <c r="B194" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C194" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E191" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="F191" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="G191" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="194" ht="18.0" customHeight="true">
-      <c r="B194" t="s" s="5">
-        <v>331</v>
+      <c r="D194" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H194" s="3" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="195" ht="18.0" customHeight="true">
-      <c r="B195" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C195" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D195" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E195" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F195" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="H195" s="3" t="s">
-        <v>312</v>
+      <c r="B195" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="D195" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="E195" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F195" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H195" s="6" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="196" ht="18.0" customHeight="true">
       <c r="B196" s="6" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D196" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E196" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="F196" s="7" t="s">
-        <v>321</v>
+        <v>368</v>
+      </c>
+      <c r="D196" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>335</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="197" ht="18.0" customHeight="true">
       <c r="B197" s="6" t="s">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="C197" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="D197" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="E197" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F197" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H197" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="198" ht="18.0" customHeight="true">
+      <c r="B198" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C198" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D198" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="F198" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G198" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H198" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="199" ht="18.0" customHeight="true">
+      <c r="B199" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D199" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F199" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H199" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="200" ht="18.0" customHeight="true">
+      <c r="B200" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C200" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D200" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H200" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="201" ht="18.0" customHeight="true">
+      <c r="B201" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C201" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="D201" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E201" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F201" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G201" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H201" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="202" ht="18.0" customHeight="true">
+      <c r="B202" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C202" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="D202" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E202" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F202" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="G202" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H202" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="205" ht="18.0" customHeight="true">
+      <c r="B205" t="s" s="5">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="206" ht="18.0" customHeight="true">
+      <c r="B206" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="207" ht="18.0" customHeight="true">
+      <c r="B207" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E207" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="F207" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="G207" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="210" ht="18.0" customHeight="true">
+      <c r="B210" t="s" s="5">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="211" ht="18.0" customHeight="true">
+      <c r="B211" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="H211" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="212" ht="18.0" customHeight="true">
+      <c r="B212" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C212" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E212" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="F212" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="G212" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H212" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="213" ht="18.0" customHeight="true">
+      <c r="B213" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C213" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D197" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E197" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="F197" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G197" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="H197" s="6" t="s">
-        <v>309</v>
+      <c r="D213" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E213" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="F213" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="G213" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H213" s="6" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -4441,7 +4750,7 @@
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <dataValidations count="48">
+  <dataValidations count="51">
     <dataValidation type="list" sqref="A5" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
@@ -4535,55 +4844,64 @@
     <dataValidation type="list" sqref="A134" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B145" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B146" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D150" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B147" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>null!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="A150" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>null!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="B161" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>null!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="D166" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E150" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E166" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F150" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F166" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A153" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A169" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B167" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B183" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D172" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D188" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E172" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E188" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F172" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F188" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A175" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A191" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B191" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B207" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D196" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D212" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D197" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D213" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E196" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E212" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E197" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E213" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F196" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F212" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F197" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F213" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4600,18 +4918,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -4759,7 +5077,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4840,6 +5158,14 @@
       </c>
       <c r="B10" s="8" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -4850,76 +5176,76 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>63</v>
@@ -4927,106 +5253,106 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
@@ -5114,28 +5440,28 @@
         <v>101</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>3</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>3</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>3</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>3</v>
@@ -5143,7 +5469,7 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>3</v>
@@ -5151,26 +5477,26 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>107</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>109</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>111</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -5227,6 +5553,38 @@
       </c>
       <c r="B47" s="8" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -5242,74 +5600,74 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -5320,87 +5678,95 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>163</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -5411,15 +5777,23 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>165</v>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -5435,546 +5809,546 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -5990,10 +6364,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
@@ -28,7 +28,7 @@
   <commentList>
     <comment ref="A5" authorId="0">
       <text>
-        <t>ObjectID:BE59DDEB-2961-4197-F76F-B817E05B3D4B;
+        <t>ObjectID:D51155F1-CB87-6486-6011-2FF99937561A;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
@@ -39,504 +39,522 @@
     </comment>
     <comment ref="B4" authorId="0">
       <text>
-        <t>ModelID:89F2C501-11B9-3D7E-8A22-96BE05DB5817</t>
+        <t>ModelID:3D635826-6EEE-8D18-4226-E5CBF72BEBB4</t>
       </text>
     </comment>
     <comment ref="B9" authorId="0">
       <text>
-        <t>ObjectID:615315FD-EF83-FB7A-8AB8-292D4194FF1E;
+        <t>ObjectID:275B3005-CA60-8E26-87EB-EC4C9886EC39;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B10" authorId="0">
       <text>
-        <t>ObjectID:21EC97DF-1E1A-CDF6-7F7F-FDB04E287767;
+        <t>ObjectID:F1720C33-5E86-A579-0090-ED7F4D559190;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B11" authorId="0">
       <text>
-        <t>ObjectID:AE5BD9F2-6313-D432-2674-B8E52865A6A2;
+        <t>ObjectID:DC25DEEB-CAED-ABDA-0F0F-4EAE61E3862B;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B12" authorId="0">
       <text>
-        <t>ObjectID:754472F2-BBC9-01D7-3065-91FA7F418345;
+        <t>ObjectID:89ED432E-DC9D-2B38-869B-AD0BFB0423DC;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B17" authorId="0">
       <text>
-        <t>ObjectID:E458BDEB-C8FF-7F66-7A7F-E99EE778EAC1;
+        <t>ObjectID:5D314F9D-79E8-A9ED-011B-F5EB056D202D;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="B22" authorId="0">
       <text>
-        <t>ObjectID:3F4F74A7-9382-56B2-EC84-398C37AC9069;
+        <t>ObjectID:5E5292AD-5A7F-80CC-4265-A9E4BF7F6FD4;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="A25" authorId="0">
       <text>
-        <t>ObjectID:B74D2B92-6181-52A3-6451-55154CCCB449;
+        <t>ObjectID:BF6EDCA5-54B6-46F9-4814-C907235A94EB;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0">
       <text>
-        <t>ObjectID:93C10ECE-2B0C-AF90-6BE3-86A5C9D53868;
+        <t>ObjectID:CB80906D-16D9-27DE-3A8B-67BA6FF423C4;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0">
       <text>
-        <t>ObjectID:254BED24-3145-3387-0719-E1E478CEFE92;
+        <t>ObjectID:26A7036D-E4B0-DE89-14BA-8E97F98305C6;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0">
       <text>
-        <t>ObjectID:463F92FB-D068-8187-1339-4D542C0FB293;
+        <t>ObjectID:ACBC239B-65C0-D6B1-CB1A-BEAE5FBA9B25;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B32" authorId="0">
       <text>
-        <t>ObjectID:A5BF70AC-2700-6399-33A6-EED3E3631787;
+        <t>ObjectID:96F0A8B5-8BE1-9346-540D-B1A5DB9E97E8;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B33" authorId="0">
       <text>
-        <t>ObjectID:6B18BD86-D78A-DFF3-2B29-D099B857B7F1;
+        <t>ObjectID:1B6B8678-D75A-AE62-7CA1-87F8E6BEC7CB;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0">
       <text>
-        <t>ObjectID:054DEEF8-1367-3A10-59DB-33C41E40E516;
+        <t>ObjectID:B8365782-DAE5-7D37-5A61-03CB7CAF3EBA;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0">
       <text>
-        <t>ObjectID:99C39193-C45C-BEDD-E898-36AD07AFBD6D;
+        <t>ObjectID:80B59BB6-F206-AC15-7CC1-25F0484CB116;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B36" authorId="0">
       <text>
-        <t>ObjectID:BE6CCBA7-246F-F003-6181-E48CD286D01F;
+        <t>ObjectID:D1671859-BB90-F668-54B8-2F6B02EEAD4A;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B37" authorId="0">
       <text>
-        <t>ObjectID:42273DB2-D04F-3BFE-39EE-567370D65DE6;
+        <t>ObjectID:65CBF565-D7E8-AE54-FDB9-5EF60471D1D8;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0">
       <text>
-        <t>ObjectID:33C1567D-0A91-FC62-7EEC-128359F701D7;
+        <t>ObjectID:29C62EEF-B381-7868-C72D-0348822B5CBB;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0">
       <text>
-        <t>ObjectID:CFE5693B-1EF3-B65F-414A-14B1577BB8EC;
+        <t>ObjectID:FB4BED2B-2004-4F9B-BFE0-FD63710FB81F;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="B48" authorId="0">
       <text>
-        <t>ObjectID:5E5996B1-0261-3FA0-89AF-68ED840980E4;
+        <t>ObjectID:DBBB9B51-44BE-4CB1-B4C3-03F6AA4A8B4C;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="B49" authorId="0">
       <text>
-        <t>ObjectID:AF7482BA-CE15-D252-8566-F3A51B3B7781;
+        <t>ObjectID:AD0A0EA6-D0BB-7281-1AF4-46C1B9A72B1F;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="A52" authorId="0">
       <text>
-        <t>ObjectID:39E5C551-B715-AEA6-BCD1-F132800F4B52;
+        <t>ObjectID:36092FE7-0536-8BFA-C716-80AC4148A7F0;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B56" authorId="0">
       <text>
-        <t>ObjectID:430DE1EB-E953-1D52-F887-98986AD97B5C;
+        <t>ObjectID:5F72E1E0-0043-42F1-DBCE-53EE47EBDC8C;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B57" authorId="0">
       <text>
-        <t>ObjectID:A8C99DEF-8D99-DCC7-4218-5AF2D7CE0460;
+        <t>ObjectID:65D1AB3F-6D27-B506-D26F-5C5DBE82A48E;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B58" authorId="0">
       <text>
-        <t>ObjectID:CF0EC2C2-1664-01B7-89AD-3E320E5A3B23;
+        <t>ObjectID:F987AE6E-E6CD-09F8-BF70-BE0B6F44F316;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B63" authorId="0">
       <text>
-        <t>ObjectID:3A1D1823-99E0-5D7E-21DB-FB4A2411277F;
+        <t>ObjectID:2F0B7274-57DF-96EA-D2EE-96C79B342FA3;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="B68" authorId="0">
       <text>
-        <t>ObjectID:6220D5A5-C299-AF56-E6BD-6F33CE588850;
+        <t>ObjectID:75D38094-908D-7A27-6D8E-4CE19596010B;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="A71" authorId="0">
       <text>
-        <t>ObjectID:9412012D-8F5A-24C5-FC14-BFDE03A3834F;
+        <t>ObjectID:62BC86AA-5EFE-4153-187E-5602C9BF4382;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B75" authorId="0">
       <text>
-        <t>ObjectID:3CD305C0-A8EE-C2AB-B4A0-FFD67093C959;
+        <t>ObjectID:C13D6EC9-6DB9-37D7-E47F-E93D182529F3;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B76" authorId="0">
       <text>
-        <t>ObjectID:E86052E6-5F17-C60F-FE23-09BFEC8ABC52;
+        <t>ObjectID:88D79E68-CA48-4058-D21F-BA79CABB78AB;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B77" authorId="0">
       <text>
-        <t>ObjectID:1B2AF109-5895-6C1E-40FB-4B222ADF5375;
+        <t>ObjectID:C01718B8-C4F8-B1C7-0F1C-6AC4FCA98611;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B78" authorId="0">
       <text>
-        <t>ObjectID:3A991CE4-51C1-A587-3F7B-FEB51550FC5E;
+        <t>ObjectID:BEE3DE21-220B-CD2A-B7E0-F2616C1F1A42;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B79" authorId="0">
       <text>
-        <t>ObjectID:1F7E614D-DB93-2852-2D76-3FD8A77404B7;
+        <t>ObjectID:8EF8F83D-FC31-6C2A-AFF0-4AAA5DEE4164;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B84" authorId="0">
       <text>
-        <t>ObjectID:69550BDE-7C21-2319-A0DC-41ABCB0DCCC8;
+        <t>ObjectID:5C96EEB9-3B9E-9966-C2E9-458E27E82794;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="B89" authorId="0">
       <text>
-        <t>ObjectID:1A7A46B4-A5BB-9963-38A7-0CA953FBC311;
+        <t>ObjectID:6A10348A-0CED-BF35-52B4-A89AE138322C;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
     <comment ref="A92" authorId="0">
       <text>
-        <t>ObjectID:2CC2FB13-8CA5-0A26-69E9-27224FF28239;
+        <t>ObjectID:2410051C-8819-3032-2EB0-236CA64DD92F;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B96" authorId="0">
       <text>
-        <t>ObjectID:B3B466F2-0B6F-1CB1-8F58-3A114F8C63BA;
+        <t>ObjectID:E4FC695C-DB7F-273E-0C47-C01648108DA5;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B97" authorId="0">
       <text>
-        <t>ObjectID:6A543D3E-CDB2-0B84-4129-647EEE7510CB;
+        <t>ObjectID:0D61A7B9-DD3E-45F7-0461-0E63A231985C;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B102" authorId="0">
       <text>
-        <t>ObjectID:2AC03C25-3831-5BC3-81A3-643523A60A9F;
+        <t>ObjectID:2D0CBBCF-394E-E5AD-939E-BD7D1DDEF56F;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
     <comment ref="A105" authorId="0">
       <text>
-        <t>ObjectID:73687451-F72D-7430-24BC-625E4A733080;
+        <t>ObjectID:8108C45A-B8F1-B876-CECF-5895B7CEA3FF;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
     <comment ref="B109" authorId="0">
       <text>
-        <t>ObjectID:CA915E21-200D-7184-1521-198020501E55;
+        <t>ObjectID:B79CB950-5BF3-4DC8-8B7C-D7770260C2F4;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B110" authorId="0">
       <text>
-        <t>ObjectID:9F5DB5DB-6466-A0C5-B055-4281B4AC4172;
+        <t>ObjectID:894BB5B3-3F0B-21E8-31BF-33DB6B10E248;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B111" authorId="0">
       <text>
-        <t>ObjectID:6B0A2361-5661-B3DF-7493-049F85F7F980;
+        <t>ObjectID:CBF3DA9C-8F51-F3C3-AF90-301736679BFB;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B112" authorId="0">
-      <text>
-        <t>ObjectID:9C6621B9-EF9D-CE31-14F3-F45EBABD4942;
+    <comment ref="B116" authorId="0">
+      <text>
+        <t>ObjectID:BE326729-75E3-5E07-0E76-69AE18D1D987;
+Class:oracle.dbtools.crest.model.design.relational.Index</t>
+      </text>
+    </comment>
+    <comment ref="B117" authorId="0">
+      <text>
+        <t>ObjectID:AF39C5BF-6E22-9FE5-D99E-5F1F4DB76760;
+Class:oracle.dbtools.crest.model.design.relational.Index</t>
+      </text>
+    </comment>
+    <comment ref="B122" authorId="0">
+      <text>
+        <t>ObjectID:FC33450B-7F2C-94F4-DC61-5DA2E42E21D7;
+Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
+      </text>
+    </comment>
+    <comment ref="A125" authorId="0">
+      <text>
+        <t>ObjectID:6BFBC7C1-6C09-D8BA-C1D1-E02F39A5CAAC;
+Class:oracle.dbtools.crest.model.design.relational.Table</t>
+      </text>
+    </comment>
+    <comment ref="B129" authorId="0">
+      <text>
+        <t>ObjectID:7ABD1485-D415-29B3-802F-B235595EFE87;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B117" authorId="0">
-      <text>
-        <t>ObjectID:90B82748-D561-5445-43F3-104EBD560BB6;
+    <comment ref="B130" authorId="0">
+      <text>
+        <t>ObjectID:5E39503B-23B3-C4BC-AF2D-6D85A3F3CAB4;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B135" authorId="0">
+      <text>
+        <t>ObjectID:C04DB6CF-A65C-FA70-A681-07292A82A1B7;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B118" authorId="0">
-      <text>
-        <t>ObjectID:F54F86BF-EDFF-D302-50C8-14B2D5BAB8D4;
+    <comment ref="A138" authorId="0">
+      <text>
+        <t>ObjectID:BE0F17A2-7714-D02E-0AB9-C0E8E1FAAD2D;
+Class:oracle.dbtools.crest.model.design.relational.Table</t>
+      </text>
+    </comment>
+    <comment ref="B142" authorId="0">
+      <text>
+        <t>ObjectID:72E7BD72-71EA-49B3-00BF-7728CE9660FC;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B143" authorId="0">
+      <text>
+        <t>ObjectID:FD10B671-C4FD-3C2C-5BF2-EC91B141B9E3;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B148" authorId="0">
+      <text>
+        <t>ObjectID:01C8FE1E-6482-FFE6-7378-D1A702CF6A5E;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="A121" authorId="0">
-      <text>
-        <t>ObjectID:0D580267-E860-C399-6E61-F0538E07B0F8;
+    <comment ref="A151" authorId="0">
+      <text>
+        <t>ObjectID:F97F7709-899E-B8F2-6565-1CA4829D3F4F;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B125" authorId="0">
-      <text>
-        <t>ObjectID:017D57CC-645E-4920-15EC-1C9568C9FECE;
+    <comment ref="B155" authorId="0">
+      <text>
+        <t>ObjectID:0BE4BE77-A5F4-D18F-417B-AD7AD0783EFD;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B126" authorId="0">
-      <text>
-        <t>ObjectID:35C45BEA-A44B-281F-776D-E686DB9F29F2;
+    <comment ref="B156" authorId="0">
+      <text>
+        <t>ObjectID:F5EB8F8E-AD04-1AEB-7179-04A01CCC1CD1;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B131" authorId="0">
-      <text>
-        <t>ObjectID:43EF62E2-4F84-8F8D-0A1E-26C238D03A72;
+    <comment ref="B157" authorId="0">
+      <text>
+        <t>ObjectID:0417C238-82AC-A5B2-88E7-F2BB25C183A5;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B158" authorId="0">
+      <text>
+        <t>ObjectID:42C891A4-63BB-6418-FAA8-D17226EC5C01;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B163" authorId="0">
+      <text>
+        <t>ObjectID:986AC3FA-C3B1-3891-F846-E0E0858FEC83;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="A134" authorId="0">
-      <text>
-        <t>ObjectID:B2D4B9D3-A8A1-261C-3323-1BFE69DC4D39;
+    <comment ref="B164" authorId="0">
+      <text>
+        <t>ObjectID:90957D93-7452-534B-1634-9D8FD61DFE4C;
+Class:oracle.dbtools.crest.model.design.relational.Index</t>
+      </text>
+    </comment>
+    <comment ref="A167" authorId="0">
+      <text>
+        <t>ObjectID:869F4D8F-4475-8FFE-A6EE-886B3184C307;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B138" authorId="0">
-      <text>
-        <t>ObjectID:F0C8DEED-9306-5A61-4CBA-8C61E7C2ED73;
+    <comment ref="B171" authorId="0">
+      <text>
+        <t>ObjectID:56F05333-4945-447A-1128-61D911628D2D;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B139" authorId="0">
-      <text>
-        <t>ObjectID:8BF22F09-ED2B-9FE3-634A-FC4550738ADC;
+    <comment ref="B172" authorId="0">
+      <text>
+        <t>ObjectID:49234B3D-D282-A611-1B13-14B049DBDA32;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B140" authorId="0">
-      <text>
-        <t>ObjectID:4B515041-ACD9-99C4-27B9-C147D82A08C4;
+    <comment ref="B173" authorId="0">
+      <text>
+        <t>ObjectID:30BDE08B-6525-28F3-CF81-72CBF76C81D0;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B141" authorId="0">
-      <text>
-        <t>ObjectID:B5DB67C7-D8D1-CB96-DB06-62643CBAD3F7;
+    <comment ref="B178" authorId="0">
+      <text>
+        <t>ObjectID:4933545D-1F61-8ED0-B934-64D572D93361;
+Class:oracle.dbtools.crest.model.design.relational.Index</t>
+      </text>
+    </comment>
+    <comment ref="B183" authorId="0">
+      <text>
+        <t>ObjectID:63048F18-7038-8AA8-09BC-D4CC9002DC1B;
+Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
+      </text>
+    </comment>
+    <comment ref="A186" authorId="0">
+      <text>
+        <t>ObjectID:D6B8A970-3939-E69C-142D-CB91197D0771;
+Class:oracle.dbtools.crest.model.design.relational.Table</t>
+      </text>
+    </comment>
+    <comment ref="B190" authorId="0">
+      <text>
+        <t>ObjectID:1E82BF4A-BAF2-4673-AE94-7E8E775F444C;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B146" authorId="0">
-      <text>
-        <t>ObjectID:BB006E51-FB85-8346-6CC6-15335EC5A711;
+    <comment ref="B191" authorId="0">
+      <text>
+        <t>ObjectID:0B4AB6A2-0A24-0EE4-0AC3-C3091003F21A;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B192" authorId="0">
+      <text>
+        <t>ObjectID:AEC573F9-790B-6348-921B-492CF00715BB;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B193" authorId="0">
+      <text>
+        <t>ObjectID:B9CE75B2-F56A-52F4-2402-0691648374D7;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B194" authorId="0">
+      <text>
+        <t>ObjectID:CBEA499C-F80C-71E9-8E6E-48362CA13E64;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B195" authorId="0">
+      <text>
+        <t>ObjectID:6FD2AB96-64C9-268D-FA84-F63872C1C776;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B200" authorId="0">
+      <text>
+        <t>ObjectID:FB03E2AC-45A7-8C05-12CC-D68C07B74E28;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B147" authorId="0">
-      <text>
-        <t>ObjectID:BA848D2E-5838-25CA-B963-D9B7AFD79E9E;
+    <comment ref="B205" authorId="0">
+      <text>
+        <t>ObjectID:83C7BCD0-3CF7-4066-575B-DCF99FCC2E77;
+Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
+      </text>
+    </comment>
+    <comment ref="A208" authorId="0">
+      <text>
+        <t>ObjectID:287B4946-F23B-8355-D758-108C565A3A9F;
+Class:oracle.dbtools.crest.model.design.relational.Table</t>
+      </text>
+    </comment>
+    <comment ref="B212" authorId="0">
+      <text>
+        <t>ObjectID:131DDB81-1720-6820-5F6D-0B072C3417E4;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B213" authorId="0">
+      <text>
+        <t>ObjectID:14D36442-EC52-B1D0-75DF-002E0A9AF76F;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B214" authorId="0">
+      <text>
+        <t>ObjectID:06DE242F-8E38-E7BC-628D-6635622276ED;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B215" authorId="0">
+      <text>
+        <t>ObjectID:914BC5D9-89EB-EF1A-FB0C-E191FFDF845A;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B216" authorId="0">
+      <text>
+        <t>ObjectID:8BBEBBE6-9B7F-C0C9-0A4D-4D9BDCE6FB56;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B217" authorId="0">
+      <text>
+        <t>ObjectID:8BEC7653-46CD-F2E0-9830-CA915F8C1373;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B218" authorId="0">
+      <text>
+        <t>ObjectID:5E11E6A3-7C82-40A3-39DE-32D3F0F53201;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B223" authorId="0">
+      <text>
+        <t>ObjectID:CBC9FCC6-07E2-6B05-99C1-EEF1B9904CB5;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="A150" authorId="0">
-      <text>
-        <t>ObjectID:E11C7B03-BD57-3A45-7BBD-3F6A277CCBB9;
-Class:oracle.dbtools.crest.model.design.relational.Table</t>
-      </text>
-    </comment>
-    <comment ref="B154" authorId="0">
-      <text>
-        <t>ObjectID:6D1A3FA8-F979-56CA-F333-DE584D71E9D8;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B155" authorId="0">
-      <text>
-        <t>ObjectID:6D73AB1A-5354-2711-3B37-A68B8A099079;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B156" authorId="0">
-      <text>
-        <t>ObjectID:BC77D151-BC65-88EA-7671-5C9A0DAB542F;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B161" authorId="0">
-      <text>
-        <t>ObjectID:083497A0-D703-EC31-71B6-AA15F2192845;
-Class:oracle.dbtools.crest.model.design.relational.Index</t>
-      </text>
-    </comment>
-    <comment ref="B166" authorId="0">
-      <text>
-        <t>ObjectID:3F8B3718-EC6C-1C37-DEBA-A1745C212A91;
+    <comment ref="B228" authorId="0">
+      <text>
+        <t>ObjectID:C1351D80-F0CC-2B58-179F-42E862C66921;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="A169" authorId="0">
-      <text>
-        <t>ObjectID:220C4288-9B1F-3E10-2C33-BDFCB9DCFD4D;
-Class:oracle.dbtools.crest.model.design.relational.Table</t>
-      </text>
-    </comment>
-    <comment ref="B173" authorId="0">
-      <text>
-        <t>ObjectID:57CAB14E-29C7-5D92-C7C0-6C6D7D014685;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B174" authorId="0">
-      <text>
-        <t>ObjectID:49039BFA-516D-0985-5B04-3EEEA8A700E2;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B175" authorId="0">
-      <text>
-        <t>ObjectID:5B69787F-90B9-14E0-8DEE-4012406206B4;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B176" authorId="0">
-      <text>
-        <t>ObjectID:15F769F5-49F6-CC43-71C2-FF704C638C1A;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B177" authorId="0">
-      <text>
-        <t>ObjectID:80BC2183-0748-53E4-0D5F-6BB3362DE3C7;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B178" authorId="0">
-      <text>
-        <t>ObjectID:7AB70A62-442D-8F1D-2832-B0B51B9FA5AB;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B183" authorId="0">
-      <text>
-        <t>ObjectID:0C93F24B-8280-1374-5824-C859E64ECFFF;
-Class:oracle.dbtools.crest.model.design.relational.Index</t>
-      </text>
-    </comment>
-    <comment ref="B188" authorId="0">
-      <text>
-        <t>ObjectID:6EBE25FD-4D8B-2C25-313E-A046D9B28639;
-Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
-      </text>
-    </comment>
-    <comment ref="A191" authorId="0">
-      <text>
-        <t>ObjectID:D7FF44B5-3811-43B7-CF6B-4CB3BCC73E65;
-Class:oracle.dbtools.crest.model.design.relational.Table</t>
-      </text>
-    </comment>
-    <comment ref="B195" authorId="0">
-      <text>
-        <t>ObjectID:E59B3F94-CF0E-64D3-034F-9ACA353FA5C6;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B196" authorId="0">
-      <text>
-        <t>ObjectID:34C50EB1-A41D-562B-AD3E-04DF31085334;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B197" authorId="0">
-      <text>
-        <t>ObjectID:A3BA4F71-0148-03F6-E94E-FB5C7863E9E4;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B198" authorId="0">
-      <text>
-        <t>ObjectID:CAD5F08D-6F7F-988F-F7C0-DBB9B261CDEB;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B199" authorId="0">
-      <text>
-        <t>ObjectID:DD80B398-AB70-2FFF-85B7-96A17D879E8C;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B200" authorId="0">
-      <text>
-        <t>ObjectID:F40997A8-17B5-799B-4070-02102A0B1F75;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B201" authorId="0">
-      <text>
-        <t>ObjectID:97AA6B84-A02A-2D10-04F0-441D367ADC7B;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B202" authorId="0">
-      <text>
-        <t>ObjectID:0C020521-4649-1A28-58F6-CE7EAD4ECC6F;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B207" authorId="0">
-      <text>
-        <t>ObjectID:9181BB6D-9394-4C19-96F6-57EAB5AF9AC7;
-Class:oracle.dbtools.crest.model.design.relational.Index</t>
-      </text>
-    </comment>
-    <comment ref="B212" authorId="0">
-      <text>
-        <t>ObjectID:C2093F02-E1DB-0F94-5C0F-3476052B2A0F;
-Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
-      </text>
-    </comment>
-    <comment ref="B213" authorId="0">
-      <text>
-        <t>ObjectID:FAB492A5-BE61-A93F-DBCC-ED412D0B3C9B;
+    <comment ref="B229" authorId="0">
+      <text>
+        <t>ObjectID:2A93B142-6F4C-4802-A894-91D9E3EE400D;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
@@ -545,7 +563,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="383">
   <si>
     <t>Diccionario de datos BD</t>
   </si>
@@ -625,460 +643,475 @@
     <t>generateInDDL</t>
   </si>
   <si>
-    <t>BE59DDEB-2961-4197-F76F-B817E05B3D4B</t>
+    <t>D51155F1-CB87-6486-6011-2FF99937561A</t>
   </si>
   <si>
     <t>Address</t>
   </si>
   <si>
-    <t>B74D2B92-6181-52A3-6451-55154CCCB449</t>
+    <t>BF6EDCA5-54B6-46F9-4814-C907235A94EB</t>
   </si>
   <si>
     <t>AppUser</t>
   </si>
   <si>
-    <t>39E5C551-B715-AEA6-BCD1-F132800F4B52</t>
+    <t>36092FE7-0536-8BFA-C716-80AC4148A7F0</t>
   </si>
   <si>
     <t>Comuna</t>
   </si>
   <si>
-    <t>9412012D-8F5A-24C5-FC14-BFDE03A3834F</t>
+    <t>62BC86AA-5EFE-4153-187E-5602C9BF4382</t>
   </si>
   <si>
     <t>Contract</t>
   </si>
   <si>
-    <t>2CC2FB13-8CA5-0A26-69E9-27224FF28239</t>
+    <t>2410051C-8819-3032-2EB0-236CA64DD92F</t>
   </si>
   <si>
     <t>Country</t>
   </si>
   <si>
-    <t>73687451-F72D-7430-24BC-625E4A733080</t>
+    <t>8108C45A-B8F1-B876-CECF-5895B7CEA3FF</t>
   </si>
   <si>
     <t>Device</t>
   </si>
   <si>
-    <t>0D580267-E860-C399-6E61-F0538E07B0F8</t>
+    <t>6BFBC7C1-6C09-D8BA-C1D1-E02F39A5CAAC</t>
+  </si>
+  <si>
+    <t>DeviceModel</t>
+  </si>
+  <si>
+    <t>BE0F17A2-7714-D02E-0AB9-C0E8E1FAAD2D</t>
   </si>
   <si>
     <t>ElectricityCompany</t>
   </si>
   <si>
-    <t>B2D4B9D3-A8A1-261C-3323-1BFE69DC4D39</t>
+    <t>F97F7709-899E-B8F2-6565-1CA4829D3F4F</t>
   </si>
   <si>
     <t>PassRecoverRequest</t>
   </si>
   <si>
-    <t>E11C7B03-BD57-3A45-7BBD-3F6A277CCBB9</t>
+    <t>869F4D8F-4475-8FFE-A6EE-886B3184C307</t>
   </si>
   <si>
     <t>Region</t>
   </si>
   <si>
-    <t>220C4288-9B1F-3E10-2C33-BDFCB9DCFD4D</t>
+    <t>D6B8A970-3939-E69C-142D-CB91197D0771</t>
   </si>
   <si>
     <t>Result</t>
   </si>
   <si>
-    <t>D7FF44B5-3811-43B7-CF6B-4CB3BCC73E65</t>
+    <t>287B4946-F23B-8355-D758-108C565A3A9F</t>
   </si>
   <si>
     <t>UserDevice</t>
   </si>
   <si>
-    <t>E59B3F94-CF0E-64D3-034F-9ACA353FA5C6</t>
+    <t>131DDB81-1720-6820-5F6D-0B072C3417E4</t>
   </si>
   <si>
     <t>alias</t>
   </si>
   <si>
-    <t>57CAB14E-29C7-5D92-C7C0-6C6D7D014685</t>
+    <t>1E82BF4A-BAF2-4673-AE94-7E8E775F444C</t>
   </si>
   <si>
     <t>ampere</t>
   </si>
   <si>
-    <t>93C10ECE-2B0C-AF90-6BE3-86A5C9D53868</t>
+    <t>CB80906D-16D9-27DE-3A8B-67BA6FF423C4</t>
   </si>
   <si>
     <t>countryCode</t>
   </si>
   <si>
-    <t>34C50EB1-A41D-562B-AD3E-04DF31085334</t>
+    <t>14D36442-EC52-B1D0-75DF-002E0A9AF76F</t>
   </si>
   <si>
     <t>creationDate</t>
   </si>
   <si>
-    <t>49039BFA-516D-0985-5B04-3EEEA8A700E2</t>
+    <t>0B4AB6A2-0A24-0EE4-0AC3-C3091003F21A</t>
   </si>
   <si>
     <t>date</t>
   </si>
   <si>
-    <t>A3BA4F71-0148-03F6-E94E-FB5C7863E9E4</t>
+    <t>06DE242F-8E38-E7BC-628D-6635622276ED</t>
   </si>
   <si>
     <t>description</t>
   </si>
   <si>
-    <t>3CD305C0-A8EE-C2AB-B4A0-FFD67093C959</t>
+    <t>C13D6EC9-6DB9-37D7-E47F-E93D182529F3</t>
   </si>
   <si>
     <t>electricityCost</t>
   </si>
   <si>
-    <t>254BED24-3145-3387-0719-E1E478CEFE92</t>
+    <t>26A7036D-E4B0-DE89-14BA-8E97F98305C6</t>
   </si>
   <si>
     <t>email</t>
   </si>
   <si>
-    <t>F0C8DEED-9306-5A61-4CBA-8C61E7C2ED73</t>
-  </si>
-  <si>
-    <t>8BF22F09-ED2B-9FE3-634A-FC4550738ADC</t>
+    <t>0BE4BE77-A5F4-D18F-417B-AD7AD0783EFD</t>
+  </si>
+  <si>
+    <t>F5EB8F8E-AD04-1AEB-7179-04A01CCC1CD1</t>
   </si>
   <si>
     <t>expireDateTime</t>
   </si>
   <si>
-    <t>463F92FB-D068-8187-1339-4D542C0FB293</t>
+    <t>ACBC239B-65C0-D6B1-CB1A-BEAE5FBA9B25</t>
   </si>
   <si>
     <t>firstName</t>
   </si>
   <si>
-    <t>615315FD-EF83-FB7A-8AB8-292D4194FF1E</t>
+    <t>275B3005-CA60-8E26-87EB-EC4C9886EC39</t>
   </si>
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>430DE1EB-E953-1D52-F887-98986AD97B5C</t>
-  </si>
-  <si>
-    <t>E86052E6-5F17-C60F-FE23-09BFEC8ABC52</t>
-  </si>
-  <si>
-    <t>B3B466F2-0B6F-1CB1-8F58-3A114F8C63BA</t>
-  </si>
-  <si>
-    <t>CA915E21-200D-7184-1521-198020501E55</t>
-  </si>
-  <si>
-    <t>017D57CC-645E-4920-15EC-1C9568C9FECE</t>
-  </si>
-  <si>
-    <t>4B515041-ACD9-99C4-27B9-C147D82A08C4</t>
-  </si>
-  <si>
-    <t>5B69787F-90B9-14E0-8DEE-4012406206B4</t>
-  </si>
-  <si>
-    <t>A5BF70AC-2700-6399-33A6-EED3E3631787</t>
-  </si>
-  <si>
-    <t>CAD5F08D-6F7F-988F-F7C0-DBB9B261CDEB</t>
-  </si>
-  <si>
-    <t>6D1A3FA8-F979-56CA-F333-DE584D71E9D8</t>
-  </si>
-  <si>
-    <t>6B18BD86-D78A-DFF3-2B29-D099B857B7F1</t>
+    <t>5F72E1E0-0043-42F1-DBCE-53EE47EBDC8C</t>
+  </si>
+  <si>
+    <t>88D79E68-CA48-4058-D21F-BA79CABB78AB</t>
+  </si>
+  <si>
+    <t>E4FC695C-DB7F-273E-0C47-C01648108DA5</t>
+  </si>
+  <si>
+    <t>B79CB950-5BF3-4DC8-8B7C-D7770260C2F4</t>
+  </si>
+  <si>
+    <t>7ABD1485-D415-29B3-802F-B235595EFE87</t>
+  </si>
+  <si>
+    <t>72E7BD72-71EA-49B3-00BF-7728CE9660FC</t>
+  </si>
+  <si>
+    <t>0417C238-82AC-A5B2-88E7-F2BB25C183A5</t>
+  </si>
+  <si>
+    <t>AEC573F9-790B-6348-921B-492CF00715BB</t>
+  </si>
+  <si>
+    <t>96F0A8B5-8BE1-9346-540D-B1A5DB9E97E8</t>
+  </si>
+  <si>
+    <t>914BC5D9-89EB-EF1A-FB0C-E191FFDF845A</t>
+  </si>
+  <si>
+    <t>56F05333-4945-447A-1128-61D911628D2D</t>
+  </si>
+  <si>
+    <t>1B6B8678-D75A-AE62-7CA1-87F8E6BEC7CB</t>
   </si>
   <si>
     <t>idAddress</t>
   </si>
   <si>
-    <t>21EC97DF-1E1A-CDF6-7F7F-FDB04E287767</t>
+    <t>F1720C33-5E86-A579-0090-ED7F4D559190</t>
   </si>
   <si>
     <t>idComuna</t>
   </si>
   <si>
-    <t>054DEEF8-1367-3A10-59DB-33C41E40E516</t>
+    <t>B8365782-DAE5-7D37-5A61-03CB7CAF3EBA</t>
   </si>
   <si>
     <t>idContract</t>
   </si>
   <si>
-    <t>6D73AB1A-5354-2711-3B37-A68B8A099079</t>
+    <t>49234B3D-D282-A611-1B13-14B049DBDA32</t>
   </si>
   <si>
     <t>idCountry</t>
   </si>
   <si>
-    <t>DD80B398-AB70-2FFF-85B7-96A17D879E8C</t>
+    <t>8BBEBBE6-9B7F-C0C9-0A4D-4D9BDCE6FB56</t>
   </si>
   <si>
     <t>idDevice</t>
   </si>
   <si>
-    <t>1B2AF109-5895-6C1E-40FB-4B222ADF5375</t>
+    <t>894BB5B3-3F0B-21E8-31BF-33DB6B10E248</t>
+  </si>
+  <si>
+    <t>idDeviceModel</t>
+  </si>
+  <si>
+    <t>C01718B8-C4F8-B1C7-0F1C-6AC4FCA98611</t>
   </si>
   <si>
     <t>idElectricityCompany</t>
   </si>
   <si>
-    <t>A8C99DEF-8D99-DCC7-4218-5AF2D7CE0460</t>
+    <t>65D1AB3F-6D27-B506-D26F-5C5DBE82A48E</t>
   </si>
   <si>
     <t>idRegion</t>
   </si>
   <si>
-    <t>F40997A8-17B5-799B-4070-02102A0B1F75</t>
+    <t>8BEC7653-46CD-F2E0-9830-CA915F8C1373</t>
   </si>
   <si>
     <t>idUser</t>
   </si>
   <si>
-    <t>15F769F5-49F6-CC43-71C2-FF704C638C1A</t>
+    <t>B9CE75B2-F56A-52F4-2402-0691648374D7</t>
   </si>
   <si>
     <t>idUserDevice</t>
   </si>
   <si>
-    <t>80BC2183-0748-53E4-0D5F-6BB3362DE3C7</t>
+    <t>CBEA499C-F80C-71E9-8E6E-48362CA13E64</t>
   </si>
   <si>
     <t>kwh</t>
   </si>
   <si>
-    <t>97AA6B84-A02A-2D10-04F0-441D367ADC7B</t>
+    <t>5E11E6A3-7C82-40A3-39DE-32D3F0F53201</t>
   </si>
   <si>
     <t>lastConection</t>
   </si>
   <si>
-    <t>99C39193-C45C-BEDD-E898-36AD07AFBD6D</t>
+    <t>80B59BB6-F206-AC15-7CC1-25F0484CB116</t>
   </si>
   <si>
     <t>lastName</t>
   </si>
   <si>
-    <t>9F5DB5DB-6466-A0C5-B055-4281B4AC4172</t>
-  </si>
-  <si>
-    <t>model</t>
-  </si>
-  <si>
-    <t>CF0EC2C2-1664-01B7-89AD-3E320E5A3B23</t>
-  </si>
-  <si>
-    <t>6A543D3E-CDB2-0B84-4129-647EEE7510CB</t>
-  </si>
-  <si>
-    <t>6B0A2361-5661-B3DF-7493-049F85F7F980</t>
-  </si>
-  <si>
-    <t>35C45BEA-A44B-281F-776D-E686DB9F29F2</t>
-  </si>
-  <si>
-    <t>BC77D151-BC65-88EA-7671-5C9A0DAB542F</t>
-  </si>
-  <si>
-    <t>BE6CCBA7-246F-F003-6181-E48CD286D01F</t>
+    <t>F987AE6E-E6CD-09F8-BF70-BE0B6F44F316</t>
+  </si>
+  <si>
+    <t>0D61A7B9-DD3E-45F7-0461-0E63A231985C</t>
+  </si>
+  <si>
+    <t>5E39503B-23B3-C4BC-AF2D-6D85A3F3CAB4</t>
+  </si>
+  <si>
+    <t>FD10B671-C4FD-3C2C-5BF2-EC91B141B9E3</t>
+  </si>
+  <si>
+    <t>30BDE08B-6525-28F3-CF81-72CBF76C81D0</t>
+  </si>
+  <si>
+    <t>D1671859-BB90-F668-54B8-2F6B02EEAD4A</t>
   </si>
   <si>
     <t>numberPhone</t>
   </si>
   <si>
-    <t>42273DB2-D04F-3BFE-39EE-567370D65DE6</t>
+    <t>65CBF565-D7E8-AE54-FDB9-5EF60471D1D8</t>
   </si>
   <si>
     <t>password</t>
   </si>
   <si>
-    <t>7AB70A62-442D-8F1D-2832-B0B51B9FA5AB</t>
+    <t>6FD2AB96-64C9-268D-FA84-F63872C1C776</t>
   </si>
   <si>
     <t>power</t>
   </si>
   <si>
-    <t>B5DB67C7-D8D1-CB96-DB06-62643CBAD3F7</t>
+    <t>42C891A4-63BB-6418-FAA8-D17226EC5C01</t>
   </si>
   <si>
     <t>request</t>
   </si>
   <si>
-    <t>33C1567D-0A91-FC62-7EEC-128359F701D7</t>
+    <t>29C62EEF-B381-7868-C72D-0348822B5CBB</t>
   </si>
   <si>
     <t>secondLastName</t>
   </si>
   <si>
-    <t>9C6621B9-EF9D-CE31-14F3-F45EBABD4942</t>
+    <t>CBF3DA9C-8F51-F3C3-AF90-301736679BFB</t>
   </si>
   <si>
     <t>serialNumber</t>
   </si>
   <si>
-    <t>3A991CE4-51C1-A587-3F7B-FEB51550FC5E</t>
+    <t>BEE3DE21-220B-CD2A-B7E0-F2616C1F1A42</t>
   </si>
   <si>
     <t>serviceAdminCost</t>
   </si>
   <si>
-    <t>0C020521-4649-1A28-58F6-CE7EAD4ECC6F</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>AE5BD9F2-6313-D432-2674-B8E52865A6A2</t>
+    <t>DC25DEEB-CAED-ABDA-0F0F-4EAE61E3862B</t>
   </si>
   <si>
     <t>streetName</t>
   </si>
   <si>
-    <t>754472F2-BBC9-01D7-3065-91FA7F418345</t>
+    <t>89ED432E-DC9D-2B38-869B-AD0BFB0423DC</t>
   </si>
   <si>
     <t>streetNumber</t>
   </si>
   <si>
-    <t>1F7E614D-DB93-2852-2D76-3FD8A77404B7</t>
+    <t>8EF8F83D-FC31-6C2A-AFF0-4AAA5DEE4164</t>
   </si>
   <si>
     <t>transportCost</t>
   </si>
   <si>
-    <t>3F4F74A7-9382-56B2-EC84-398C37AC9069</t>
-  </si>
-  <si>
-    <t>Address_Comuna_FK</t>
-  </si>
-  <si>
-    <t>5E5996B1-0261-3FA0-89AF-68ED840980E4</t>
-  </si>
-  <si>
-    <t>AppUser_Address_FK</t>
-  </si>
-  <si>
-    <t>AF7482BA-CE15-D252-8566-F3A51B3B7781</t>
-  </si>
-  <si>
-    <t>AppUser_Contract_FK</t>
-  </si>
-  <si>
-    <t>6220D5A5-C299-AF56-E6BD-6F33CE588850</t>
-  </si>
-  <si>
-    <t>Comuna_Region_FK</t>
-  </si>
-  <si>
-    <t>1A7A46B4-A5BB-9963-38A7-0CA953FBC311</t>
-  </si>
-  <si>
-    <t>Contract_ElectricityCompany_FK</t>
-  </si>
-  <si>
-    <t>3F8B3718-EC6C-1C37-DEBA-A1745C212A91</t>
-  </si>
-  <si>
-    <t>Region_Country_FK</t>
-  </si>
-  <si>
-    <t>6EBE25FD-4D8B-2C25-313E-A046D9B28639</t>
-  </si>
-  <si>
-    <t>Result_UserDevice_FK</t>
-  </si>
-  <si>
-    <t>C2093F02-E1DB-0F94-5C0F-3476052B2A0F</t>
-  </si>
-  <si>
-    <t>UserDevice_AppUser_FK</t>
-  </si>
-  <si>
-    <t>FAB492A5-BE61-A93F-DBCC-ED412D0B3C9B</t>
-  </si>
-  <si>
-    <t>UserDevice_Device_FK</t>
-  </si>
-  <si>
-    <t>E458BDEB-C8FF-7F66-7A7F-E99EE778EAC1</t>
+    <t>DBBB9B51-44BE-4CB1-B4C3-03F6AA4A8B4C</t>
+  </si>
+  <si>
+    <t>Address_FK</t>
+  </si>
+  <si>
+    <t>C1351D80-F0CC-2B58-179F-42E862C66921</t>
+  </si>
+  <si>
+    <t>AppUser_FK</t>
+  </si>
+  <si>
+    <t>5E5292AD-5A7F-80CC-4265-A9E4BF7F6FD4</t>
+  </si>
+  <si>
+    <t>Comuna_FK</t>
+  </si>
+  <si>
+    <t>AD0A0EA6-D0BB-7281-1AF4-46C1B9A72B1F</t>
+  </si>
+  <si>
+    <t>Contract_FK</t>
+  </si>
+  <si>
+    <t>63048F18-7038-8AA8-09BC-D4CC9002DC1B</t>
+  </si>
+  <si>
+    <t>Country_FK</t>
+  </si>
+  <si>
+    <t>2A93B142-6F4C-4802-A894-91D9E3EE400D</t>
+  </si>
+  <si>
+    <t>Device_FK</t>
+  </si>
+  <si>
+    <t>FC33450B-7F2C-94F4-DC61-5DA2E42E21D7</t>
+  </si>
+  <si>
+    <t>DeviceModel_FK</t>
+  </si>
+  <si>
+    <t>6A10348A-0CED-BF35-52B4-A89AE138322C</t>
+  </si>
+  <si>
+    <t>ElectricityCompany_FK</t>
+  </si>
+  <si>
+    <t>75D38094-908D-7A27-6D8E-4CE19596010B</t>
+  </si>
+  <si>
+    <t>Region_FK</t>
+  </si>
+  <si>
+    <t>83C7BCD0-3CF7-4066-575B-DCF99FCC2E77</t>
+  </si>
+  <si>
+    <t>UserDevice_FK</t>
+  </si>
+  <si>
+    <t>5D314F9D-79E8-A9ED-011B-F5EB056D202D</t>
   </si>
   <si>
     <t>Address_PK</t>
   </si>
   <si>
-    <t>CFE5693B-1EF3-B65F-414A-14B1577BB8EC</t>
+    <t>FB4BED2B-2004-4F9B-BFE0-FD63710FB81F</t>
   </si>
   <si>
     <t>AppUser_PK</t>
   </si>
   <si>
-    <t>3A1D1823-99E0-5D7E-21DB-FB4A2411277F</t>
+    <t>2F0B7274-57DF-96EA-D2EE-96C79B342FA3</t>
   </si>
   <si>
     <t>Comuna_PK</t>
   </si>
   <si>
-    <t>69550BDE-7C21-2319-A0DC-41ABCB0DCCC8</t>
+    <t>5C96EEB9-3B9E-9966-C2E9-458E27E82794</t>
   </si>
   <si>
     <t>Contract_PK</t>
   </si>
   <si>
-    <t>2AC03C25-3831-5BC3-81A3-643523A60A9F</t>
+    <t>2D0CBBCF-394E-E5AD-939E-BD7D1DDEF56F</t>
   </si>
   <si>
     <t>Country_PK</t>
   </si>
   <si>
-    <t>90B82748-D561-5445-43F3-104EBD560BB6</t>
+    <t>BE326729-75E3-5E07-0E76-69AE18D1D987</t>
   </si>
   <si>
     <t>Device_PK</t>
   </si>
   <si>
-    <t>43EF62E2-4F84-8F8D-0A1E-26C238D03A72</t>
+    <t>C04DB6CF-A65C-FA70-A681-07292A82A1B7</t>
+  </si>
+  <si>
+    <t>DeviceModel_PK</t>
+  </si>
+  <si>
+    <t>01C8FE1E-6482-FFE6-7378-D1A702CF6A5E</t>
   </si>
   <si>
     <t>ElectricityCompany_PK</t>
   </si>
   <si>
-    <t>BB006E51-FB85-8346-6CC6-15335EC5A711</t>
+    <t>986AC3FA-C3B1-3891-F846-E0E0858FEC83</t>
   </si>
   <si>
     <t>PassRecoverRequest_PK</t>
   </si>
   <si>
-    <t>083497A0-D703-EC31-71B6-AA15F2192845</t>
+    <t>4933545D-1F61-8ED0-B934-64D572D93361</t>
   </si>
   <si>
     <t>Region_PK</t>
   </si>
   <si>
-    <t>0C93F24B-8280-1374-5824-C859E64ECFFF</t>
+    <t>FB03E2AC-45A7-8C05-12CC-D68C07B74E28</t>
   </si>
   <si>
     <t>Result_PK</t>
   </si>
   <si>
-    <t>9181BB6D-9394-4C19-96F6-57EAB5AF9AC7</t>
+    <t>CBC9FCC6-07E2-6B05-99C1-EEF1B9904CB5</t>
   </si>
   <si>
     <t>UserDevice_PK</t>
   </si>
   <si>
-    <t>BA848D2E-5838-25CA-B963-D9B7AFD79E9E</t>
-  </si>
-  <si>
-    <t>UK_PassRecoverRequest</t>
-  </si>
-  <si>
-    <t>F54F86BF-EDFF-D302-50C8-14B2D5BAB8D4</t>
-  </si>
-  <si>
-    <t>UK_serialNumber</t>
+    <t>90957D93-7452-534B-1634-9D8FD61DFE4C</t>
+  </si>
+  <si>
+    <t>request_UN</t>
+  </si>
+  <si>
+    <t>AF39C5BF-6E22-9FE5-D99E-5F1F4DB76760</t>
+  </si>
+  <si>
+    <t>serialNumber_UN</t>
   </si>
   <si>
     <t>LOGDT005</t>
@@ -1633,49 +1666,49 @@
     <t>Country.id</t>
   </si>
   <si>
+    <t>Unique Constraint</t>
+  </si>
+  <si>
+    <t>Device.id</t>
+  </si>
+  <si>
+    <t>Device.serialNumber</t>
+  </si>
+  <si>
+    <t>VARCHAR2 (30)</t>
+  </si>
+  <si>
+    <t>DeviceModel.id</t>
+  </si>
+  <si>
+    <t>VARCHAR2 (40)</t>
+  </si>
+  <si>
+    <t>ElectricityCompany.id</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>PassRecoverRequest.id</t>
+  </si>
+  <si>
+    <t>PassRecoverRequest.request</t>
+  </si>
+  <si>
+    <t>Region.id</t>
+  </si>
+  <si>
+    <t>Contiene mediciones de dispositivo despues de los 60 minutos</t>
+  </si>
+  <si>
+    <t>NUMBER (10,3)</t>
+  </si>
+  <si>
+    <t>Result.id</t>
+  </si>
+  <si>
     <t>VARCHAR2 (15)</t>
-  </si>
-  <si>
-    <t>Unique Constraint</t>
-  </si>
-  <si>
-    <t>Device.id</t>
-  </si>
-  <si>
-    <t>Device.serialNumber</t>
-  </si>
-  <si>
-    <t>VARCHAR2 (40)</t>
-  </si>
-  <si>
-    <t>ElectricityCompany.id</t>
-  </si>
-  <si>
-    <t>DATE</t>
-  </si>
-  <si>
-    <t>PassRecoverRequest.id</t>
-  </si>
-  <si>
-    <t>PassRecoverRequest.request</t>
-  </si>
-  <si>
-    <t>Region.id</t>
-  </si>
-  <si>
-    <t>Contiene mediciones de dispositivo despues de los 60 minutos</t>
-  </si>
-  <si>
-    <t>NUMBER (10,3)</t>
-  </si>
-  <si>
-    <t>Result.id</t>
-  </si>
-  <si>
-    <t>VARCHAR2 (30)</t>
-  </si>
-  <si>
-    <t>CHAR (1)</t>
   </si>
   <si>
     <t>UserDevice.id</t>
@@ -1868,12 +1901,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:H213"/>
+  <dimension ref="A2:H229"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.61328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.4296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.2734375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.19921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="27.0234375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="25.59375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="67.140625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="16.640625" customWidth="true" bestFit="true"/>
@@ -1888,789 +1921,789 @@
     </row>
     <row r="4" ht="18.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" ht="18.0" customHeight="true">
       <c r="A5" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="true">
       <c r="B7" t="s" s="5">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" ht="18.0" customHeight="true">
       <c r="B8" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" ht="18.0" customHeight="true">
       <c r="B9" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" ht="18.0" customHeight="true">
       <c r="B10" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" ht="18.0" customHeight="true">
       <c r="B11" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" ht="18.0" customHeight="true">
       <c r="B12" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" ht="18.0" customHeight="true">
       <c r="B15" t="s" s="5">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" ht="18.0" customHeight="true">
       <c r="B16" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" ht="18.0" customHeight="true">
       <c r="B17" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20" ht="18.0" customHeight="true">
       <c r="B20" t="s" s="5">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" ht="18.0" customHeight="true">
       <c r="B21" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" ht="18.0" customHeight="true">
       <c r="B22" s="6" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" ht="18.0" customHeight="true">
       <c r="A24" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="25" ht="18.0" customHeight="true">
       <c r="A25" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="27" ht="18.0" customHeight="true">
       <c r="B27" t="s" s="5">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" ht="18.0" customHeight="true">
       <c r="B28" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="29" ht="18.0" customHeight="true">
       <c r="B29" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" ht="18.0" customHeight="true">
       <c r="B30" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31" ht="18.0" customHeight="true">
       <c r="B31" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="32" ht="18.0" customHeight="true">
       <c r="B32" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33" ht="18.0" customHeight="true">
       <c r="B33" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" ht="18.0" customHeight="true">
       <c r="B34" s="6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35" ht="18.0" customHeight="true">
       <c r="B35" s="6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" ht="18.0" customHeight="true">
       <c r="B36" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="37" ht="18.0" customHeight="true">
       <c r="B37" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" ht="18.0" customHeight="true">
       <c r="B38" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="41" ht="18.0" customHeight="true">
       <c r="B41" t="s" s="5">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="42" ht="18.0" customHeight="true">
       <c r="B42" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="43" ht="18.0" customHeight="true">
       <c r="B43" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="46" ht="18.0" customHeight="true">
       <c r="B46" t="s" s="5">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47" ht="18.0" customHeight="true">
       <c r="B47" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="48" ht="18.0" customHeight="true">
       <c r="B48" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="49" ht="18.0" customHeight="true">
       <c r="B49" s="6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="51" ht="18.0" customHeight="true">
       <c r="A51" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52" ht="18.0" customHeight="true">
       <c r="A52" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="54" ht="18.0" customHeight="true">
       <c r="B54" t="s" s="5">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="55" ht="18.0" customHeight="true">
       <c r="B55" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="56" ht="18.0" customHeight="true">
       <c r="B56" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" ht="18.0" customHeight="true">
       <c r="B57" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" ht="18.0" customHeight="true">
@@ -2678,488 +2711,488 @@
         <v>3</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" ht="18.0" customHeight="true">
       <c r="B61" t="s" s="5">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="62" ht="18.0" customHeight="true">
       <c r="B62" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" ht="18.0" customHeight="true">
       <c r="B63" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" ht="18.0" customHeight="true">
       <c r="B66" t="s" s="5">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="67" ht="18.0" customHeight="true">
       <c r="B67" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" ht="18.0" customHeight="true">
       <c r="B68" s="6" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="70" ht="18.0" customHeight="true">
       <c r="A70" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" ht="18.0" customHeight="true">
       <c r="A71" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="73" ht="18.0" customHeight="true">
       <c r="B73" t="s" s="5">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" ht="18.0" customHeight="true">
       <c r="B74" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" ht="18.0" customHeight="true">
       <c r="B75" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="76" ht="18.0" customHeight="true">
       <c r="B76" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="77" ht="18.0" customHeight="true">
       <c r="B77" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="78" ht="18.0" customHeight="true">
       <c r="B78" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="79" ht="18.0" customHeight="true">
       <c r="B79" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="82" ht="18.0" customHeight="true">
       <c r="B82" t="s" s="5">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" ht="18.0" customHeight="true">
       <c r="B83" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="84" ht="18.0" customHeight="true">
       <c r="B84" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="87" ht="18.0" customHeight="true">
       <c r="B87" t="s" s="5">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" ht="18.0" customHeight="true">
       <c r="B88" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="89" ht="18.0" customHeight="true">
       <c r="B89" s="6" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="91" ht="18.0" customHeight="true">
       <c r="A91" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="92" ht="18.0" customHeight="true">
       <c r="A92" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="94" ht="18.0" customHeight="true">
       <c r="B94" t="s" s="5">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="95" ht="18.0" customHeight="true">
       <c r="B95" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="96" ht="18.0" customHeight="true">
       <c r="B96" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="97" ht="18.0" customHeight="true">
@@ -3167,1582 +3200,1746 @@
         <v>3</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="100" ht="18.0" customHeight="true">
       <c r="B100" t="s" s="5">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="101" ht="18.0" customHeight="true">
       <c r="B101" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="102" ht="18.0" customHeight="true">
       <c r="B102" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="104" ht="18.0" customHeight="true">
       <c r="A104" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="105" ht="18.0" customHeight="true">
       <c r="A105" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="107" ht="18.0" customHeight="true">
       <c r="B107" t="s" s="5">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="108" ht="18.0" customHeight="true">
       <c r="B108" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="109" ht="18.0" customHeight="true">
       <c r="B109" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="110" ht="18.0" customHeight="true">
       <c r="B110" s="6" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="111" ht="18.0" customHeight="true">
       <c r="B111" s="6" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="112" ht="18.0" customHeight="true">
-      <c r="B112" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="D112" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G112" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="114" ht="18.0" customHeight="true">
+      <c r="B114" t="s" s="5">
+        <v>343</v>
       </c>
     </row>
     <row r="115" ht="18.0" customHeight="true">
-      <c r="B115" t="s" s="5">
-        <v>338</v>
+      <c r="B115" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="116" ht="18.0" customHeight="true">
-      <c r="B116" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G116" s="3" t="s">
-        <v>324</v>
+      <c r="B116" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="117" ht="18.0" customHeight="true">
       <c r="B117" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>340</v>
+        <v>367</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="118" ht="18.0" customHeight="true">
-      <c r="B118" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="G118" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="120" ht="18.0" customHeight="true">
-      <c r="A120" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E120" s="2" t="s">
+      <c r="B120" t="s" s="5">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="121" ht="18.0" customHeight="true">
+      <c r="B121" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="122" ht="18.0" customHeight="true">
+      <c r="B122" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="124" ht="18.0" customHeight="true">
+      <c r="A124" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F120" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="121" ht="18.0" customHeight="true">
-      <c r="A121" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B121" s="6" t="s">
+      <c r="B124" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="125" ht="18.0" customHeight="true">
+      <c r="A125" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B125" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C121" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="123" ht="18.0" customHeight="true">
-      <c r="B123" t="s" s="5">
+      <c r="C125" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="127" ht="18.0" customHeight="true">
+      <c r="B127" t="s" s="5">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="128" ht="18.0" customHeight="true">
+      <c r="B128" s="3" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="124" ht="18.0" customHeight="true">
-      <c r="B124" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C124" s="3" t="s">
+      <c r="C128" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="129" ht="18.0" customHeight="true">
+      <c r="B129" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H129" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="130" ht="18.0" customHeight="true">
+      <c r="B130" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="133" ht="18.0" customHeight="true">
+      <c r="B133" t="s" s="5">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="134" ht="18.0" customHeight="true">
+      <c r="B134" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="135" ht="18.0" customHeight="true">
+      <c r="B135" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G135" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="137" ht="18.0" customHeight="true">
+      <c r="A137" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C137" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D124" s="3" t="s">
+      <c r="D137" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="138" ht="18.0" customHeight="true">
+      <c r="A138" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="140" ht="18.0" customHeight="true">
+      <c r="B140" t="s" s="5">
         <v>332</v>
       </c>
-      <c r="E124" s="3" t="s">
+    </row>
+    <row r="141" ht="18.0" customHeight="true">
+      <c r="B141" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="142" ht="18.0" customHeight="true">
+      <c r="B142" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C142" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="F124" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G124" s="3" t="s">
+      <c r="D142" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="143" ht="18.0" customHeight="true">
+      <c r="B143" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H143" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="146" ht="18.0" customHeight="true">
+      <c r="B146" t="s" s="5">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="147" ht="18.0" customHeight="true">
+      <c r="B147" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="148" ht="18.0" customHeight="true">
+      <c r="B148" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="150" ht="18.0" customHeight="true">
+      <c r="A150" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="151" ht="18.0" customHeight="true">
+      <c r="A151" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="153" ht="18.0" customHeight="true">
+      <c r="B153" t="s" s="5">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="154" ht="18.0" customHeight="true">
+      <c r="B154" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D154" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="H124" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="125" ht="18.0" customHeight="true">
-      <c r="B125" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C125" s="8" t="s">
+      <c r="E154" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="H154" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="D125" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="F125" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G125" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H125" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="126" ht="18.0" customHeight="true">
-      <c r="B126" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C126" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="D126" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F126" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G126" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="129" ht="18.0" customHeight="true">
-      <c r="B129" t="s" s="5">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="130" ht="18.0" customHeight="true">
-      <c r="B130" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="F130" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G130" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="131" ht="18.0" customHeight="true">
-      <c r="B131" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="E131" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="F131" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="G131" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="133" ht="18.0" customHeight="true">
-      <c r="A133" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="134" ht="18.0" customHeight="true">
-      <c r="A134" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C134" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="E134" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="136" ht="18.0" customHeight="true">
-      <c r="B136" t="s" s="5">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="137" ht="18.0" customHeight="true">
-      <c r="B137" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D137" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="F137" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G137" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H137" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="138" ht="18.0" customHeight="true">
-      <c r="B138" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="D138" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E138" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F138" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G138" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="139" ht="18.0" customHeight="true">
-      <c r="B139" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="D139" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E139" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F139" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G139" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H139" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="140" ht="18.0" customHeight="true">
-      <c r="B140" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="D140" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E140" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="F140" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G140" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="141" ht="18.0" customHeight="true">
-      <c r="B141" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="D141" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E141" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F141" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G141" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H141" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="144" ht="18.0" customHeight="true">
-      <c r="B144" t="s" s="5">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="145" ht="18.0" customHeight="true">
-      <c r="B145" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="F145" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G145" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="146" ht="18.0" customHeight="true">
-      <c r="B146" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D146" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="E146" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="F146" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="G146" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="147" ht="18.0" customHeight="true">
-      <c r="B147" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C147" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D147" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="E147" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="F147" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="G147" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="149" ht="18.0" customHeight="true">
-      <c r="A149" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="150" ht="18.0" customHeight="true">
-      <c r="A150" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="E150" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="F150" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="152" ht="18.0" customHeight="true">
-      <c r="B152" t="s" s="5">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="153" ht="18.0" customHeight="true">
-      <c r="B153" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="E153" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="F153" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G153" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H153" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="154" ht="18.0" customHeight="true">
-      <c r="B154" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="D154" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E154" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="F154" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G154" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="155" ht="18.0" customHeight="true">
       <c r="B155" s="6" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="156" ht="18.0" customHeight="true">
       <c r="B156" s="6" t="s">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="D156" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="157" ht="18.0" customHeight="true">
+      <c r="B157" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H157" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="158" ht="18.0" customHeight="true">
+      <c r="B158" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H158" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="161" ht="18.0" customHeight="true">
+      <c r="B161" t="s" s="5">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="162" ht="18.0" customHeight="true">
+      <c r="B162" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="163" ht="18.0" customHeight="true">
+      <c r="B163" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G163" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="164" ht="18.0" customHeight="true">
+      <c r="B164" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G164" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="166" ht="18.0" customHeight="true">
+      <c r="A166" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="167" ht="18.0" customHeight="true">
+      <c r="A167" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F167" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="169" ht="18.0" customHeight="true">
+      <c r="B169" t="s" s="5">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="170" ht="18.0" customHeight="true">
+      <c r="B170" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C170" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="E156" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F156" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G156" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="159" ht="18.0" customHeight="true">
-      <c r="B159" t="s" s="5">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="160" ht="18.0" customHeight="true">
-      <c r="B160" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D160" s="3" t="s">
+      <c r="D170" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E170" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="E160" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="F160" s="3" t="s">
+      <c r="F170" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G170" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="G160" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="161" ht="18.0" customHeight="true">
-      <c r="B161" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C161" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="E161" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F161" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="G161" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="164" ht="18.0" customHeight="true">
-      <c r="B164" t="s" s="5">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="165" ht="18.0" customHeight="true">
-      <c r="B165" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E165" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F165" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="G165" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H165" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="166" ht="18.0" customHeight="true">
-      <c r="B166" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C166" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D166" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E166" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="F166" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="G166" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="H166" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="168" ht="18.0" customHeight="true">
-      <c r="A168" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="169" ht="18.0" customHeight="true">
-      <c r="A169" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B169" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C169" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D169" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="E169" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="F169" s="6" t="s">
-        <v>321</v>
+      <c r="H170" s="3" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="171" ht="18.0" customHeight="true">
-      <c r="B171" t="s" s="5">
-        <v>327</v>
+      <c r="B171" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E171" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H171" s="6" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="172" ht="18.0" customHeight="true">
-      <c r="B172" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C172" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D172" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="E172" s="3" t="s">
+      <c r="B172" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C172" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="F172" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H172" s="3" t="s">
-        <v>324</v>
+      <c r="D172" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E172" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H172" s="6" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="173" ht="18.0" customHeight="true">
       <c r="B173" s="6" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F173" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="174" ht="18.0" customHeight="true">
-      <c r="B174" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C174" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="D174" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="E174" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F174" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G174" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H174" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="175" ht="18.0" customHeight="true">
-      <c r="B175" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C175" s="8" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="176" ht="18.0" customHeight="true">
+      <c r="B176" t="s" s="5">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="177" ht="18.0" customHeight="true">
+      <c r="B177" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G177" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="D175" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E175" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="F175" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G175" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H175" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="176" ht="18.0" customHeight="true">
-      <c r="B176" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C176" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="D176" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E176" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F176" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="G176" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H176" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="177" ht="18.0" customHeight="true">
-      <c r="B177" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C177" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="D177" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="E177" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F177" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G177" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H177" s="6" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="178" ht="18.0" customHeight="true">
       <c r="B178" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C178" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="D178" s="8" t="s">
-        <v>335</v>
+        <v>326</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>345</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F178" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G178" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H178" s="6" t="s">
-        <v>321</v>
+        <v>377</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G178" s="6" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="181" ht="18.0" customHeight="true">
       <c r="B181" t="s" s="5">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="182" ht="18.0" customHeight="true">
       <c r="B182" s="3" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>324</v>
+        <v>352</v>
+      </c>
+      <c r="H182" s="3" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="183" ht="18.0" customHeight="true">
       <c r="B183" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C183" s="6" t="s">
-        <v>171</v>
+        <v>144</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="E183" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="F183" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="H183" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="185" ht="18.0" customHeight="true">
+      <c r="A185" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="186" ht="18.0" customHeight="true">
+      <c r="A186" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="188" ht="18.0" customHeight="true">
+      <c r="B188" t="s" s="5">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="189" ht="18.0" customHeight="true">
+      <c r="B189" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="H189" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="190" ht="18.0" customHeight="true">
+      <c r="B190" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H190" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="191" ht="18.0" customHeight="true">
+      <c r="B191" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C191" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="F183" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="G183" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="186" ht="18.0" customHeight="true">
-      <c r="B186" t="s" s="5">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="187" ht="18.0" customHeight="true">
-      <c r="B187" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C187" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E187" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F187" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H187" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="188" ht="18.0" customHeight="true">
-      <c r="B188" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C188" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D188" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="E188" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="F188" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="G188" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="190" ht="18.0" customHeight="true">
-      <c r="A190" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D190" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E190" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F190" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="191" ht="18.0" customHeight="true">
-      <c r="A191" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C191" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D191" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="E191" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="F191" s="6" t="s">
-        <v>321</v>
+      <c r="D191" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H191" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="192" ht="18.0" customHeight="true">
+      <c r="B192" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D192" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H192" s="6" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="193" ht="18.0" customHeight="true">
-      <c r="B193" t="s" s="5">
-        <v>327</v>
+      <c r="B193" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D193" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H193" s="6" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="194" ht="18.0" customHeight="true">
-      <c r="B194" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C194" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D194" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="E194" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="F194" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G194" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H194" s="3" t="s">
-        <v>324</v>
+      <c r="B194" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="D194" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H194" s="6" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="195" ht="18.0" customHeight="true">
       <c r="B195" s="6" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E195" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F195" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H195" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="196" ht="18.0" customHeight="true">
-      <c r="B196" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C196" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="D196" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E196" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F196" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G196" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H196" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="197" ht="18.0" customHeight="true">
-      <c r="B197" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C197" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="D197" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="E197" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F197" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G197" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H197" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="198" ht="18.0" customHeight="true">
-      <c r="B198" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C198" s="8" t="s">
+      <c r="B198" t="s" s="5">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="199" ht="18.0" customHeight="true">
+      <c r="B199" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G199" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="D198" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E198" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="F198" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G198" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H198" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="199" ht="18.0" customHeight="true">
-      <c r="B199" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C199" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="D199" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E199" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F199" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="G199" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H199" s="6" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="200" ht="18.0" customHeight="true">
       <c r="B200" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C200" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="F200" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G200" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="203" ht="18.0" customHeight="true">
+      <c r="B203" t="s" s="5">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="204" ht="18.0" customHeight="true">
+      <c r="B204" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="H204" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="D200" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E200" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F200" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="G200" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H200" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="201" ht="18.0" customHeight="true">
-      <c r="B201" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C201" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="D201" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E201" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F201" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G201" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H201" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="202" ht="18.0" customHeight="true">
-      <c r="B202" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C202" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="D202" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E202" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="F202" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G202" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="H202" s="6" t="s">
-        <v>321</v>
-      </c>
     </row>
     <row r="205" ht="18.0" customHeight="true">
-      <c r="B205" t="s" s="5">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="206" ht="18.0" customHeight="true">
-      <c r="B206" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C206" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D206" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="E206" s="3" t="s">
+      <c r="B205" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C205" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E205" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G205" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="H205" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="207" ht="18.0" customHeight="true">
+      <c r="A207" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B207" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F206" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G206" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="207" ht="18.0" customHeight="true">
-      <c r="B207" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C207" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="D207" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="E207" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="F207" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="G207" s="6" t="s">
-        <v>321</v>
+      <c r="C207" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="208" ht="18.0" customHeight="true">
+      <c r="A208" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C208" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="E208" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F208" s="6" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="210" ht="18.0" customHeight="true">
       <c r="B210" t="s" s="5">
-        <v>343</v>
+        <v>332</v>
       </c>
     </row>
     <row r="211" ht="18.0" customHeight="true">
       <c r="B211" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="212" ht="18.0" customHeight="true">
       <c r="B212" s="6" t="s">
-        <v>149</v>
+        <v>51</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D212" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E212" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="F212" s="7" t="s">
-        <v>333</v>
+        <v>381</v>
+      </c>
+      <c r="D212" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E212" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F212" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="213" ht="18.0" customHeight="true">
       <c r="B213" s="6" t="s">
-        <v>151</v>
+        <v>57</v>
       </c>
       <c r="C213" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="D213" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E213" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F213" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G213" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H213" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="214" ht="18.0" customHeight="true">
+      <c r="B214" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C214" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="D214" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E214" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F214" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G214" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H214" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="215" ht="18.0" customHeight="true">
+      <c r="B215" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C215" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D215" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E215" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F215" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G215" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H215" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="216" ht="18.0" customHeight="true">
+      <c r="B216" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C216" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D216" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E216" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F216" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="G216" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H216" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="217" ht="18.0" customHeight="true">
+      <c r="B217" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C217" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D217" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E217" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F217" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="G217" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H217" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="218" ht="18.0" customHeight="true">
+      <c r="B218" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C218" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="D218" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E218" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F218" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G218" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H218" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="221" ht="18.0" customHeight="true">
+      <c r="B221" t="s" s="5">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="222" ht="18.0" customHeight="true">
+      <c r="B222" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="223" ht="18.0" customHeight="true">
+      <c r="B223" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E223" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="F223" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G223" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="226" ht="18.0" customHeight="true">
+      <c r="B226" t="s" s="5">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="227" ht="18.0" customHeight="true">
+      <c r="B227" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="H227" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="228" ht="18.0" customHeight="true">
+      <c r="B228" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C228" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E228" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="F228" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G228" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="H228" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="229" ht="18.0" customHeight="true">
+      <c r="B229" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C229" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D213" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E213" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="F213" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="G213" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="H213" s="6" t="s">
-        <v>321</v>
+      <c r="D229" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E229" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="F229" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G229" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="H229" s="6" t="s">
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -4750,7 +4947,7 @@
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <dataValidations count="51">
+  <dataValidations count="56">
     <dataValidation type="list" sqref="A5" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
@@ -4829,79 +5026,94 @@
     <dataValidation type="list" sqref="A105" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
+    <dataValidation type="list" sqref="B116" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>null!B1:B65000</formula1>
+    </dataValidation>
     <dataValidation type="list" sqref="B117" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B118" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D122" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>lov_4!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E122" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="F122" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="A125" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A121" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B135" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B131" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A138" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A134" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B148" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B146" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A151" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B147" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B163" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A150" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B164" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B161" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A167" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D166" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B178" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+      <formula1>null!B1:B65000</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="D183" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E166" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E183" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F166" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F183" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A169" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A186" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B183" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B200" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D188" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D205" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E188" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E205" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F188" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F205" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A191" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A208" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B207" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B223" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D212" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D228" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D213" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D229" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E212" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E228" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E213" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E229" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F212" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F228" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F213" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F229" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4918,18 +5130,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -5077,7 +5289,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5166,6 +5378,14 @@
       </c>
       <c r="B11" s="8" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -5181,295 +5401,295 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>3</v>
@@ -5477,7 +5697,7 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>3</v>
@@ -5485,7 +5705,7 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>3</v>
@@ -5493,7 +5713,7 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>3</v>
@@ -5501,90 +5721,90 @@
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>113</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -5595,79 +5815,87 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -5678,95 +5906,103 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>173</v>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -5782,18 +6018,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -5809,546 +6045,546 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -6364,10 +6600,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
@@ -778,45 +778,45 @@
     <t>firstName</t>
   </si>
   <si>
+    <t>E4FC695C-DB7F-273E-0C47-C01648108DA5</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>914BC5D9-89EB-EF1A-FB0C-E191FFDF845A</t>
+  </si>
+  <si>
+    <t>5F72E1E0-0043-42F1-DBCE-53EE47EBDC8C</t>
+  </si>
+  <si>
+    <t>88D79E68-CA48-4058-D21F-BA79CABB78AB</t>
+  </si>
+  <si>
+    <t>7ABD1485-D415-29B3-802F-B235595EFE87</t>
+  </si>
+  <si>
+    <t>B79CB950-5BF3-4DC8-8B7C-D7770260C2F4</t>
+  </si>
+  <si>
+    <t>56F05333-4945-447A-1128-61D911628D2D</t>
+  </si>
+  <si>
+    <t>72E7BD72-71EA-49B3-00BF-7728CE9660FC</t>
+  </si>
+  <si>
+    <t>96F0A8B5-8BE1-9346-540D-B1A5DB9E97E8</t>
+  </si>
+  <si>
     <t>275B3005-CA60-8E26-87EB-EC4C9886EC39</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>5F72E1E0-0043-42F1-DBCE-53EE47EBDC8C</t>
-  </si>
-  <si>
-    <t>88D79E68-CA48-4058-D21F-BA79CABB78AB</t>
-  </si>
-  <si>
-    <t>E4FC695C-DB7F-273E-0C47-C01648108DA5</t>
-  </si>
-  <si>
-    <t>B79CB950-5BF3-4DC8-8B7C-D7770260C2F4</t>
-  </si>
-  <si>
-    <t>7ABD1485-D415-29B3-802F-B235595EFE87</t>
-  </si>
-  <si>
-    <t>72E7BD72-71EA-49B3-00BF-7728CE9660FC</t>
+    <t>AEC573F9-790B-6348-921B-492CF00715BB</t>
   </si>
   <si>
     <t>0417C238-82AC-A5B2-88E7-F2BB25C183A5</t>
   </si>
   <si>
-    <t>AEC573F9-790B-6348-921B-492CF00715BB</t>
-  </si>
-  <si>
-    <t>96F0A8B5-8BE1-9346-540D-B1A5DB9E97E8</t>
-  </si>
-  <si>
-    <t>914BC5D9-89EB-EF1A-FB0C-E191FFDF845A</t>
-  </si>
-  <si>
-    <t>56F05333-4945-447A-1128-61D911628D2D</t>
-  </si>
-  <si>
     <t>1B6B8678-D75A-AE62-7CA1-87F8E6BEC7CB</t>
   </si>
   <si>
@@ -886,7 +886,7 @@
     <t>5E11E6A3-7C82-40A3-39DE-32D3F0F53201</t>
   </si>
   <si>
-    <t>lastConection</t>
+    <t>lastConnection</t>
   </si>
   <si>
     <t>80B59BB6-F206-AC15-7CC1-25F0484CB116</t>
@@ -895,19 +895,19 @@
     <t>lastName</t>
   </si>
   <si>
+    <t>0D61A7B9-DD3E-45F7-0461-0E63A231985C</t>
+  </si>
+  <si>
     <t>F987AE6E-E6CD-09F8-BF70-BE0B6F44F316</t>
   </si>
   <si>
-    <t>0D61A7B9-DD3E-45F7-0461-0E63A231985C</t>
-  </si>
-  <si>
     <t>5E39503B-23B3-C4BC-AF2D-6D85A3F3CAB4</t>
   </si>
   <si>
+    <t>30BDE08B-6525-28F3-CF81-72CBF76C81D0</t>
+  </si>
+  <si>
     <t>FD10B671-C4FD-3C2C-5BF2-EC91B141B9E3</t>
-  </si>
-  <si>
-    <t>30BDE08B-6525-28F3-CF81-72CBF76C81D0</t>
   </si>
   <si>
     <t>D1671859-BB90-F668-54B8-2F6B02EEAD4A</t>

--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/Diccionario de datos BD.xlsx
@@ -446,113 +446,101 @@
     </comment>
     <comment ref="B190" authorId="0">
       <text>
-        <t>ObjectID:1E82BF4A-BAF2-4673-AE94-7E8E775F444C;
+        <t>ObjectID:AEC573F9-790B-6348-921B-492CF00715BB;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
     <comment ref="B191" authorId="0">
+      <text>
+        <t>ObjectID:B9CE75B2-F56A-52F4-2402-0691648374D7;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B192" authorId="0">
+      <text>
+        <t>ObjectID:CBEA499C-F80C-71E9-8E6E-48362CA13E64;
+Class:oracle.dbtools.crest.model.design.relational.Column</t>
+      </text>
+    </comment>
+    <comment ref="B193" authorId="0">
       <text>
         <t>ObjectID:0B4AB6A2-0A24-0EE4-0AC3-C3091003F21A;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B192" authorId="0">
-      <text>
-        <t>ObjectID:AEC573F9-790B-6348-921B-492CF00715BB;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B193" authorId="0">
-      <text>
-        <t>ObjectID:B9CE75B2-F56A-52F4-2402-0691648374D7;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B194" authorId="0">
-      <text>
-        <t>ObjectID:CBEA499C-F80C-71E9-8E6E-48362CA13E64;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B195" authorId="0">
-      <text>
-        <t>ObjectID:6FD2AB96-64C9-268D-FA84-F63872C1C776;
-Class:oracle.dbtools.crest.model.design.relational.Column</t>
-      </text>
-    </comment>
-    <comment ref="B200" authorId="0">
+    <comment ref="B198" authorId="0">
       <text>
         <t>ObjectID:FB03E2AC-45A7-8C05-12CC-D68C07B74E28;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B205" authorId="0">
+    <comment ref="B203" authorId="0">
       <text>
         <t>ObjectID:83C7BCD0-3CF7-4066-575B-DCF99FCC2E77;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="A208" authorId="0">
+    <comment ref="A206" authorId="0">
       <text>
         <t>ObjectID:287B4946-F23B-8355-D758-108C565A3A9F;
 Class:oracle.dbtools.crest.model.design.relational.Table</t>
       </text>
     </comment>
-    <comment ref="B212" authorId="0">
+    <comment ref="B210" authorId="0">
       <text>
         <t>ObjectID:131DDB81-1720-6820-5F6D-0B072C3417E4;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B213" authorId="0">
+    <comment ref="B211" authorId="0">
       <text>
         <t>ObjectID:14D36442-EC52-B1D0-75DF-002E0A9AF76F;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B214" authorId="0">
+    <comment ref="B212" authorId="0">
       <text>
         <t>ObjectID:06DE242F-8E38-E7BC-628D-6635622276ED;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B215" authorId="0">
+    <comment ref="B213" authorId="0">
       <text>
         <t>ObjectID:914BC5D9-89EB-EF1A-FB0C-E191FFDF845A;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B216" authorId="0">
+    <comment ref="B214" authorId="0">
       <text>
         <t>ObjectID:8BBEBBE6-9B7F-C0C9-0A4D-4D9BDCE6FB56;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B217" authorId="0">
+    <comment ref="B215" authorId="0">
       <text>
         <t>ObjectID:8BEC7653-46CD-F2E0-9830-CA915F8C1373;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B218" authorId="0">
+    <comment ref="B216" authorId="0">
       <text>
         <t>ObjectID:5E11E6A3-7C82-40A3-39DE-32D3F0F53201;
 Class:oracle.dbtools.crest.model.design.relational.Column</t>
       </text>
     </comment>
-    <comment ref="B223" authorId="0">
+    <comment ref="B221" authorId="0">
       <text>
         <t>ObjectID:CBC9FCC6-07E2-6B05-99C1-EEF1B9904CB5;
 Class:oracle.dbtools.crest.model.design.relational.Index</t>
       </text>
     </comment>
-    <comment ref="B228" authorId="0">
+    <comment ref="B226" authorId="0">
       <text>
         <t>ObjectID:C1351D80-F0CC-2B58-179F-42E862C66921;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
       </text>
     </comment>
-    <comment ref="B229" authorId="0">
+    <comment ref="B227" authorId="0">
       <text>
         <t>ObjectID:2A93B142-6F4C-4802-A894-91D9E3EE400D;
 Class:oracle.dbtools.crest.model.design.relational.FKIndexAssociation</t>
@@ -563,7 +551,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="379">
   <si>
     <t>Diccionario de datos BD</t>
   </si>
@@ -721,12 +709,6 @@
     <t>alias</t>
   </si>
   <si>
-    <t>1E82BF4A-BAF2-4673-AE94-7E8E775F444C</t>
-  </si>
-  <si>
-    <t>ampere</t>
-  </si>
-  <si>
     <t>CB80906D-16D9-27DE-3A8B-67BA6FF423C4</t>
   </si>
   <si>
@@ -739,160 +721,160 @@
     <t>creationDate</t>
   </si>
   <si>
+    <t>06DE242F-8E38-E7BC-628D-6635622276ED</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>C13D6EC9-6DB9-37D7-E47F-E93D182529F3</t>
+  </si>
+  <si>
+    <t>electricityCost</t>
+  </si>
+  <si>
+    <t>26A7036D-E4B0-DE89-14BA-8E97F98305C6</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>0BE4BE77-A5F4-D18F-417B-AD7AD0783EFD</t>
+  </si>
+  <si>
+    <t>F5EB8F8E-AD04-1AEB-7179-04A01CCC1CD1</t>
+  </si>
+  <si>
+    <t>expireDateTime</t>
+  </si>
+  <si>
+    <t>ACBC239B-65C0-D6B1-CB1A-BEAE5FBA9B25</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>E4FC695C-DB7F-273E-0C47-C01648108DA5</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>914BC5D9-89EB-EF1A-FB0C-E191FFDF845A</t>
+  </si>
+  <si>
+    <t>5F72E1E0-0043-42F1-DBCE-53EE47EBDC8C</t>
+  </si>
+  <si>
+    <t>88D79E68-CA48-4058-D21F-BA79CABB78AB</t>
+  </si>
+  <si>
+    <t>7ABD1485-D415-29B3-802F-B235595EFE87</t>
+  </si>
+  <si>
+    <t>B79CB950-5BF3-4DC8-8B7C-D7770260C2F4</t>
+  </si>
+  <si>
+    <t>56F05333-4945-447A-1128-61D911628D2D</t>
+  </si>
+  <si>
+    <t>72E7BD72-71EA-49B3-00BF-7728CE9660FC</t>
+  </si>
+  <si>
+    <t>96F0A8B5-8BE1-9346-540D-B1A5DB9E97E8</t>
+  </si>
+  <si>
+    <t>275B3005-CA60-8E26-87EB-EC4C9886EC39</t>
+  </si>
+  <si>
+    <t>AEC573F9-790B-6348-921B-492CF00715BB</t>
+  </si>
+  <si>
+    <t>0417C238-82AC-A5B2-88E7-F2BB25C183A5</t>
+  </si>
+  <si>
+    <t>1B6B8678-D75A-AE62-7CA1-87F8E6BEC7CB</t>
+  </si>
+  <si>
+    <t>idAddress</t>
+  </si>
+  <si>
+    <t>F1720C33-5E86-A579-0090-ED7F4D559190</t>
+  </si>
+  <si>
+    <t>idComuna</t>
+  </si>
+  <si>
+    <t>B8365782-DAE5-7D37-5A61-03CB7CAF3EBA</t>
+  </si>
+  <si>
+    <t>idContract</t>
+  </si>
+  <si>
+    <t>49234B3D-D282-A611-1B13-14B049DBDA32</t>
+  </si>
+  <si>
+    <t>idCountry</t>
+  </si>
+  <si>
+    <t>8BBEBBE6-9B7F-C0C9-0A4D-4D9BDCE6FB56</t>
+  </si>
+  <si>
+    <t>idDevice</t>
+  </si>
+  <si>
+    <t>894BB5B3-3F0B-21E8-31BF-33DB6B10E248</t>
+  </si>
+  <si>
+    <t>idDeviceModel</t>
+  </si>
+  <si>
+    <t>C01718B8-C4F8-B1C7-0F1C-6AC4FCA98611</t>
+  </si>
+  <si>
+    <t>idElectricityCompany</t>
+  </si>
+  <si>
+    <t>65D1AB3F-6D27-B506-D26F-5C5DBE82A48E</t>
+  </si>
+  <si>
+    <t>idRegion</t>
+  </si>
+  <si>
+    <t>8BEC7653-46CD-F2E0-9830-CA915F8C1373</t>
+  </si>
+  <si>
+    <t>idUser</t>
+  </si>
+  <si>
+    <t>B9CE75B2-F56A-52F4-2402-0691648374D7</t>
+  </si>
+  <si>
+    <t>idUserDevice</t>
+  </si>
+  <si>
+    <t>CBEA499C-F80C-71E9-8E6E-48362CA13E64</t>
+  </si>
+  <si>
+    <t>kws</t>
+  </si>
+  <si>
+    <t>5E11E6A3-7C82-40A3-39DE-32D3F0F53201</t>
+  </si>
+  <si>
+    <t>lastConnection</t>
+  </si>
+  <si>
+    <t>80B59BB6-F206-AC15-7CC1-25F0484CB116</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
     <t>0B4AB6A2-0A24-0EE4-0AC3-C3091003F21A</t>
   </si>
   <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>06DE242F-8E38-E7BC-628D-6635622276ED</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>C13D6EC9-6DB9-37D7-E47F-E93D182529F3</t>
-  </si>
-  <si>
-    <t>electricityCost</t>
-  </si>
-  <si>
-    <t>26A7036D-E4B0-DE89-14BA-8E97F98305C6</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>0BE4BE77-A5F4-D18F-417B-AD7AD0783EFD</t>
-  </si>
-  <si>
-    <t>F5EB8F8E-AD04-1AEB-7179-04A01CCC1CD1</t>
-  </si>
-  <si>
-    <t>expireDateTime</t>
-  </si>
-  <si>
-    <t>ACBC239B-65C0-D6B1-CB1A-BEAE5FBA9B25</t>
-  </si>
-  <si>
-    <t>firstName</t>
-  </si>
-  <si>
-    <t>E4FC695C-DB7F-273E-0C47-C01648108DA5</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>914BC5D9-89EB-EF1A-FB0C-E191FFDF845A</t>
-  </si>
-  <si>
-    <t>5F72E1E0-0043-42F1-DBCE-53EE47EBDC8C</t>
-  </si>
-  <si>
-    <t>88D79E68-CA48-4058-D21F-BA79CABB78AB</t>
-  </si>
-  <si>
-    <t>7ABD1485-D415-29B3-802F-B235595EFE87</t>
-  </si>
-  <si>
-    <t>B79CB950-5BF3-4DC8-8B7C-D7770260C2F4</t>
-  </si>
-  <si>
-    <t>56F05333-4945-447A-1128-61D911628D2D</t>
-  </si>
-  <si>
-    <t>72E7BD72-71EA-49B3-00BF-7728CE9660FC</t>
-  </si>
-  <si>
-    <t>96F0A8B5-8BE1-9346-540D-B1A5DB9E97E8</t>
-  </si>
-  <si>
-    <t>275B3005-CA60-8E26-87EB-EC4C9886EC39</t>
-  </si>
-  <si>
-    <t>AEC573F9-790B-6348-921B-492CF00715BB</t>
-  </si>
-  <si>
-    <t>0417C238-82AC-A5B2-88E7-F2BB25C183A5</t>
-  </si>
-  <si>
-    <t>1B6B8678-D75A-AE62-7CA1-87F8E6BEC7CB</t>
-  </si>
-  <si>
-    <t>idAddress</t>
-  </si>
-  <si>
-    <t>F1720C33-5E86-A579-0090-ED7F4D559190</t>
-  </si>
-  <si>
-    <t>idComuna</t>
-  </si>
-  <si>
-    <t>B8365782-DAE5-7D37-5A61-03CB7CAF3EBA</t>
-  </si>
-  <si>
-    <t>idContract</t>
-  </si>
-  <si>
-    <t>49234B3D-D282-A611-1B13-14B049DBDA32</t>
-  </si>
-  <si>
-    <t>idCountry</t>
-  </si>
-  <si>
-    <t>8BBEBBE6-9B7F-C0C9-0A4D-4D9BDCE6FB56</t>
-  </si>
-  <si>
-    <t>idDevice</t>
-  </si>
-  <si>
-    <t>894BB5B3-3F0B-21E8-31BF-33DB6B10E248</t>
-  </si>
-  <si>
-    <t>idDeviceModel</t>
-  </si>
-  <si>
-    <t>C01718B8-C4F8-B1C7-0F1C-6AC4FCA98611</t>
-  </si>
-  <si>
-    <t>idElectricityCompany</t>
-  </si>
-  <si>
-    <t>65D1AB3F-6D27-B506-D26F-5C5DBE82A48E</t>
-  </si>
-  <si>
-    <t>idRegion</t>
-  </si>
-  <si>
-    <t>8BEC7653-46CD-F2E0-9830-CA915F8C1373</t>
-  </si>
-  <si>
-    <t>idUser</t>
-  </si>
-  <si>
-    <t>B9CE75B2-F56A-52F4-2402-0691648374D7</t>
-  </si>
-  <si>
-    <t>idUserDevice</t>
-  </si>
-  <si>
-    <t>CBEA499C-F80C-71E9-8E6E-48362CA13E64</t>
-  </si>
-  <si>
-    <t>kwh</t>
-  </si>
-  <si>
-    <t>5E11E6A3-7C82-40A3-39DE-32D3F0F53201</t>
-  </si>
-  <si>
-    <t>lastConnection</t>
-  </si>
-  <si>
-    <t>80B59BB6-F206-AC15-7CC1-25F0484CB116</t>
-  </si>
-  <si>
-    <t>lastName</t>
+    <t>measureTime</t>
   </si>
   <si>
     <t>0D61A7B9-DD3E-45F7-0461-0E63A231985C</t>
@@ -922,12 +904,6 @@
     <t>password</t>
   </si>
   <si>
-    <t>6FD2AB96-64C9-268D-FA84-F63872C1C776</t>
-  </si>
-  <si>
-    <t>power</t>
-  </si>
-  <si>
     <t>42C891A4-63BB-6418-FAA8-D17226EC5C01</t>
   </si>
   <si>
@@ -1687,7 +1663,7 @@
     <t>ElectricityCompany.id</t>
   </si>
   <si>
-    <t>DATE</t>
+    <t>TIMESTAMP</t>
   </si>
   <si>
     <t>PassRecoverRequest.id</t>
@@ -1901,7 +1877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:H229"/>
+  <dimension ref="A2:H227"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.61328125" customWidth="true" bestFit="true"/>
@@ -1921,789 +1897,789 @@
     </row>
     <row r="4" ht="18.0" customHeight="true">
       <c r="A4" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="5" ht="18.0" customHeight="true">
       <c r="A5" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="true">
       <c r="B7" t="s" s="5">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" ht="18.0" customHeight="true">
       <c r="B8" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" ht="18.0" customHeight="true">
       <c r="B9" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" ht="18.0" customHeight="true">
       <c r="B10" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" ht="18.0" customHeight="true">
       <c r="B11" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" ht="18.0" customHeight="true">
       <c r="B12" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" ht="18.0" customHeight="true">
       <c r="B15" t="s" s="5">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" ht="18.0" customHeight="true">
       <c r="B16" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="17" ht="18.0" customHeight="true">
       <c r="B17" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" ht="18.0" customHeight="true">
       <c r="B20" t="s" s="5">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" ht="18.0" customHeight="true">
       <c r="B21" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" ht="18.0" customHeight="true">
       <c r="B22" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="24" ht="18.0" customHeight="true">
       <c r="A24" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="E24" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="25" ht="18.0" customHeight="true">
       <c r="A25" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" ht="18.0" customHeight="true">
       <c r="B27" t="s" s="5">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28" ht="18.0" customHeight="true">
       <c r="B28" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" ht="18.0" customHeight="true">
       <c r="B29" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" ht="18.0" customHeight="true">
       <c r="B30" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" ht="18.0" customHeight="true">
       <c r="B31" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32" ht="18.0" customHeight="true">
       <c r="B32" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" ht="18.0" customHeight="true">
       <c r="B33" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" ht="18.0" customHeight="true">
       <c r="B34" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35" ht="18.0" customHeight="true">
       <c r="B35" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36" ht="18.0" customHeight="true">
       <c r="B36" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" ht="18.0" customHeight="true">
       <c r="B37" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" ht="18.0" customHeight="true">
       <c r="B38" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41" ht="18.0" customHeight="true">
       <c r="B41" t="s" s="5">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="42" ht="18.0" customHeight="true">
       <c r="B42" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G42" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="43" ht="18.0" customHeight="true">
       <c r="B43" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="46" ht="18.0" customHeight="true">
       <c r="B46" t="s" s="5">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="47" ht="18.0" customHeight="true">
       <c r="B47" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="48" ht="18.0" customHeight="true">
       <c r="B48" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="49" ht="18.0" customHeight="true">
       <c r="B49" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" ht="18.0" customHeight="true">
       <c r="A51" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="E51" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="52" ht="18.0" customHeight="true">
       <c r="A52" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" ht="18.0" customHeight="true">
       <c r="B54" t="s" s="5">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="55" ht="18.0" customHeight="true">
       <c r="B55" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="G55" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" ht="18.0" customHeight="true">
       <c r="B56" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" ht="18.0" customHeight="true">
       <c r="B57" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" ht="18.0" customHeight="true">
@@ -2711,488 +2687,488 @@
         <v>3</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" ht="18.0" customHeight="true">
       <c r="B61" t="s" s="5">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="62" ht="18.0" customHeight="true">
       <c r="B62" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G62" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="63" ht="18.0" customHeight="true">
       <c r="B63" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" ht="18.0" customHeight="true">
       <c r="B66" t="s" s="5">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="67" ht="18.0" customHeight="true">
       <c r="B67" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" ht="18.0" customHeight="true">
       <c r="B68" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" ht="18.0" customHeight="true">
       <c r="A70" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="E70" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="71" ht="18.0" customHeight="true">
       <c r="A71" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="73" ht="18.0" customHeight="true">
       <c r="B73" t="s" s="5">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="74" ht="18.0" customHeight="true">
       <c r="B74" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="E74" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F74" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="G74" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="75" ht="18.0" customHeight="true">
       <c r="B75" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="76" ht="18.0" customHeight="true">
       <c r="B76" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="77" ht="18.0" customHeight="true">
       <c r="B77" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="78" ht="18.0" customHeight="true">
       <c r="B78" s="6" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="79" ht="18.0" customHeight="true">
       <c r="B79" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="82" ht="18.0" customHeight="true">
       <c r="B82" t="s" s="5">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" ht="18.0" customHeight="true">
       <c r="B83" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G83" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="84" ht="18.0" customHeight="true">
       <c r="B84" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="87" ht="18.0" customHeight="true">
       <c r="B87" t="s" s="5">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="88" ht="18.0" customHeight="true">
       <c r="B88" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="89" ht="18.0" customHeight="true">
       <c r="B89" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>41</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="91" ht="18.0" customHeight="true">
       <c r="A91" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="E91" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="92" ht="18.0" customHeight="true">
       <c r="A92" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="94" ht="18.0" customHeight="true">
       <c r="B94" t="s" s="5">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="95" ht="18.0" customHeight="true">
       <c r="B95" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C95" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="E95" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F95" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E95" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="G95" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="96" ht="18.0" customHeight="true">
       <c r="B96" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="97" ht="18.0" customHeight="true">
@@ -3200,411 +3176,411 @@
         <v>3</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="100" ht="18.0" customHeight="true">
       <c r="B100" t="s" s="5">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="101" ht="18.0" customHeight="true">
       <c r="B101" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G101" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="102" ht="18.0" customHeight="true">
       <c r="B102" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="104" ht="18.0" customHeight="true">
       <c r="A104" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="E104" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="105" ht="18.0" customHeight="true">
       <c r="A105" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="107" ht="18.0" customHeight="true">
       <c r="B107" t="s" s="5">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="108" ht="18.0" customHeight="true">
       <c r="B108" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C108" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="E108" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F108" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E108" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="G108" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="109" ht="18.0" customHeight="true">
       <c r="B109" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="110" ht="18.0" customHeight="true">
       <c r="B110" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="111" ht="18.0" customHeight="true">
       <c r="B111" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="114" ht="18.0" customHeight="true">
       <c r="B114" t="s" s="5">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="115" ht="18.0" customHeight="true">
       <c r="B115" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G115" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="116" ht="18.0" customHeight="true">
       <c r="B116" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="117" ht="18.0" customHeight="true">
       <c r="B117" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="120" ht="18.0" customHeight="true">
       <c r="B120" t="s" s="5">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="121" ht="18.0" customHeight="true">
       <c r="B121" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="122" ht="18.0" customHeight="true">
       <c r="B122" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="124" ht="18.0" customHeight="true">
       <c r="A124" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D124" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="E124" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F124" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="125" ht="18.0" customHeight="true">
       <c r="A125" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="127" ht="18.0" customHeight="true">
       <c r="B127" t="s" s="5">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="128" ht="18.0" customHeight="true">
       <c r="B128" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C128" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D128" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D128" s="3" t="s">
+      <c r="E128" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F128" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E128" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F128" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="G128" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="129" ht="18.0" customHeight="true">
       <c r="B129" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="130" ht="18.0" customHeight="true">
@@ -3612,158 +3588,158 @@
         <v>3</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="133" ht="18.0" customHeight="true">
       <c r="B133" t="s" s="5">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="134" ht="18.0" customHeight="true">
       <c r="B134" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G134" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E134" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F134" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="135" ht="18.0" customHeight="true">
       <c r="B135" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G135" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="137" ht="18.0" customHeight="true">
       <c r="A137" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D137" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="E137" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="138" ht="18.0" customHeight="true">
       <c r="A138" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="140" ht="18.0" customHeight="true">
       <c r="B140" t="s" s="5">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="141" ht="18.0" customHeight="true">
       <c r="B141" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C141" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D141" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D141" s="3" t="s">
+      <c r="E141" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F141" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E141" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F141" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="G141" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="142" ht="18.0" customHeight="true">
       <c r="B142" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="143" ht="18.0" customHeight="true">
@@ -3771,406 +3747,406 @@
         <v>3</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H143" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="146" ht="18.0" customHeight="true">
       <c r="B146" t="s" s="5">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" ht="18.0" customHeight="true">
       <c r="B147" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G147" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G147" s="3" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="148" ht="18.0" customHeight="true">
       <c r="B148" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="150" ht="18.0" customHeight="true">
       <c r="A150" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D150" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="E150" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F150" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="151" ht="18.0" customHeight="true">
       <c r="A151" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="153" ht="18.0" customHeight="true">
       <c r="B153" t="s" s="5">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="154" ht="18.0" customHeight="true">
       <c r="B154" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C154" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D154" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D154" s="3" t="s">
+      <c r="E154" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F154" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E154" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F154" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="G154" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="155" ht="18.0" customHeight="true">
       <c r="B155" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="156" ht="18.0" customHeight="true">
       <c r="B156" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="157" ht="18.0" customHeight="true">
       <c r="B157" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="158" ht="18.0" customHeight="true">
       <c r="B158" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="161" ht="18.0" customHeight="true">
       <c r="B161" t="s" s="5">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="162" ht="18.0" customHeight="true">
       <c r="B162" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G162" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D162" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E162" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F162" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G162" s="3" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="163" ht="18.0" customHeight="true">
       <c r="B163" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G163" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="164" ht="18.0" customHeight="true">
       <c r="B164" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="166" ht="18.0" customHeight="true">
       <c r="A166" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D166" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="E166" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F166" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F166" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="167" ht="18.0" customHeight="true">
       <c r="A167" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>45</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="169" ht="18.0" customHeight="true">
       <c r="B169" t="s" s="5">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="170" ht="18.0" customHeight="true">
       <c r="B170" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C170" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D170" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D170" s="3" t="s">
+      <c r="E170" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F170" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E170" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F170" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="G170" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="171" ht="18.0" customHeight="true">
       <c r="B171" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E171" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F171" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H171" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="172" ht="18.0" customHeight="true">
       <c r="B172" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E172" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F172" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="173" ht="18.0" customHeight="true">
@@ -4178,768 +4154,722 @@
         <v>3</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F173" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="176" ht="18.0" customHeight="true">
       <c r="B176" t="s" s="5">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="177" ht="18.0" customHeight="true">
       <c r="B177" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G177" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="C177" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D177" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E177" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F177" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G177" s="3" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="178" ht="18.0" customHeight="true">
       <c r="B178" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="181" ht="18.0" customHeight="true">
       <c r="B181" t="s" s="5">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="182" ht="18.0" customHeight="true">
       <c r="B182" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="183" ht="18.0" customHeight="true">
       <c r="B183" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C183" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="185" ht="18.0" customHeight="true">
       <c r="A185" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D185" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B185" s="2" t="s">
+      <c r="E185" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F185" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F185" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="186" ht="18.0" customHeight="true">
       <c r="A186" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="188" ht="18.0" customHeight="true">
       <c r="B188" t="s" s="5">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="189" ht="18.0" customHeight="true">
       <c r="B189" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C189" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D189" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D189" s="3" t="s">
+      <c r="E189" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F189" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E189" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F189" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="G189" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="190" ht="18.0" customHeight="true">
       <c r="B190" s="6" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>379</v>
+        <v>330</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E190" s="8" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="F190" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="191" ht="18.0" customHeight="true">
       <c r="B191" s="6" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>374</v>
+        <v>330</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E191" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F191" s="8" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="192" ht="18.0" customHeight="true">
       <c r="B192" s="6" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F192" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="193" ht="18.0" customHeight="true">
       <c r="B193" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="D193" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="H193" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="196" ht="18.0" customHeight="true">
+      <c r="B196" t="s" s="5">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="197" ht="18.0" customHeight="true">
+      <c r="B197" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="198" ht="18.0" customHeight="true">
+      <c r="B198" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F198" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G198" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="201" ht="18.0" customHeight="true">
+      <c r="B201" t="s" s="5">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="202" ht="18.0" customHeight="true">
+      <c r="B202" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="H202" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="203" ht="18.0" customHeight="true">
+      <c r="B203" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C203" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E203" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="F203" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="G203" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="H203" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="205" ht="18.0" customHeight="true">
+      <c r="A205" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="206" ht="18.0" customHeight="true">
+      <c r="A206" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C206" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E206" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F206" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="208" ht="18.0" customHeight="true">
+      <c r="B208" t="s" s="5">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="209" ht="18.0" customHeight="true">
+      <c r="B209" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="G209" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="E193" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="F193" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="G193" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="H193" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="194" ht="18.0" customHeight="true">
-      <c r="B194" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C194" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="D194" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="E194" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="F194" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="G194" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="H194" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="195" ht="18.0" customHeight="true">
-      <c r="B195" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C195" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="D195" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="E195" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="F195" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="G195" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="H195" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="198" ht="18.0" customHeight="true">
-      <c r="B198" t="s" s="5">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="199" ht="18.0" customHeight="true">
-      <c r="B199" s="3" t="s">
+      <c r="H209" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="C199" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D199" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E199" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F199" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G199" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="200" ht="18.0" customHeight="true">
-      <c r="B200" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="C200" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D200" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="E200" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F200" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="G200" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="203" ht="18.0" customHeight="true">
-      <c r="B203" t="s" s="5">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="204" ht="18.0" customHeight="true">
-      <c r="B204" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C204" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D204" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="E204" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F204" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="G204" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="H204" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="205" ht="18.0" customHeight="true">
-      <c r="B205" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C205" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D205" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="E205" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="F205" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="G205" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="H205" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="207" ht="18.0" customHeight="true">
-      <c r="A207" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="208" ht="18.0" customHeight="true">
-      <c r="A208" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B208" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C208" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="D208" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="E208" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="F208" s="6" t="s">
-        <v>326</v>
-      </c>
     </row>
     <row r="210" ht="18.0" customHeight="true">
-      <c r="B210" t="s" s="5">
-        <v>332</v>
+      <c r="B210" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C210" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="D210" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="E210" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="F210" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="G210" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="H210" s="6" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="211" ht="18.0" customHeight="true">
-      <c r="B211" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C211" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="E211" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F211" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="G211" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="H211" s="3" t="s">
-        <v>329</v>
+      <c r="B211" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C211" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D211" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="E211" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="F211" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="G211" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="H211" s="6" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="212" ht="18.0" customHeight="true">
       <c r="B212" s="6" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="D212" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E212" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F212" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="213" ht="18.0" customHeight="true">
       <c r="B213" s="6" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>374</v>
+        <v>330</v>
       </c>
       <c r="D213" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E213" s="8" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="F213" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H213" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="214" ht="18.0" customHeight="true">
       <c r="B214" s="6" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D214" s="8" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E214" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F214" s="8" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="215" ht="18.0" customHeight="true">
       <c r="B215" s="6" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D215" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E215" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F215" s="8" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H215" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="216" ht="18.0" customHeight="true">
       <c r="B216" s="6" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="D216" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E216" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="F216" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="G216" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="H216" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="219" ht="18.0" customHeight="true">
+      <c r="B219" t="s" s="5">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="220" ht="18.0" customHeight="true">
+      <c r="B220" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D220" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="F216" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="G216" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="H216" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="217" ht="18.0" customHeight="true">
-      <c r="B217" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C217" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="D217" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="E217" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="F217" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="G217" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="H217" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="218" ht="18.0" customHeight="true">
-      <c r="B218" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C218" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="D218" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="E218" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="F218" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="G218" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="H218" s="6" t="s">
-        <v>326</v>
+      <c r="E220" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="221" ht="18.0" customHeight="true">
-      <c r="B221" t="s" s="5">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="222" ht="18.0" customHeight="true">
-      <c r="B222" s="3" t="s">
+      <c r="B221" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E221" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="F221" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G221" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="224" ht="18.0" customHeight="true">
+      <c r="B224" t="s" s="5">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="225" ht="18.0" customHeight="true">
+      <c r="B225" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="H225" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="C222" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E222" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F222" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G222" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="223" ht="18.0" customHeight="true">
-      <c r="B223" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="C223" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D223" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="E223" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="F223" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="G223" s="6" t="s">
-        <v>326</v>
-      </c>
     </row>
     <row r="226" ht="18.0" customHeight="true">
-      <c r="B226" t="s" s="5">
-        <v>348</v>
+      <c r="B226" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C226" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E226" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="F226" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="G226" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="H226" s="6" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="227" ht="18.0" customHeight="true">
-      <c r="B227" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C227" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="E227" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F227" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="G227" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="H227" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="228" ht="18.0" customHeight="true">
-      <c r="B228" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C228" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D228" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E228" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="F228" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="G228" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="229" ht="18.0" customHeight="true">
-      <c r="B229" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C229" s="8" t="s">
+      <c r="B227" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C227" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D229" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="E229" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="F229" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="G229" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="H229" s="6" t="s">
-        <v>326</v>
+      <c r="D227" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E227" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="F227" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="G227" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="H227" s="6" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -5080,40 +5010,40 @@
     <dataValidation type="list" sqref="A186" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B200" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B198" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D205" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D203" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E205" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E203" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F205" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F203" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A208" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="A206" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B223" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="B221" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>null!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D228" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D226" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D229" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="D227" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>lov_4!B1:B65000</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E228" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E226" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E229" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="E227" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F228" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F226" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F229" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
+    <dataValidation type="list" sqref="F227" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Entered value is not in valid list of values! _x000a_Choose item from drop down list." showErrorMessage="true">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5130,18 +5060,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -5396,7 +5326,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5452,23 +5382,23 @@
         <v>62</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -5484,103 +5414,103 @@
         <v>69</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>83</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="24">
@@ -5684,12 +5614,12 @@
         <v>108</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>109</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>3</v>
@@ -5697,7 +5627,7 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>3</v>
@@ -5705,7 +5635,7 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>3</v>
@@ -5713,7 +5643,7 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>3</v>
@@ -5721,10 +5651,10 @@
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -5789,22 +5719,6 @@
       </c>
       <c r="B49" s="8" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -5820,82 +5734,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -5911,98 +5825,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -6018,18 +5932,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -6045,546 +5959,546 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -6600,10 +6514,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
